--- a/outputs/01a04fdf-3751-72e2-88f1-daf19b8b9d1d/comprehensive_budget.xlsx
+++ b/outputs/01a04fdf-3751-72e2-88f1-daf19b8b9d1d/comprehensive_budget.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Start" sheetId="1" r:id="R29a9971798eb4675"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Tuesday Review" sheetId="2" r:id="Rb3262cc55c7a4fe9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. This Week" sheetId="3" r:id="Rf5e99455921b4529"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Money Plan" sheetId="4" r:id="R91f0ee20a002451c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Savings &amp; Debt" sheetId="5" r:id="R6dc5a0fe1c9649d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. History" sheetId="6" r:id="R93cca396501b4ad2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Ledger" sheetId="7" r:id="Rdd2069a35d4b424f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Budget Inputs" sheetId="8" r:id="R74ffef3cdb3a4a49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Funding Detail" sheetId="9" r:id="R440d7ae26efc4a82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Debt Detail" sheetId="10" r:id="R35a1f9c7e1b04dc5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Promo Detail" sheetId="11" r:id="R903bfa5e44b44d3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Account Snapshots" sheetId="12" r:id="R43c93c5e63cb4e1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Pending Review" sheetId="13" r:id="Rc296076c31934464"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Rules" sheetId="14" r:id="R3323d7a11cff4af5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Sources" sheetId="15" r:id="R33e3520749304973"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Start" sheetId="1" r:id="R8dce6b1616b44a7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Tuesday Review" sheetId="2" r:id="R20f8461391724fc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. This Week" sheetId="3" r:id="R63f3503aa61a4806"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Money Plan" sheetId="4" r:id="R39f6aa95fd3d4945"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Savings &amp; Debt" sheetId="5" r:id="Rb9845a1e90d0469c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. History" sheetId="6" r:id="R6e8d62f2685446fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Ledger" sheetId="7" r:id="R2cd3accae9fc4d5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Budget Inputs" sheetId="8" r:id="Rdf917bcb6cf2450f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Funding Detail" sheetId="9" r:id="R2b8d8271aa944d5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Debt Detail" sheetId="10" r:id="R4817fb1a492140e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Promo Detail" sheetId="11" r:id="Rd338409f71d74478"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Account Snapshots" sheetId="12" r:id="R41f15c41e3524239"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Pending Review" sheetId="13" r:id="Ra17a62bfcbe949b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Rules" sheetId="14" r:id="Re84c0c0b40724d21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Sources" sheetId="15" r:id="Ra37e92f0c0cf43c2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -27,13 +27,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
+  <x:numFmts count="5">
     <x:numFmt numFmtId="200" formatCode="$#,##0.00;[Red]($#,##0.00);-"/>
     <x:numFmt numFmtId="201" formatCode="0.0000"/>
     <x:numFmt numFmtId="202" formatCode="CA$#,##0.00;[Red](CA$#,##0.00);-"/>
     <x:numFmt numFmtId="203" formatCode="mmm d, yyyy"/>
+    <x:numFmt numFmtId="204" formatCode="mmm d"/>
   </x:numFmts>
-  <x:fonts count="23">
+  <x:fonts count="24">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -79,6 +80,17 @@
     <x:font>
       <x:b/>
       <x:sz val="12"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="12"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="12"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
@@ -89,11 +101,6 @@
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
-      <x:sz val="12"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:sz val="12"/>
       <x:name val="Carlito"/>
     </x:font>
@@ -565,7 +572,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="291">
+  <x:cellXfs count="336">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -721,8 +728,9 @@
     <x:xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="7" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="7" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="7" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="7" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="4" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -735,22 +743,111 @@
     <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="10" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="0" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="0" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="0" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="10" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="6" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="5" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="5" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="5" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="10" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="8" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="9" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="9" fillId="10" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="9" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
     <x:xf numFmtId="200" fontId="7" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="7" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="7" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="7" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -768,127 +865,154 @@
     <x:xf numFmtId="200" fontId="7" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
     <x:xf numFmtId="200" fontId="7" fillId="10" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="4" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
     <x:xf numFmtId="203" fontId="4" fillId="10" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="5" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="8" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="10" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="11" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="11" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="11" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="11" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="11" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="11" fillId="10" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="11" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="12" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="9" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="203" fontId="11" fillId="10" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="9" fillId="10" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="12" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="10" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="12" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="6" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="13" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="6" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="12" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="12" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="13" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="13" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -913,9 +1037,6 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -960,39 +1081,39 @@
     <x:xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="203" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="203" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="11" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="14" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="200" fontId="15" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="15" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="15" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="16" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="7" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="7" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1000,13 +1121,13 @@
     <x:xf numFmtId="200" fontId="7" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="7" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="7" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="15" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="7" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1015,37 +1136,34 @@
     <x:xf numFmtId="200" fontId="7" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="7" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="17" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="11" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="11" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="11" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="18" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1150,22 +1268,22 @@
     <x:xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="15" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="16" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="15" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="16" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="12" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="19" fillId="12" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="20" fillId="12" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="20" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="21" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1176,62 +1294,56 @@
     <x:xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="11" fillId="10" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="11" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="17" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="200" fontId="9" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="12" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="21" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="22" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="18" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="6" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="12" fillId="6" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="12" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="11" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="22" fillId="12" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="12" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="12" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="12" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="20">
+  <x:dxfs count="24">
     <x:dxf>
       <x:font>
         <x:b/>
@@ -1266,6 +1378,50 @@
     </x:dxf>
     <x:dxf>
       <x:font>
+        <x:color rgb="FFB91C1C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE9E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFB91C1C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE9E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFB91C1C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE9E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFB91C1C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE9E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
         <x:color rgb="FFB91C1C"/>
       </x:font>
       <x:fill>
@@ -1659,304 +1815,304 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="192" t="str">
+      <x:c r="A1" s="240" t="str">
         <x:v>Start — Weekly Cash Plan</x:v>
       </x:c>
-      <x:c r="B1" s="192"/>
-      <x:c r="C1" s="192"/>
-      <x:c r="D1" s="131"/>
-      <x:c r="E1" s="192" t="str">
+      <x:c r="B1" s="240"/>
+      <x:c r="C1" s="240"/>
+      <x:c r="D1" s="173"/>
+      <x:c r="E1" s="240" t="str">
         <x:v>Import checkpoints</x:v>
       </x:c>
-      <x:c r="F1" s="192"/>
-      <x:c r="G1" s="192"/>
-      <x:c r="H1" s="192"/>
+      <x:c r="F1" s="240"/>
+      <x:c r="G1" s="240"/>
+      <x:c r="H1" s="240"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="130" t="str">
+      <x:c r="A2" s="172" t="str">
         <x:v>Open this page first. It answers whether this week’s plan can be funded from Wells and the exact transfer needed. Use Tuesday Review to complete the actions; use This Week only for spending analysis.</x:v>
       </x:c>
-      <x:c r="B2" s="130"/>
-      <x:c r="C2" s="130"/>
-      <x:c r="D2" s="131"/>
-      <x:c r="E2" s="130" t="str">
+      <x:c r="B2" s="172"/>
+      <x:c r="C2" s="172"/>
+      <x:c r="D2" s="173"/>
+      <x:c r="E2" s="172" t="str">
         <x:v>Green is formula-based: the expected visible entry count, pending total, and anchor check must match the ledger. A received screenshot alone is not verification.</x:v>
       </x:c>
-      <x:c r="F2" s="130"/>
-      <x:c r="G2" s="130"/>
-      <x:c r="H2" s="130"/>
+      <x:c r="F2" s="172"/>
+      <x:c r="G2" s="172"/>
+      <x:c r="H2" s="172"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="131"/>
-      <x:c r="B3" s="131"/>
-      <x:c r="C3" s="131"/>
-      <x:c r="D3" s="131"/>
-      <x:c r="E3" s="131"/>
-      <x:c r="F3" s="131"/>
-      <x:c r="G3" s="131"/>
-      <x:c r="H3" s="131"/>
+      <x:c r="A3" s="173"/>
+      <x:c r="B3" s="173"/>
+      <x:c r="C3" s="173"/>
+      <x:c r="D3" s="173"/>
+      <x:c r="E3" s="173"/>
+      <x:c r="F3" s="173"/>
+      <x:c r="G3" s="173"/>
+      <x:c r="H3" s="173"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="132" t="str">
+      <x:c r="A4" s="174" t="str">
         <x:v>Today’s cash plan — Sep 9</x:v>
       </x:c>
-      <x:c r="B4" s="132"/>
-      <x:c r="C4" s="132"/>
-      <x:c r="D4" s="131"/>
-      <x:c r="E4" s="132" t="str">
+      <x:c r="B4" s="174"/>
+      <x:c r="C4" s="174"/>
+      <x:c r="D4" s="173"/>
+      <x:c r="E4" s="174" t="str">
         <x:v>Source checkpoints</x:v>
       </x:c>
-      <x:c r="F4" s="132"/>
-      <x:c r="G4" s="132"/>
-      <x:c r="H4" s="132"/>
+      <x:c r="F4" s="174"/>
+      <x:c r="G4" s="174"/>
+      <x:c r="H4" s="174"/>
     </x:row>
     <x:row r="5" ht="29" customHeight="1">
-      <x:c r="A5" s="133" t="str">
+      <x:c r="A5" s="175" t="str">
         <x:v>Wells available now</x:v>
       </x:c>
-      <x:c r="B5" s="274" t="n">
+      <x:c r="B5" s="196" t="n">
         <x:f>'2. Tuesday Review'!E22</x:f>
         <x:v>1227.78</x:v>
       </x:c>
-      <x:c r="C5" s="275" t="str">
+      <x:c r="C5" s="198" t="str">
         <x:v>After pending Fidelity debit</x:v>
       </x:c>
-      <x:c r="D5" s="131"/>
-      <x:c r="E5" s="145" t="str">
+      <x:c r="D5" s="173"/>
+      <x:c r="E5" s="184" t="str">
         <x:v>Import status</x:v>
       </x:c>
-      <x:c r="F5" s="146" t="str">
+      <x:c r="F5" s="185" t="str">
         <x:v>Account</x:v>
       </x:c>
-      <x:c r="G5" s="146" t="str">
+      <x:c r="G5" s="185" t="str">
         <x:v>Latest posted anchor</x:v>
       </x:c>
-      <x:c r="H5" s="147" t="str">
+      <x:c r="H5" s="186" t="str">
         <x:v>Next statement check</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="141" t="str">
+      <x:c r="A6" s="181" t="str">
         <x:v>Cash required today</x:v>
       </x:c>
-      <x:c r="B6" s="276" t="n">
+      <x:c r="B6" s="321" t="n">
         <x:f>'2. Tuesday Review'!E21</x:f>
-        <x:v>1348.2883076923076</x:v>
-      </x:c>
-      <x:c r="C6" s="277" t="str">
-        <x:v>Including scheduled PayPal savings transfers</x:v>
-      </x:c>
-      <x:c r="D6" s="131"/>
-      <x:c r="E6" s="278" t="str">
+        <x:v>1226.78</x:v>
+      </x:c>
+      <x:c r="C6" s="322" t="str">
+        <x:v>Rent uses only Wells capacity after required actions</x:v>
+      </x:c>
+      <x:c r="D6" s="173"/>
+      <x:c r="E6" s="323" t="str">
         <x:f>'Support - Account Snapshots'!I12</x:f>
         <x:v>Verified</x:v>
       </x:c>
-      <x:c r="F6" s="279" t="str">
+      <x:c r="F6" s="324" t="str">
         <x:v>Wells Fargo</x:v>
       </x:c>
-      <x:c r="G6" s="279" t="str">
+      <x:c r="G6" s="324" t="str">
         <x:v>Sep 8 · Chase ePay · $1,141.57</x:v>
       </x:c>
-      <x:c r="H6" s="280" t="str">
+      <x:c r="H6" s="325" t="str">
         <x:v>Statement received Sep 8</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="141" t="str">
+      <x:c r="A7" s="181" t="str">
         <x:v>Move from Wealthfront</x:v>
       </x:c>
-      <x:c r="B7" s="276" t="n">
+      <x:c r="B7" s="321" t="n">
         <x:f>'2. Tuesday Review'!E24</x:f>
-        <x:v>121.50830769230765</x:v>
-      </x:c>
-      <x:c r="C7" s="277" t="str">
-        <x:v>Covers the gap while retaining $1 in Wells</x:v>
-      </x:c>
-      <x:c r="D7" s="131"/>
-      <x:c r="E7" s="281" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C7" s="322" t="str">
+        <x:v>Only if still short after net rent funding; retain $1 in Wells</x:v>
+      </x:c>
+      <x:c r="D7" s="173"/>
+      <x:c r="E7" s="326" t="str">
         <x:f>'Support - Account Snapshots'!I13</x:f>
         <x:v>Verified</x:v>
       </x:c>
-      <x:c r="F7" s="282" t="str">
+      <x:c r="F7" s="327" t="str">
         <x:v>Wealthfront</x:v>
       </x:c>
-      <x:c r="G7" s="282" t="str">
+      <x:c r="G7" s="327" t="str">
         <x:v>Sep 2 · Wells transfer · $631.34</x:v>
       </x:c>
-      <x:c r="H7" s="283" t="str">
+      <x:c r="H7" s="328" t="str">
         <x:v>Confirm statement date</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="284" t="str">
+      <x:c r="A8" s="329" t="str">
         <x:v>Wells left after plan</x:v>
       </x:c>
-      <x:c r="B8" s="285" t="n">
+      <x:c r="B8" s="330" t="n">
         <x:f>B5+B7-B6</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C8" s="286" t="str">
+      <x:c r="C8" s="331" t="str">
         <x:v>This must match Tuesday Review</x:v>
       </x:c>
-      <x:c r="D8" s="131"/>
-      <x:c r="E8" s="281" t="str">
+      <x:c r="D8" s="173"/>
+      <x:c r="E8" s="326" t="str">
         <x:f>IF(AND('Support - Account Snapshots'!I14="Verified",'Support - Account Snapshots'!I15="Verified"),"Verified","Source check needed")</x:f>
         <x:v>Verified</x:v>
       </x:c>
-      <x:c r="F8" s="282" t="str">
+      <x:c r="F8" s="327" t="str">
         <x:v>Chase Sapphire</x:v>
       </x:c>
-      <x:c r="G8" s="282" t="str">
+      <x:c r="G8" s="327" t="str">
         <x:v>Sep 6 · Card payment · $1,141.57</x:v>
       </x:c>
-      <x:c r="H8" s="283" t="str">
+      <x:c r="H8" s="328" t="str">
         <x:v>Check after Sep 27</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="131"/>
-      <x:c r="B9" s="131"/>
-      <x:c r="C9" s="131"/>
-      <x:c r="D9" s="131"/>
-      <x:c r="E9" s="281" t="str">
+      <x:c r="A9" s="173"/>
+      <x:c r="B9" s="173"/>
+      <x:c r="C9" s="173"/>
+      <x:c r="D9" s="173"/>
+      <x:c r="E9" s="326" t="str">
         <x:f>'Support - Account Snapshots'!I16</x:f>
         <x:v>Verified</x:v>
       </x:c>
-      <x:c r="F9" s="282" t="str">
+      <x:c r="F9" s="327" t="str">
         <x:v>Citi AAdvantage</x:v>
       </x:c>
-      <x:c r="G9" s="282" t="str">
+      <x:c r="G9" s="327" t="str">
         <x:v>Sep 3 · PCC Ingleside · $68.75</x:v>
       </x:c>
-      <x:c r="H9" s="283" t="str">
+      <x:c r="H9" s="328" t="str">
         <x:v>Check after Oct 7</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="131"/>
-      <x:c r="B10" s="131"/>
-      <x:c r="C10" s="131"/>
-      <x:c r="D10" s="131"/>
-      <x:c r="E10" s="281" t="str">
+      <x:c r="A10" s="173"/>
+      <x:c r="B10" s="173"/>
+      <x:c r="C10" s="173"/>
+      <x:c r="D10" s="173"/>
+      <x:c r="E10" s="326" t="str">
         <x:f>'Support - Account Snapshots'!I17</x:f>
         <x:v>Verified</x:v>
       </x:c>
-      <x:c r="F10" s="282" t="str">
+      <x:c r="F10" s="327" t="str">
         <x:v>Prime Visa</x:v>
       </x:c>
-      <x:c r="G10" s="282" t="str">
+      <x:c r="G10" s="327" t="str">
         <x:v>No activity shown · $0 balance</x:v>
       </x:c>
-      <x:c r="H10" s="283" t="str">
+      <x:c r="H10" s="328" t="str">
         <x:v>Confirm statement date</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="131"/>
-      <x:c r="B11" s="131"/>
-      <x:c r="C11" s="131"/>
-      <x:c r="D11" s="131"/>
-      <x:c r="E11" s="281" t="str">
+      <x:c r="A11" s="173"/>
+      <x:c r="B11" s="173"/>
+      <x:c r="C11" s="173"/>
+      <x:c r="D11" s="173"/>
+      <x:c r="E11" s="326" t="str">
         <x:f>'Support - Account Snapshots'!I18</x:f>
         <x:v>Verified</x:v>
       </x:c>
-      <x:c r="F11" s="282" t="str">
+      <x:c r="F11" s="327" t="str">
         <x:v>Discover</x:v>
       </x:c>
-      <x:c r="G11" s="282" t="str">
+      <x:c r="G11" s="327" t="str">
         <x:v>Aug 11 · internet payment · $48.27</x:v>
       </x:c>
-      <x:c r="H11" s="283" t="str">
+      <x:c r="H11" s="328" t="str">
         <x:v>Confirm statement date</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
-      <x:c r="A12" s="131"/>
-      <x:c r="B12" s="131"/>
-      <x:c r="C12" s="131"/>
-      <x:c r="D12" s="131"/>
-      <x:c r="E12" s="281" t="str">
+      <x:c r="A12" s="173"/>
+      <x:c r="B12" s="173"/>
+      <x:c r="C12" s="173"/>
+      <x:c r="D12" s="173"/>
+      <x:c r="E12" s="326" t="str">
         <x:f>'Support - Account Snapshots'!I19</x:f>
         <x:v>Verified</x:v>
       </x:c>
-      <x:c r="F12" s="282" t="str">
+      <x:c r="F12" s="327" t="str">
         <x:v>Capital One</x:v>
       </x:c>
-      <x:c r="G12" s="282" t="str">
+      <x:c r="G12" s="327" t="str">
         <x:v>No activity shown · $0 balance</x:v>
       </x:c>
-      <x:c r="H12" s="283" t="str">
+      <x:c r="H12" s="328" t="str">
         <x:v>Confirm statement date</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="30" customHeight="1">
-      <x:c r="A13" s="131"/>
-      <x:c r="B13" s="131"/>
-      <x:c r="C13" s="131"/>
-      <x:c r="D13" s="131"/>
-      <x:c r="E13" s="281" t="str">
+      <x:c r="A13" s="173"/>
+      <x:c r="B13" s="173"/>
+      <x:c r="C13" s="173"/>
+      <x:c r="D13" s="173"/>
+      <x:c r="E13" s="326" t="str">
         <x:f>'Support - Account Snapshots'!I20</x:f>
         <x:v>Verified</x:v>
       </x:c>
-      <x:c r="F13" s="282" t="str">
+      <x:c r="F13" s="327" t="str">
         <x:v>PayPal Credit</x:v>
       </x:c>
-      <x:c r="G13" s="282" t="str">
+      <x:c r="G13" s="327" t="str">
         <x:v>Sep 2 · payment · $148.65</x:v>
       </x:c>
-      <x:c r="H13" s="283" t="str">
+      <x:c r="H13" s="328" t="str">
         <x:v>Confirm statement date</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="30" customHeight="1">
-      <x:c r="A14" s="131"/>
-      <x:c r="B14" s="131"/>
-      <x:c r="C14" s="131"/>
-      <x:c r="D14" s="131"/>
-      <x:c r="E14" s="287" t="str">
+      <x:c r="A14" s="173"/>
+      <x:c r="B14" s="173"/>
+      <x:c r="C14" s="173"/>
+      <x:c r="D14" s="173"/>
+      <x:c r="E14" s="332" t="str">
         <x:v>Not due</x:v>
       </x:c>
-      <x:c r="F14" s="288" t="str">
+      <x:c r="F14" s="333" t="str">
         <x:v>RBC Canada</x:v>
       </x:c>
-      <x:c r="G14" s="288" t="str">
+      <x:c r="G14" s="333" t="str">
         <x:v>Month-end loan + insurance</x:v>
       </x:c>
-      <x:c r="H14" s="289" t="str">
+      <x:c r="H14" s="334" t="str">
         <x:v>Check at month-end</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="131"/>
-      <x:c r="B15" s="131"/>
-      <x:c r="C15" s="131"/>
-      <x:c r="D15" s="131"/>
-      <x:c r="E15" s="131"/>
-      <x:c r="F15" s="131"/>
-      <x:c r="G15" s="131"/>
-      <x:c r="H15" s="131"/>
+      <x:c r="A15" s="173"/>
+      <x:c r="B15" s="173"/>
+      <x:c r="C15" s="173"/>
+      <x:c r="D15" s="173"/>
+      <x:c r="E15" s="173"/>
+      <x:c r="F15" s="173"/>
+      <x:c r="G15" s="173"/>
+      <x:c r="H15" s="173"/>
     </x:row>
     <x:row r="16" ht="28" customHeight="1">
-      <x:c r="A16" s="131"/>
-      <x:c r="B16" s="131"/>
-      <x:c r="C16" s="131"/>
-      <x:c r="D16" s="131"/>
-      <x:c r="E16" s="290" t="str">
+      <x:c r="A16" s="173"/>
+      <x:c r="B16" s="173"/>
+      <x:c r="C16" s="173"/>
+      <x:c r="D16" s="173"/>
+      <x:c r="E16" s="335" t="str">
         <x:v>Fidelity is verified through Wells Fargo transfers. PayPal Credit is reviewed weekly because its promotional balances have payment deadlines.</x:v>
       </x:c>
-      <x:c r="F16" s="290"/>
-      <x:c r="G16" s="290"/>
-      <x:c r="H16" s="290"/>
+      <x:c r="F16" s="335"/>
+      <x:c r="G16" s="335"/>
+      <x:c r="H16" s="335"/>
     </x:row>
     <x:row r="17" ht="28" customHeight="1">
-      <x:c r="A17" s="131"/>
-      <x:c r="B17" s="131"/>
-      <x:c r="C17" s="131"/>
-      <x:c r="D17" s="131"/>
-      <x:c r="E17" s="290"/>
-      <x:c r="F17" s="290"/>
-      <x:c r="G17" s="290"/>
-      <x:c r="H17" s="290"/>
+      <x:c r="A17" s="173"/>
+      <x:c r="B17" s="173"/>
+      <x:c r="C17" s="173"/>
+      <x:c r="D17" s="173"/>
+      <x:c r="E17" s="335"/>
+      <x:c r="F17" s="335"/>
+      <x:c r="G17" s="335"/>
+      <x:c r="H17" s="335"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1969,8 +2125,8 @@
     <x:mergeCell ref="E16:H17"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="E6:E13">
-    <x:cfRule type="containsText" dxfId="18" priority="1" operator="containsText" text="Needs"/>
-    <x:cfRule type="containsText" dxfId="19" priority="2" operator="containsText" text="Source check"/>
+    <x:cfRule type="containsText" dxfId="22" priority="1" operator="containsText" text="Needs"/>
+    <x:cfRule type="containsText" dxfId="23" priority="2" operator="containsText" text="Source check"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2970,10 +3126,10 @@
     <x:mergeCell ref="A10:J10"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="I12:I21">
-    <x:cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="Verified"/>
-    <x:cfRule type="containsText" dxfId="15" priority="2" operator="containsText" text="Missing"/>
-    <x:cfRule type="containsText" dxfId="16" priority="3" operator="containsText" text="mismatch"/>
-    <x:cfRule type="containsText" dxfId="17" priority="4" operator="containsText" text="Needs"/>
+    <x:cfRule type="containsText" dxfId="18" priority="1" operator="containsText" text="Verified"/>
+    <x:cfRule type="containsText" dxfId="19" priority="2" operator="containsText" text="Missing"/>
+    <x:cfRule type="containsText" dxfId="20" priority="3" operator="containsText" text="mismatch"/>
+    <x:cfRule type="containsText" dxfId="21" priority="4" operator="containsText" text="Needs"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3444,462 +3600,462 @@
       <x:c r="F2" s="5"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="171" t="str">
+      <x:c r="A4" s="220" t="str">
         <x:v>Exact merchant / description</x:v>
       </x:c>
-      <x:c r="B4" s="172" t="str">
+      <x:c r="B4" s="221" t="str">
         <x:v>Workbook category</x:v>
       </x:c>
-      <x:c r="C4" s="172" t="str">
+      <x:c r="C4" s="221" t="str">
         <x:v>Treatment</x:v>
       </x:c>
-      <x:c r="D4" s="172" t="str">
+      <x:c r="D4" s="221" t="str">
         <x:v>Bank category fallback</x:v>
       </x:c>
-      <x:c r="E4" s="172" t="str">
+      <x:c r="E4" s="221" t="str">
         <x:v>Fallback category</x:v>
       </x:c>
-      <x:c r="F4" s="173" t="str">
+      <x:c r="F4" s="222" t="str">
         <x:v>Fallback treatment</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="174" t="str">
+      <x:c r="A5" s="223" t="str">
         <x:v>H-E-B</x:v>
       </x:c>
-      <x:c r="B5" s="175" t="str">
+      <x:c r="B5" s="129" t="str">
         <x:v>H-E-B / groceries</x:v>
       </x:c>
-      <x:c r="C5" s="175" t="str">
+      <x:c r="C5" s="129" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="D5" s="175" t="str">
+      <x:c r="D5" s="129" t="str">
         <x:v>Groceries</x:v>
       </x:c>
-      <x:c r="E5" s="175" t="str">
+      <x:c r="E5" s="129" t="str">
         <x:v>H-E-B / groceries</x:v>
       </x:c>
-      <x:c r="F5" s="176" t="str">
+      <x:c r="F5" s="224" t="str">
         <x:v>Include</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="174" t="str">
+      <x:c r="A6" s="223" t="str">
         <x:v>DoorDash</x:v>
       </x:c>
-      <x:c r="B6" s="175" t="str">
+      <x:c r="B6" s="129" t="str">
         <x:v>DoorDash</x:v>
       </x:c>
-      <x:c r="C6" s="175" t="str">
+      <x:c r="C6" s="129" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="D6" s="175" t="str">
+      <x:c r="D6" s="129" t="str">
         <x:v>Restaurants</x:v>
       </x:c>
-      <x:c r="E6" s="175" t="str">
+      <x:c r="E6" s="129" t="str">
         <x:v>DoorDash</x:v>
       </x:c>
-      <x:c r="F6" s="176" t="str">
+      <x:c r="F6" s="224" t="str">
         <x:v>Include</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="174" t="str">
+      <x:c r="A7" s="223" t="str">
         <x:v>Starbucks</x:v>
       </x:c>
-      <x:c r="B7" s="175" t="str">
+      <x:c r="B7" s="129" t="str">
         <x:v>Starbucks</x:v>
       </x:c>
-      <x:c r="C7" s="175" t="str">
+      <x:c r="C7" s="129" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="D7" s="175" t="str">
+      <x:c r="D7" s="129" t="str">
         <x:v>Coffee Shops</x:v>
       </x:c>
-      <x:c r="E7" s="175" t="str">
+      <x:c r="E7" s="129" t="str">
         <x:v>Starbucks</x:v>
       </x:c>
-      <x:c r="F7" s="176" t="str">
+      <x:c r="F7" s="224" t="str">
         <x:v>Include</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="174" t="str">
+      <x:c r="A8" s="223" t="str">
         <x:v>INVINCIBLE APPCHARGE</x:v>
       </x:c>
-      <x:c r="B8" s="175" t="str">
+      <x:c r="B8" s="129" t="str">
         <x:v>Apple &amp; Invincibles</x:v>
       </x:c>
-      <x:c r="C8" s="175" t="str">
+      <x:c r="C8" s="129" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="D8" s="175" t="str">
+      <x:c r="D8" s="129" t="str">
         <x:v>Gas</x:v>
       </x:c>
-      <x:c r="E8" s="175" t="str">
+      <x:c r="E8" s="129" t="str">
         <x:v>Fuel</x:v>
       </x:c>
-      <x:c r="F8" s="176" t="str">
+      <x:c r="F8" s="224" t="str">
         <x:v>Include</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="174" t="str">
+      <x:c r="A9" s="223" t="str">
         <x:v>Apple</x:v>
       </x:c>
-      <x:c r="B9" s="175" t="str">
+      <x:c r="B9" s="129" t="str">
         <x:v>Apple &amp; Invincibles</x:v>
       </x:c>
-      <x:c r="C9" s="175" t="str">
+      <x:c r="C9" s="129" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="D9" s="175" t="str">
+      <x:c r="D9" s="129" t="str">
         <x:v>Pet Care</x:v>
       </x:c>
-      <x:c r="E9" s="175" t="str">
+      <x:c r="E9" s="129" t="str">
         <x:v>Pet costs</x:v>
       </x:c>
-      <x:c r="F9" s="176" t="str">
+      <x:c r="F9" s="224" t="str">
         <x:v>Include</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="174" t="str">
+      <x:c r="A10" s="223" t="str">
         <x:v>OpenAI</x:v>
       </x:c>
-      <x:c r="B10" s="175" t="str">
+      <x:c r="B10" s="129" t="str">
         <x:v>Subscriptions</x:v>
       </x:c>
-      <x:c r="C10" s="175" t="str">
+      <x:c r="C10" s="129" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="D10" s="175" t="str">
+      <x:c r="D10" s="129" t="str">
         <x:v>Utilities</x:v>
       </x:c>
-      <x:c r="E10" s="175" t="str">
+      <x:c r="E10" s="129" t="str">
         <x:v>Electricity</x:v>
       </x:c>
-      <x:c r="F10" s="176" t="str">
+      <x:c r="F10" s="224" t="str">
         <x:v>Include</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="174" t="str">
+      <x:c r="A11" s="223" t="str">
         <x:v>AMAZON MARKETPLACE</x:v>
       </x:c>
-      <x:c r="B11" s="175" t="str">
+      <x:c r="B11" s="129" t="str">
         <x:v>Shopping / personal care</x:v>
       </x:c>
-      <x:c r="C11" s="175" t="str">
+      <x:c r="C11" s="129" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="D11" s="175" t="str">
+      <x:c r="D11" s="129" t="str">
         <x:v>Internet</x:v>
       </x:c>
-      <x:c r="E11" s="175" t="str">
+      <x:c r="E11" s="129" t="str">
         <x:v>Spectrum internet</x:v>
       </x:c>
-      <x:c r="F11" s="176" t="str">
+      <x:c r="F11" s="224" t="str">
         <x:v>Include</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="174" t="str">
+      <x:c r="A12" s="223" t="str">
         <x:v>AMAZON PRIME MEMBERSHIP</x:v>
       </x:c>
-      <x:c r="B12" s="175" t="str">
+      <x:c r="B12" s="129" t="str">
         <x:v>Subscriptions</x:v>
       </x:c>
-      <x:c r="C12" s="175" t="str">
+      <x:c r="C12" s="129" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="D12" s="175" t="str">
+      <x:c r="D12" s="129" t="str">
         <x:v>Mobile Phone</x:v>
       </x:c>
-      <x:c r="E12" s="175" t="str">
+      <x:c r="E12" s="129" t="str">
         <x:v>Phone + Visible</x:v>
       </x:c>
-      <x:c r="F12" s="176" t="str">
+      <x:c r="F12" s="224" t="str">
         <x:v>Include</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="174" t="str">
+      <x:c r="A13" s="223" t="str">
         <x:v>365 MARKET</x:v>
       </x:c>
-      <x:c r="B13" s="175" t="str">
+      <x:c r="B13" s="129" t="str">
         <x:v>Work snacks</x:v>
       </x:c>
-      <x:c r="C13" s="175" t="str">
+      <x:c r="C13" s="129" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="D13" s="175" t="str">
+      <x:c r="D13" s="129" t="str">
         <x:v>Shopping</x:v>
       </x:c>
-      <x:c r="E13" s="175" t="str">
+      <x:c r="E13" s="129" t="str">
         <x:v>Shopping / personal care</x:v>
       </x:c>
-      <x:c r="F13" s="176" t="str">
+      <x:c r="F13" s="224" t="str">
         <x:v>Include</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="174" t="str">
+      <x:c r="A14" s="223" t="str">
         <x:v>Vape</x:v>
       </x:c>
-      <x:c r="B14" s="175" t="str">
+      <x:c r="B14" s="129" t="str">
         <x:v>Vapes</x:v>
       </x:c>
-      <x:c r="C14" s="175" t="str">
+      <x:c r="C14" s="129" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="D14" s="175" t="str">
+      <x:c r="D14" s="129" t="str">
         <x:v>Entertainment</x:v>
       </x:c>
-      <x:c r="E14" s="175" t="str">
+      <x:c r="E14" s="129" t="str">
         <x:v>Invincibles + other Apple</x:v>
       </x:c>
-      <x:c r="F14" s="176" t="str">
+      <x:c r="F14" s="224" t="str">
         <x:v>Include</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="174" t="str">
+      <x:c r="A15" s="223" t="str">
         <x:v>Direct Energy</x:v>
       </x:c>
-      <x:c r="B15" s="175" t="str">
+      <x:c r="B15" s="129" t="str">
         <x:v>Electricity</x:v>
       </x:c>
-      <x:c r="C15" s="175" t="str">
+      <x:c r="C15" s="129" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="D15" s="177" t="str"/>
-      <x:c r="E15" s="177" t="str"/>
-      <x:c r="F15" s="178" t="str"/>
+      <x:c r="D15" s="225" t="str"/>
+      <x:c r="E15" s="225" t="str"/>
+      <x:c r="F15" s="226" t="str"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="174" t="str">
+      <x:c r="A16" s="223" t="str">
         <x:v>Spectrum</x:v>
       </x:c>
-      <x:c r="B16" s="175" t="str">
+      <x:c r="B16" s="129" t="str">
         <x:v>Spectrum internet</x:v>
       </x:c>
-      <x:c r="C16" s="175" t="str">
+      <x:c r="C16" s="129" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="D16" s="177" t="str"/>
-      <x:c r="E16" s="177" t="str"/>
-      <x:c r="F16" s="178" t="str"/>
+      <x:c r="D16" s="225" t="str"/>
+      <x:c r="E16" s="225" t="str"/>
+      <x:c r="F16" s="226" t="str"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="174" t="str">
+      <x:c r="A17" s="223" t="str">
         <x:v>AT&amp;T</x:v>
       </x:c>
-      <x:c r="B17" s="175" t="str">
+      <x:c r="B17" s="129" t="str">
         <x:v>Phone + Visible</x:v>
       </x:c>
-      <x:c r="C17" s="175" t="str">
+      <x:c r="C17" s="129" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="D17" s="177" t="str"/>
-      <x:c r="E17" s="177" t="str"/>
-      <x:c r="F17" s="178" t="str"/>
+      <x:c r="D17" s="225" t="str"/>
+      <x:c r="E17" s="225" t="str"/>
+      <x:c r="F17" s="226" t="str"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="174" t="str">
+      <x:c r="A18" s="223" t="str">
         <x:v>Visible</x:v>
       </x:c>
-      <x:c r="B18" s="175" t="str">
+      <x:c r="B18" s="129" t="str">
         <x:v>Phone + Visible</x:v>
       </x:c>
-      <x:c r="C18" s="175" t="str">
+      <x:c r="C18" s="129" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="D18" s="177" t="str"/>
-      <x:c r="E18" s="177" t="str"/>
-      <x:c r="F18" s="178" t="str"/>
+      <x:c r="D18" s="225" t="str"/>
+      <x:c r="E18" s="225" t="str"/>
+      <x:c r="F18" s="226" t="str"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="174" t="str">
+      <x:c r="A19" s="223" t="str">
         <x:v>BudgetPetCare</x:v>
       </x:c>
-      <x:c r="B19" s="175" t="str">
+      <x:c r="B19" s="129" t="str">
         <x:v>Pet costs</x:v>
       </x:c>
-      <x:c r="C19" s="175" t="str">
+      <x:c r="C19" s="129" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="D19" s="177" t="str"/>
-      <x:c r="E19" s="177" t="str"/>
-      <x:c r="F19" s="178" t="str"/>
+      <x:c r="D19" s="225" t="str"/>
+      <x:c r="E19" s="225" t="str"/>
+      <x:c r="F19" s="226" t="str"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="174" t="str">
+      <x:c r="A20" s="223" t="str">
         <x:v>Nationwide Pet</x:v>
       </x:c>
-      <x:c r="B20" s="175" t="str">
+      <x:c r="B20" s="129" t="str">
         <x:v>Pet costs</x:v>
       </x:c>
-      <x:c r="C20" s="175" t="str">
+      <x:c r="C20" s="129" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="D20" s="177" t="str"/>
-      <x:c r="E20" s="177" t="str"/>
-      <x:c r="F20" s="178" t="str"/>
+      <x:c r="D20" s="225" t="str"/>
+      <x:c r="E20" s="225" t="str"/>
+      <x:c r="F20" s="226" t="str"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="174" t="str">
+      <x:c r="A21" s="223" t="str">
         <x:v>Coastal Cuts</x:v>
       </x:c>
-      <x:c r="B21" s="175" t="str">
+      <x:c r="B21" s="129" t="str">
         <x:v>Pet costs</x:v>
       </x:c>
-      <x:c r="C21" s="175" t="str">
+      <x:c r="C21" s="129" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="D21" s="177" t="str"/>
-      <x:c r="E21" s="177" t="str"/>
-      <x:c r="F21" s="178" t="str"/>
+      <x:c r="D21" s="225" t="str"/>
+      <x:c r="E21" s="225" t="str"/>
+      <x:c r="F21" s="226" t="str"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="174" t="str">
+      <x:c r="A22" s="223" t="str">
         <x:v>Gas Fusion</x:v>
       </x:c>
-      <x:c r="B22" s="175" t="str">
+      <x:c r="B22" s="129" t="str">
         <x:v>Fuel</x:v>
       </x:c>
-      <x:c r="C22" s="175" t="str">
+      <x:c r="C22" s="129" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="D22" s="177" t="str"/>
-      <x:c r="E22" s="177" t="str"/>
-      <x:c r="F22" s="178" t="str"/>
+      <x:c r="D22" s="225" t="str"/>
+      <x:c r="E22" s="225" t="str"/>
+      <x:c r="F22" s="226" t="str"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="174" t="str">
+      <x:c r="A23" s="223" t="str">
         <x:v>Exxon</x:v>
       </x:c>
-      <x:c r="B23" s="175" t="str">
+      <x:c r="B23" s="129" t="str">
         <x:v>Fuel</x:v>
       </x:c>
-      <x:c r="C23" s="175" t="str">
+      <x:c r="C23" s="129" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="D23" s="177" t="str"/>
-      <x:c r="E23" s="177" t="str"/>
-      <x:c r="F23" s="178" t="str"/>
+      <x:c r="D23" s="225" t="str"/>
+      <x:c r="E23" s="225" t="str"/>
+      <x:c r="F23" s="226" t="str"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="174" t="str">
+      <x:c r="A24" s="223" t="str">
         <x:v>Citi</x:v>
       </x:c>
-      <x:c r="B24" s="175" t="str">
+      <x:c r="B24" s="129" t="str">
         <x:v>Fuel</x:v>
       </x:c>
-      <x:c r="C24" s="175" t="str">
+      <x:c r="C24" s="129" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="D24" s="177" t="str"/>
-      <x:c r="E24" s="177" t="str"/>
-      <x:c r="F24" s="178" t="str"/>
+      <x:c r="D24" s="225" t="str"/>
+      <x:c r="E24" s="225" t="str"/>
+      <x:c r="F24" s="226" t="str"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="174" t="str">
+      <x:c r="A25" s="223" t="str">
         <x:v>Fidelity</x:v>
       </x:c>
-      <x:c r="B25" s="175" t="str">
+      <x:c r="B25" s="129" t="str">
         <x:v>Fidelity 401(k)</x:v>
       </x:c>
-      <x:c r="C25" s="175" t="str">
+      <x:c r="C25" s="129" t="str">
         <x:v>Transfer / verify</x:v>
       </x:c>
-      <x:c r="D25" s="177" t="str"/>
-      <x:c r="E25" s="177" t="str"/>
-      <x:c r="F25" s="178" t="str"/>
+      <x:c r="D25" s="225" t="str"/>
+      <x:c r="E25" s="225" t="str"/>
+      <x:c r="F25" s="226" t="str"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="174" t="str">
+      <x:c r="A26" s="223" t="str">
         <x:v>UMB</x:v>
       </x:c>
-      <x:c r="B26" s="175" t="str">
+      <x:c r="B26" s="129" t="str">
         <x:v>Rent set-aside</x:v>
       </x:c>
-      <x:c r="C26" s="175" t="str">
+      <x:c r="C26" s="129" t="str">
         <x:v>Transfer / verify</x:v>
       </x:c>
-      <x:c r="D26" s="177" t="str"/>
-      <x:c r="E26" s="177" t="str"/>
-      <x:c r="F26" s="178" t="str"/>
+      <x:c r="D26" s="225" t="str"/>
+      <x:c r="E26" s="225" t="str"/>
+      <x:c r="F26" s="226" t="str"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="174" t="str">
+      <x:c r="A27" s="223" t="str">
         <x:v>Wealthfront</x:v>
       </x:c>
-      <x:c r="B27" s="175" t="str">
+      <x:c r="B27" s="129" t="str">
         <x:v>Savings transfer</x:v>
       </x:c>
-      <x:c r="C27" s="175" t="str">
+      <x:c r="C27" s="129" t="str">
         <x:v>Transfer / verify</x:v>
       </x:c>
-      <x:c r="D27" s="177" t="str"/>
-      <x:c r="E27" s="177" t="str"/>
-      <x:c r="F27" s="178" t="str"/>
+      <x:c r="D27" s="225" t="str"/>
+      <x:c r="E27" s="225" t="str"/>
+      <x:c r="F27" s="226" t="str"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="174" t="str">
+      <x:c r="A28" s="223" t="str">
         <x:v>PayPal</x:v>
       </x:c>
-      <x:c r="B28" s="175" t="str">
+      <x:c r="B28" s="129" t="str">
         <x:v>Cruise / PayPal</x:v>
       </x:c>
-      <x:c r="C28" s="175" t="str">
+      <x:c r="C28" s="129" t="str">
         <x:v>Transfer / verify</x:v>
       </x:c>
-      <x:c r="D28" s="177" t="str"/>
-      <x:c r="E28" s="177" t="str"/>
-      <x:c r="F28" s="178" t="str"/>
+      <x:c r="D28" s="225" t="str"/>
+      <x:c r="E28" s="225" t="str"/>
+      <x:c r="F28" s="226" t="str"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="174" t="str">
+      <x:c r="A29" s="223" t="str">
         <x:v>Chase Payment</x:v>
       </x:c>
-      <x:c r="B29" s="175" t="str">
+      <x:c r="B29" s="129" t="str">
         <x:v>Credit-card payment</x:v>
       </x:c>
-      <x:c r="C29" s="175" t="str">
+      <x:c r="C29" s="129" t="str">
         <x:v>Exclude</x:v>
       </x:c>
-      <x:c r="D29" s="177" t="str"/>
-      <x:c r="E29" s="177" t="str"/>
-      <x:c r="F29" s="178" t="str"/>
+      <x:c r="D29" s="225" t="str"/>
+      <x:c r="E29" s="225" t="str"/>
+      <x:c r="F29" s="226" t="str"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="174" t="str">
+      <x:c r="A30" s="223" t="str">
         <x:v>Discover Payment</x:v>
       </x:c>
-      <x:c r="B30" s="175" t="str">
+      <x:c r="B30" s="129" t="str">
         <x:v>Credit-card payment</x:v>
       </x:c>
-      <x:c r="C30" s="175" t="str">
+      <x:c r="C30" s="129" t="str">
         <x:v>Exclude</x:v>
       </x:c>
-      <x:c r="D30" s="177" t="str"/>
-      <x:c r="E30" s="177" t="str"/>
-      <x:c r="F30" s="178" t="str"/>
+      <x:c r="D30" s="225" t="str"/>
+      <x:c r="E30" s="225" t="str"/>
+      <x:c r="F30" s="226" t="str"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="179" t="str">
+      <x:c r="A31" s="227" t="str">
         <x:v>Capital One Payment</x:v>
       </x:c>
-      <x:c r="B31" s="180" t="str">
+      <x:c r="B31" s="228" t="str">
         <x:v>Credit-card payment</x:v>
       </x:c>
-      <x:c r="C31" s="180" t="str">
+      <x:c r="C31" s="228" t="str">
         <x:v>Exclude</x:v>
       </x:c>
-      <x:c r="D31" s="181" t="str"/>
-      <x:c r="E31" s="181" t="str"/>
-      <x:c r="F31" s="182" t="str"/>
+      <x:c r="D31" s="229" t="str"/>
+      <x:c r="E31" s="229" t="str"/>
+      <x:c r="F31" s="230" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -4133,419 +4289,420 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="192" t="str">
+      <x:c r="A1" s="240" t="str">
         <x:v>Tuesday Review — Live Sep 9</x:v>
       </x:c>
-      <x:c r="B1" s="192"/>
-      <x:c r="C1" s="192"/>
-      <x:c r="D1" s="192"/>
-      <x:c r="E1" s="192"/>
-      <x:c r="F1" s="192"/>
-      <x:c r="G1" s="192"/>
+      <x:c r="B1" s="240"/>
+      <x:c r="C1" s="240"/>
+      <x:c r="D1" s="240"/>
+      <x:c r="E1" s="240"/>
+      <x:c r="F1" s="240"/>
+      <x:c r="G1" s="240"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="130" t="str">
+      <x:c r="A2" s="172" t="str">
         <x:v>Use this live checklist after Start is verified. Planned amounts come from the Sep. 9 account snapshots and funding rules. Done means no further action is needed from you; a bank transaction may still be pending settlement. Scheduled means a transfer is expected but not yet confirmed.</x:v>
       </x:c>
-      <x:c r="B2" s="130"/>
-      <x:c r="C2" s="130"/>
-      <x:c r="D2" s="130"/>
-      <x:c r="E2" s="130"/>
-      <x:c r="F2" s="130"/>
-      <x:c r="G2" s="130"/>
+      <x:c r="B2" s="172"/>
+      <x:c r="C2" s="172"/>
+      <x:c r="D2" s="172"/>
+      <x:c r="E2" s="172"/>
+      <x:c r="F2" s="172"/>
+      <x:c r="G2" s="172"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="131"/>
-      <x:c r="B3" s="131"/>
-      <x:c r="C3" s="131"/>
-      <x:c r="D3" s="131"/>
-      <x:c r="E3" s="131"/>
-      <x:c r="F3" s="131"/>
-      <x:c r="G3" s="131"/>
+      <x:c r="A3" s="173"/>
+      <x:c r="B3" s="173"/>
+      <x:c r="C3" s="173"/>
+      <x:c r="D3" s="173"/>
+      <x:c r="E3" s="173"/>
+      <x:c r="F3" s="173"/>
+      <x:c r="G3" s="173"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="132" t="str">
+      <x:c r="A4" s="174" t="str">
         <x:v>Sep 9 payment and funding plan</x:v>
       </x:c>
-      <x:c r="B4" s="132"/>
-      <x:c r="C4" s="132"/>
-      <x:c r="D4" s="132"/>
-      <x:c r="E4" s="132"/>
-      <x:c r="F4" s="132"/>
-      <x:c r="G4" s="132"/>
+      <x:c r="B4" s="174"/>
+      <x:c r="C4" s="174"/>
+      <x:c r="D4" s="174"/>
+      <x:c r="E4" s="174"/>
+      <x:c r="F4" s="174"/>
+      <x:c r="G4" s="174"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="145" t="str">
+      <x:c r="A5" s="184" t="str">
         <x:v>Source sets verified</x:v>
       </x:c>
-      <x:c r="B5" s="146" t="str">
+      <x:c r="B5" s="185" t="str">
         <x:v>Review period</x:v>
       </x:c>
-      <x:c r="C5" s="146" t="str">
+      <x:c r="C5" s="185" t="str">
         <x:v>Actions completed</x:v>
       </x:c>
-      <x:c r="D5" s="146" t="str">
+      <x:c r="D5" s="185" t="str">
         <x:v>Live plan</x:v>
       </x:c>
-      <x:c r="E5" s="146"/>
-      <x:c r="F5" s="146"/>
-      <x:c r="G5" s="147"/>
+      <x:c r="E5" s="185"/>
+      <x:c r="F5" s="185"/>
+      <x:c r="G5" s="186"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="221" t="str">
+      <x:c r="A6" s="269" t="str">
         <x:f>COUNTIF('1. Start'!E6:E13,"Verified")&amp;" of "&amp;(COUNTA('1. Start'!F6:F14)-COUNTIF('1. Start'!E6:E14,"Not due"))&amp;" source sets verified"</x:f>
         <x:v>8 of 8 source sets verified</x:v>
       </x:c>
-      <x:c r="B6" s="221" t="str">
+      <x:c r="B6" s="269" t="str">
         <x:v>Sep 1–Sep 7 purchases</x:v>
       </x:c>
-      <x:c r="C6" s="221" t="str">
+      <x:c r="C6" s="269" t="str">
         <x:f>COUNTIF(F9:F19,"✓ Done")&amp;" / "&amp;COUNTA(B9:B19)&amp;" actions completed"</x:f>
         <x:v>1 / 11 actions completed</x:v>
       </x:c>
-      <x:c r="D6" s="221" t="str">
+      <x:c r="D6" s="269" t="str">
         <x:v>Use now</x:v>
       </x:c>
-      <x:c r="E6" s="221"/>
-      <x:c r="F6" s="221"/>
-      <x:c r="G6" s="221"/>
+      <x:c r="E6" s="269"/>
+      <x:c r="F6" s="269"/>
+      <x:c r="G6" s="269"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="131"/>
-      <x:c r="B7" s="131"/>
-      <x:c r="C7" s="131"/>
-      <x:c r="D7" s="131"/>
-      <x:c r="E7" s="131"/>
-      <x:c r="F7" s="131"/>
-      <x:c r="G7" s="131"/>
+      <x:c r="A7" s="173"/>
+      <x:c r="B7" s="173"/>
+      <x:c r="C7" s="173"/>
+      <x:c r="D7" s="173"/>
+      <x:c r="E7" s="173"/>
+      <x:c r="F7" s="173"/>
+      <x:c r="G7" s="173"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="145" t="str">
+      <x:c r="A8" s="184" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="B8" s="146" t="str">
+      <x:c r="B8" s="185" t="str">
         <x:v>Payment or transfer</x:v>
       </x:c>
-      <x:c r="C8" s="146" t="str">
+      <x:c r="C8" s="185" t="str">
         <x:v>Basis</x:v>
       </x:c>
-      <x:c r="D8" s="146" t="str">
+      <x:c r="D8" s="185" t="str">
         <x:v>Planned amount</x:v>
       </x:c>
-      <x:c r="E8" s="146" t="str">
+      <x:c r="E8" s="185" t="str">
         <x:v>Completed amount</x:v>
       </x:c>
-      <x:c r="F8" s="146" t="str">
+      <x:c r="F8" s="185" t="str">
         <x:v>Done?</x:v>
       </x:c>
-      <x:c r="G8" s="147" t="str">
+      <x:c r="G8" s="186" t="str">
         <x:v>Confirmation note</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="25" customHeight="1">
-      <x:c r="A9" s="131" t="str">
+      <x:c r="A9" s="173" t="str">
         <x:v>Card payment</x:v>
       </x:c>
-      <x:c r="B9" s="131" t="str">
+      <x:c r="B9" s="173" t="str">
         <x:v>Chase Sapphire</x:v>
       </x:c>
-      <x:c r="C9" s="131" t="str">
+      <x:c r="C9" s="173" t="str">
         <x:v>Current Sep. 9 balance</x:v>
       </x:c>
-      <x:c r="D9" s="200" t="n">
+      <x:c r="D9" s="248" t="n">
         <x:f>'Support - Debt Detail'!B5</x:f>
         <x:v>266.96</x:v>
       </x:c>
-      <x:c r="E9" s="148"/>
-      <x:c r="F9" s="149" t="str">
+      <x:c r="E9" s="187"/>
+      <x:c r="F9" s="188" t="str">
         <x:v>Not done</x:v>
       </x:c>
-      <x:c r="G9" s="131" t="str">
+      <x:c r="G9" s="173" t="str">
         <x:v>Pay the current balance if maintaining the weekly payoff routine</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="25" customHeight="1">
-      <x:c r="A10" s="131" t="str">
+      <x:c r="A10" s="173" t="str">
         <x:v>Card payment</x:v>
       </x:c>
-      <x:c r="B10" s="131" t="str">
+      <x:c r="B10" s="173" t="str">
         <x:v>Citi card</x:v>
       </x:c>
-      <x:c r="C10" s="131" t="str">
+      <x:c r="C10" s="173" t="str">
         <x:v>Current Sep. 9 balance</x:v>
       </x:c>
-      <x:c r="D10" s="200" t="n">
+      <x:c r="D10" s="248" t="n">
         <x:f>'Support - Debt Detail'!B6</x:f>
         <x:v>132.09</x:v>
       </x:c>
-      <x:c r="E10" s="148"/>
-      <x:c r="F10" s="149" t="str">
+      <x:c r="E10" s="187"/>
+      <x:c r="F10" s="188" t="str">
         <x:v>Not done</x:v>
       </x:c>
-      <x:c r="G10" s="131" t="str">
+      <x:c r="G10" s="173" t="str">
         <x:v>Pay the current balance if maintaining the weekly payoff routine</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="25" customHeight="1">
-      <x:c r="A11" s="131" t="str">
+      <x:c r="A11" s="173" t="str">
         <x:v>Card payment</x:v>
       </x:c>
-      <x:c r="B11" s="131" t="str">
+      <x:c r="B11" s="173" t="str">
         <x:v>Prime Visa</x:v>
       </x:c>
-      <x:c r="C11" s="131" t="str">
+      <x:c r="C11" s="173" t="str">
         <x:v>No balance due</x:v>
       </x:c>
-      <x:c r="D11" s="200" t="n">
+      <x:c r="D11" s="248" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E11" s="148"/>
-      <x:c r="F11" s="149" t="str">
+      <x:c r="E11" s="187"/>
+      <x:c r="F11" s="188" t="str">
         <x:v>Not due</x:v>
       </x:c>
-      <x:c r="G11" s="131" t="str">
+      <x:c r="G11" s="173" t="str">
         <x:v>No payment needed</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="25" customHeight="1">
-      <x:c r="A12" s="131" t="str">
+      <x:c r="A12" s="173" t="str">
         <x:v>Debt payment</x:v>
       </x:c>
-      <x:c r="B12" s="131" t="str">
+      <x:c r="B12" s="173" t="str">
         <x:v>PayPal promotional payoff</x:v>
       </x:c>
-      <x:c r="C12" s="131" t="str">
+      <x:c r="C12" s="173" t="str">
         <x:v>Stage 1 payoff target</x:v>
       </x:c>
-      <x:c r="D12" s="200" t="n">
+      <x:c r="D12" s="248" t="n">
         <x:f>'Support - Promo Detail'!F12</x:f>
         <x:v>148.616</x:v>
       </x:c>
-      <x:c r="E12" s="148"/>
-      <x:c r="F12" s="149" t="str">
+      <x:c r="E12" s="187"/>
+      <x:c r="F12" s="188" t="str">
         <x:v>Not done</x:v>
       </x:c>
-      <x:c r="G12" s="131" t="str">
+      <x:c r="G12" s="173" t="str">
         <x:v>Five weekly payments remain before Oct. 10</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="25" customHeight="1">
-      <x:c r="A13" s="131" t="str">
+      <x:c r="A13" s="173" t="str">
         <x:v>Transfer</x:v>
       </x:c>
-      <x:c r="B13" s="131" t="str">
+      <x:c r="B13" s="173" t="str">
         <x:v>Rent fund — October</x:v>
       </x:c>
-      <x:c r="C13" s="131" t="str">
-        <x:v>First of four weekly deposits</x:v>
-      </x:c>
-      <x:c r="D13" s="200" t="n">
-        <x:f>'Support - Budget Inputs'!E12</x:f>
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="E13" s="148"/>
-      <x:c r="F13" s="149" t="str">
+      <x:c r="C13" s="173" t="str">
+        <x:v>Wells capacity after required actions; capped at normal plan</x:v>
+      </x:c>
+      <x:c r="D13" s="248" t="n">
+        <x:f>MIN('5. Savings &amp; Debt'!$B$26,MAX(0,$E$22-SUM($D$9:$D$12,$D$14,$D$16:$D$18)-$E$23))</x:f>
+        <x:v>178.49169230769235</x:v>
+      </x:c>
+      <x:c r="E13" s="187"/>
+      <x:c r="F13" s="188" t="str">
         <x:v>Not done</x:v>
       </x:c>
-      <x:c r="G13" s="131" t="str">
-        <x:v>Move to Wealthfront rent reserve</x:v>
+      <x:c r="G13" s="173" t="str">
+        <x:v>Move only this calculated amount to rent reserve; it records today’s actual funding</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="25" customHeight="1">
-      <x:c r="A14" s="131" t="str">
+      <x:c r="A14" s="173" t="str">
         <x:v>Transfer</x:v>
       </x:c>
-      <x:c r="B14" s="131" t="str">
+      <x:c r="B14" s="173" t="str">
         <x:v>Car fund / CUTX</x:v>
       </x:c>
-      <x:c r="C14" s="131" t="str">
+      <x:c r="C14" s="173" t="str">
         <x:v>Weekly reserve toward Sep. 27 due date</x:v>
       </x:c>
-      <x:c r="D14" s="200" t="n">
+      <x:c r="D14" s="248" t="n">
         <x:f>'Support - Budget Inputs'!E13</x:f>
         <x:v>172.26230769230767</x:v>
       </x:c>
-      <x:c r="E14" s="148"/>
-      <x:c r="F14" s="149" t="str">
+      <x:c r="E14" s="187"/>
+      <x:c r="F14" s="188" t="str">
         <x:v>Not done</x:v>
       </x:c>
-      <x:c r="G14" s="131" t="str">
+      <x:c r="G14" s="173" t="str">
         <x:v>Move to CUTX reserve; do not pay the loan early</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="25" customHeight="1">
-      <x:c r="A15" s="131" t="str">
+      <x:c r="A15" s="173" t="str">
         <x:v>Automatic</x:v>
       </x:c>
-      <x:c r="B15" s="131" t="str">
+      <x:c r="B15" s="173" t="str">
         <x:v>Fidelity 401(k)</x:v>
       </x:c>
-      <x:c r="C15" s="131" t="str">
+      <x:c r="C15" s="173" t="str">
         <x:v>Pending; already in Wells available balance</x:v>
       </x:c>
-      <x:c r="D15" s="200" t="n">
+      <x:c r="D15" s="248" t="n">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="E15" s="148"/>
-      <x:c r="F15" s="149" t="str">
+      <x:c r="E15" s="187"/>
+      <x:c r="F15" s="188" t="str">
         <x:v>✓ Done</x:v>
       </x:c>
-      <x:c r="G15" s="131" t="str">
+      <x:c r="G15" s="173" t="str">
         <x:v>Do not count again in cash required</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="25" customHeight="1">
-      <x:c r="A16" s="131" t="str">
+      <x:c r="A16" s="173" t="str">
         <x:v>Automatic</x:v>
       </x:c>
-      <x:c r="B16" s="131" t="str">
+      <x:c r="B16" s="173" t="str">
         <x:v>PayPal cruise savings</x:v>
       </x:c>
-      <x:c r="C16" s="131" t="str">
+      <x:c r="C16" s="173" t="str">
         <x:v>Flexible savings contribution</x:v>
       </x:c>
-      <x:c r="D16" s="200" t="n">
+      <x:c r="D16" s="248" t="n">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="E16" s="148"/>
-      <x:c r="F16" s="149" t="str">
+      <x:c r="E16" s="187"/>
+      <x:c r="F16" s="188" t="str">
         <x:v>Scheduled</x:v>
       </x:c>
-      <x:c r="G16" s="131" t="str">
+      <x:c r="G16" s="173" t="str">
         <x:v>Included in cash required; confirm after it posts</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="25" customHeight="1">
-      <x:c r="A17" s="131" t="str">
+      <x:c r="A17" s="173" t="str">
         <x:v>Automatic</x:v>
       </x:c>
-      <x:c r="B17" s="131" t="str">
+      <x:c r="B17" s="173" t="str">
         <x:v>PayPal tuition savings</x:v>
       </x:c>
-      <x:c r="C17" s="131" t="str">
+      <x:c r="C17" s="173" t="str">
         <x:v>Weekly scheduled transfer</x:v>
       </x:c>
-      <x:c r="D17" s="200" t="n">
+      <x:c r="D17" s="248" t="n">
         <x:v>193.36</x:v>
       </x:c>
-      <x:c r="E17" s="148"/>
-      <x:c r="F17" s="149" t="str">
+      <x:c r="E17" s="187"/>
+      <x:c r="F17" s="188" t="str">
         <x:v>Scheduled</x:v>
       </x:c>
-      <x:c r="G17" s="131" t="str">
+      <x:c r="G17" s="173" t="str">
         <x:v>Included in cash required; confirm after it posts</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="25" customHeight="1">
-      <x:c r="A18" s="131" t="str">
+      <x:c r="A18" s="173" t="str">
         <x:v>Automatic</x:v>
       </x:c>
-      <x:c r="B18" s="131" t="str">
+      <x:c r="B18" s="173" t="str">
         <x:v>PayPal future-expenses savings</x:v>
       </x:c>
-      <x:c r="C18" s="131" t="str">
+      <x:c r="C18" s="173" t="str">
         <x:v>Flexible savings contribution</x:v>
       </x:c>
-      <x:c r="D18" s="200" t="n">
+      <x:c r="D18" s="248" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="E18" s="148"/>
-      <x:c r="F18" s="149" t="str">
+      <x:c r="E18" s="187"/>
+      <x:c r="F18" s="188" t="str">
         <x:v>Scheduled</x:v>
       </x:c>
-      <x:c r="G18" s="131" t="str">
+      <x:c r="G18" s="173" t="str">
         <x:v>Included in cash required; confirm after it posts</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="25" customHeight="1">
-      <x:c r="A19" s="131" t="str">
+      <x:c r="A19" s="173" t="str">
         <x:v>Transfer</x:v>
       </x:c>
-      <x:c r="B19" s="131" t="str">
+      <x:c r="B19" s="173" t="str">
         <x:v>Wealthfront to Wells</x:v>
       </x:c>
-      <x:c r="C19" s="131" t="str">
+      <x:c r="C19" s="173" t="str">
         <x:v>Cover a remaining cash shortfall</x:v>
       </x:c>
-      <x:c r="D19" s="200" t="n">
+      <x:c r="D19" s="248" t="n">
         <x:f>MAX(0,E21+E23-E22)</x:f>
-        <x:v>121.50830769230765</x:v>
-      </x:c>
-      <x:c r="E19" s="148"/>
-      <x:c r="F19" s="149" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E19" s="187"/>
+      <x:c r="F19" s="188" t="str">
         <x:v>Not done</x:v>
       </x:c>
-      <x:c r="G19" s="131" t="str">
-        <x:v>Transfer this amount from Wealthfront so Wells retains $1 after all actions</x:v>
+      <x:c r="G19" s="173" t="str">
+        <x:f>IF(D19=0,"No transfer needed after net rent funding","Transfer this amount from Wealthfront so Wells retains $1 after all actions")</x:f>
+        <x:v>No transfer needed after net rent funding</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="222" t="str">
+      <x:c r="A20" s="270" t="str">
         <x:v>Planned subtotal (cash actions)</x:v>
       </x:c>
-      <x:c r="B20" s="222"/>
-      <x:c r="C20" s="222"/>
-      <x:c r="D20" s="223" t="n">
+      <x:c r="B20" s="270"/>
+      <x:c r="C20" s="270"/>
+      <x:c r="D20" s="271" t="n">
         <x:f>SUM(D9:D14,D16:D18)</x:f>
-        <x:v>1348.2883076923076</x:v>
-      </x:c>
-      <x:c r="E20" s="131"/>
-      <x:c r="F20" s="131"/>
-      <x:c r="G20" s="131"/>
+        <x:v>1226.78</x:v>
+      </x:c>
+      <x:c r="E20" s="173"/>
+      <x:c r="F20" s="173"/>
+      <x:c r="G20" s="173"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="224" t="str">
+      <x:c r="A21" s="272" t="str">
         <x:v>Cash required for payments and transfers</x:v>
       </x:c>
-      <x:c r="B21" s="224"/>
-      <x:c r="C21" s="224"/>
-      <x:c r="D21" s="224"/>
-      <x:c r="E21" s="225" t="n">
+      <x:c r="B21" s="272"/>
+      <x:c r="C21" s="272"/>
+      <x:c r="D21" s="272"/>
+      <x:c r="E21" s="273" t="n">
         <x:f>SUM(D9:D14,D16:D18)</x:f>
-        <x:v>1348.2883076923076</x:v>
-      </x:c>
-      <x:c r="F21" s="131"/>
-      <x:c r="G21" s="131"/>
+        <x:v>1226.78</x:v>
+      </x:c>
+      <x:c r="F21" s="173"/>
+      <x:c r="G21" s="173"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="224" t="str">
+      <x:c r="A22" s="272" t="str">
         <x:v>Wells available now after pending Fidelity</x:v>
       </x:c>
-      <x:c r="B22" s="224"/>
-      <x:c r="C22" s="224"/>
-      <x:c r="D22" s="224"/>
-      <x:c r="E22" s="226" t="n">
+      <x:c r="B22" s="272"/>
+      <x:c r="C22" s="272"/>
+      <x:c r="D22" s="272"/>
+      <x:c r="E22" s="274" t="n">
         <x:v>1227.78</x:v>
       </x:c>
-      <x:c r="F22" s="131"/>
-      <x:c r="G22" s="131"/>
+      <x:c r="F22" s="173"/>
+      <x:c r="G22" s="173"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="227" t="str">
+      <x:c r="A23" s="275" t="str">
         <x:v>Minimum Wells balance after all actions</x:v>
       </x:c>
-      <x:c r="B23" s="227"/>
-      <x:c r="C23" s="227"/>
-      <x:c r="D23" s="227"/>
-      <x:c r="E23" s="226" t="n">
+      <x:c r="B23" s="275"/>
+      <x:c r="C23" s="275"/>
+      <x:c r="D23" s="275"/>
+      <x:c r="E23" s="274" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F23" s="131"/>
-      <x:c r="G23" s="131"/>
+      <x:c r="F23" s="173"/>
+      <x:c r="G23" s="173"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="224" t="str">
+      <x:c r="A24" s="272" t="str">
         <x:v>Move from Wealthfront to Wells if needed</x:v>
       </x:c>
-      <x:c r="B24" s="224"/>
-      <x:c r="C24" s="224"/>
-      <x:c r="D24" s="224"/>
-      <x:c r="E24" s="228" t="n">
+      <x:c r="B24" s="272"/>
+      <x:c r="C24" s="272"/>
+      <x:c r="D24" s="272"/>
+      <x:c r="E24" s="276" t="n">
         <x:f>D19</x:f>
-        <x:v>121.50830769230765</x:v>
-      </x:c>
-      <x:c r="F24" s="131"/>
-      <x:c r="G24" s="131"/>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F24" s="173"/>
+      <x:c r="G24" s="173"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -4581,606 +4738,606 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="192" t="str">
+      <x:c r="A1" s="240" t="str">
         <x:v>This Week — Spending Analysis</x:v>
       </x:c>
-      <x:c r="B1" s="192"/>
-      <x:c r="C1" s="192"/>
-      <x:c r="D1" s="192"/>
-      <x:c r="E1" s="192"/>
-      <x:c r="F1" s="192"/>
-      <x:c r="G1" s="192"/>
+      <x:c r="B1" s="240"/>
+      <x:c r="C1" s="240"/>
+      <x:c r="D1" s="240"/>
+      <x:c r="E1" s="240"/>
+      <x:c r="F1" s="240"/>
+      <x:c r="G1" s="240"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="130" t="str">
+      <x:c r="A2" s="172" t="str">
         <x:v>Review new purchases against their weekly category limits here. Pending charges count so the week cannot look safer than it is. This is analysis, not the cash decision for today; payments and transfers do not belong here. Only source-verified ledger rows are counted.</x:v>
       </x:c>
-      <x:c r="B2" s="130"/>
-      <x:c r="C2" s="130"/>
-      <x:c r="D2" s="130"/>
-      <x:c r="E2" s="130"/>
-      <x:c r="F2" s="130"/>
-      <x:c r="G2" s="130"/>
+      <x:c r="B2" s="172"/>
+      <x:c r="C2" s="172"/>
+      <x:c r="D2" s="172"/>
+      <x:c r="E2" s="172"/>
+      <x:c r="F2" s="172"/>
+      <x:c r="G2" s="172"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="131" t="str">
+      <x:c r="A3" s="173" t="str">
         <x:v>Week beginning (Tuesday)</x:v>
       </x:c>
-      <x:c r="B3" s="193" t="n">
+      <x:c r="B3" s="241" t="n">
         <x:v>46266</x:v>
       </x:c>
-      <x:c r="C3" s="131"/>
-      <x:c r="D3" s="131" t="str">
+      <x:c r="C3" s="173"/>
+      <x:c r="D3" s="173" t="str">
         <x:v>Week ends</x:v>
       </x:c>
-      <x:c r="E3" s="194" t="n">
+      <x:c r="E3" s="242" t="n">
         <x:f>B3+6</x:f>
         <x:v>46272</x:v>
       </x:c>
-      <x:c r="F3" s="131" t="str">
+      <x:c r="F3" s="173" t="str">
         <x:v>Budget status</x:v>
       </x:c>
-      <x:c r="G3" s="131" t="str">
+      <x:c r="G3" s="173" t="str">
         <x:f>IF(COUNTIFS('Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"&lt;&gt;Verified")&gt;0,"Source check needed",IF(F23&lt;0,"Over plan","Within plan"))</x:f>
         <x:v>Within plan</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="131"/>
-      <x:c r="B4" s="131"/>
-      <x:c r="C4" s="131"/>
-      <x:c r="D4" s="131"/>
-      <x:c r="E4" s="131"/>
-      <x:c r="F4" s="131"/>
-      <x:c r="G4" s="131"/>
+      <x:c r="A4" s="173"/>
+      <x:c r="B4" s="173"/>
+      <x:c r="C4" s="173"/>
+      <x:c r="D4" s="173"/>
+      <x:c r="E4" s="173"/>
+      <x:c r="F4" s="173"/>
+      <x:c r="G4" s="173"/>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
-      <x:c r="A5" s="145" t="str">
+      <x:c r="A5" s="184" t="str">
         <x:v>Category</x:v>
       </x:c>
-      <x:c r="B5" s="146" t="str">
+      <x:c r="B5" s="185" t="str">
         <x:v>Weekly target</x:v>
       </x:c>
-      <x:c r="C5" s="146" t="str">
+      <x:c r="C5" s="185" t="str">
         <x:v>Posted actual</x:v>
       </x:c>
-      <x:c r="D5" s="146" t="str">
+      <x:c r="D5" s="185" t="str">
         <x:v>Pending</x:v>
       </x:c>
-      <x:c r="E5" s="146" t="str">
+      <x:c r="E5" s="185" t="str">
         <x:v>Committed</x:v>
       </x:c>
-      <x:c r="F5" s="146" t="str">
+      <x:c r="F5" s="185" t="str">
         <x:v>Remaining / over</x:v>
       </x:c>
-      <x:c r="G5" s="147" t="str">
+      <x:c r="G5" s="186" t="str">
         <x:v>Status</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="23" customHeight="1">
-      <x:c r="A6" s="131" t="str">
+      <x:c r="A6" s="173" t="str">
         <x:v>H-E-B / groceries</x:v>
       </x:c>
-      <x:c r="B6" s="150" t="n">
+      <x:c r="B6" s="189" t="n">
         <x:f>'Support - Budget Inputs'!E23</x:f>
         <x:v>79.77692307692307</x:v>
       </x:c>
-      <x:c r="C6" s="150" t="n">
+      <x:c r="C6" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A6,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>199.04</x:v>
       </x:c>
-      <x:c r="D6" s="150" t="n">
+      <x:c r="D6" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A6,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E6" s="150" t="n">
+      <x:c r="E6" s="189" t="n">
         <x:f>C6+D6</x:f>
         <x:v>199.04</x:v>
       </x:c>
-      <x:c r="F6" s="150" t="n">
+      <x:c r="F6" s="189" t="n">
         <x:f>IF(B6=0,"",B6-E6)</x:f>
         <x:v>-119.26307692307692</x:v>
       </x:c>
-      <x:c r="G6" s="131" t="str">
+      <x:c r="G6" s="173" t="str">
         <x:f>IF(B6=0,"No target set",IF(E6=0,"No activity",IF(F6&lt;0,"Over plan","On track")))</x:f>
         <x:v>Over plan</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="23" customHeight="1">
-      <x:c r="A7" s="131" t="str">
+      <x:c r="A7" s="173" t="str">
         <x:v>DoorDash</x:v>
       </x:c>
-      <x:c r="B7" s="150" t="n">
+      <x:c r="B7" s="189" t="n">
         <x:f>'Support - Budget Inputs'!E24</x:f>
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C7" s="150" t="n">
+      <x:c r="C7" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A7,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D7" s="150" t="n">
+      <x:c r="D7" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A7,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E7" s="150" t="n">
+      <x:c r="E7" s="189" t="n">
         <x:f>C7+D7</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F7" s="150" t="n">
+      <x:c r="F7" s="189" t="n">
         <x:f>IF(B7=0,"",B7-E7)</x:f>
         <x:v>25</x:v>
       </x:c>
-      <x:c r="G7" s="131" t="str">
+      <x:c r="G7" s="173" t="str">
         <x:f>IF(B7=0,"No target set",IF(E7=0,"No activity",IF(F7&lt;0,"Over plan","On track")))</x:f>
         <x:v>No activity</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="23" customHeight="1">
-      <x:c r="A8" s="131" t="str">
+      <x:c r="A8" s="173" t="str">
         <x:v>Starbucks</x:v>
       </x:c>
-      <x:c r="B8" s="150" t="n">
+      <x:c r="B8" s="189" t="n">
         <x:f>'Support - Budget Inputs'!E28</x:f>
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C8" s="150" t="n">
+      <x:c r="C8" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A8,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>42.55</x:v>
       </x:c>
-      <x:c r="D8" s="150" t="n">
+      <x:c r="D8" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A8,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E8" s="150" t="n">
+      <x:c r="E8" s="189" t="n">
         <x:f>C8+D8</x:f>
         <x:v>42.55</x:v>
       </x:c>
-      <x:c r="F8" s="150" t="n">
+      <x:c r="F8" s="189" t="n">
         <x:f>IF(B8=0,"",B8-E8)</x:f>
         <x:v>-12.549999999999997</x:v>
       </x:c>
-      <x:c r="G8" s="131" t="str">
+      <x:c r="G8" s="173" t="str">
         <x:f>IF(B8=0,"No target set",IF(E8=0,"No activity",IF(F8&lt;0,"Over plan","On track")))</x:f>
         <x:v>Over plan</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="23" customHeight="1">
-      <x:c r="A9" s="131" t="str">
+      <x:c r="A9" s="173" t="str">
         <x:v>Invincibles + other Apple</x:v>
       </x:c>
-      <x:c r="B9" s="150" t="n">
+      <x:c r="B9" s="189" t="n">
         <x:f>'Support - Budget Inputs'!E19</x:f>
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C9" s="150" t="n">
+      <x:c r="C9" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A9,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>54.56</x:v>
       </x:c>
-      <x:c r="D9" s="150" t="n">
+      <x:c r="D9" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A9,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E9" s="150" t="n">
+      <x:c r="E9" s="189" t="n">
         <x:f>C9+D9</x:f>
         <x:v>54.56</x:v>
       </x:c>
-      <x:c r="F9" s="150" t="n">
+      <x:c r="F9" s="189" t="n">
         <x:f>IF(B9=0,"",B9-E9)</x:f>
         <x:v>-4.560000000000002</x:v>
       </x:c>
-      <x:c r="G9" s="131" t="str">
+      <x:c r="G9" s="173" t="str">
         <x:f>IF(B9=0,"No target set",IF(E9=0,"No activity",IF(F9&lt;0,"Over plan","On track")))</x:f>
         <x:v>Over plan</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="23" customHeight="1">
-      <x:c r="A10" s="131" t="str">
+      <x:c r="A10" s="173" t="str">
         <x:v>Work snacks</x:v>
       </x:c>
-      <x:c r="B10" s="150" t="n">
+      <x:c r="B10" s="189" t="n">
         <x:f>'Support - Budget Inputs'!E29</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C10" s="150" t="n">
+      <x:c r="C10" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A10,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>13.989999999999998</x:v>
       </x:c>
-      <x:c r="D10" s="150" t="n">
+      <x:c r="D10" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A10,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E10" s="150" t="n">
+      <x:c r="E10" s="189" t="n">
         <x:f>C10+D10</x:f>
         <x:v>13.989999999999998</x:v>
       </x:c>
-      <x:c r="F10" s="150" t="n">
+      <x:c r="F10" s="189" t="n">
         <x:f>IF(B10=0,"",B10-E10)</x:f>
         <x:v>-3.9899999999999984</x:v>
       </x:c>
-      <x:c r="G10" s="131" t="str">
+      <x:c r="G10" s="173" t="str">
         <x:f>IF(B10=0,"No target set",IF(E10=0,"No activity",IF(F10&lt;0,"Over plan","On track")))</x:f>
         <x:v>Over plan</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="23" customHeight="1">
-      <x:c r="A11" s="131" t="str">
+      <x:c r="A11" s="173" t="str">
         <x:v>Shopping / personal care</x:v>
       </x:c>
-      <x:c r="B11" s="150" t="n">
+      <x:c r="B11" s="189" t="n">
         <x:f>'Support - Budget Inputs'!E30</x:f>
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C11" s="150" t="n">
+      <x:c r="C11" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A11,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>-71.46</x:v>
       </x:c>
-      <x:c r="D11" s="150" t="n">
+      <x:c r="D11" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A11,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E11" s="150" t="n">
+      <x:c r="E11" s="189" t="n">
         <x:f>C11+D11</x:f>
         <x:v>-71.46</x:v>
       </x:c>
-      <x:c r="F11" s="150" t="n">
+      <x:c r="F11" s="189" t="n">
         <x:f>IF(B11=0,"",B11-E11)</x:f>
         <x:v>121.46</x:v>
       </x:c>
-      <x:c r="G11" s="131" t="str">
+      <x:c r="G11" s="173" t="str">
         <x:f>IF(B11=0,"No target set",IF(E11=0,"No activity",IF(F11&lt;0,"Over plan","On track")))</x:f>
         <x:v>On track</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="23" customHeight="1">
-      <x:c r="A12" s="131" t="str">
+      <x:c r="A12" s="173" t="str">
         <x:v>Vapes</x:v>
       </x:c>
-      <x:c r="B12" s="150" t="n">
+      <x:c r="B12" s="189" t="n">
         <x:f>'Support - Budget Inputs'!E31</x:f>
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C12" s="150" t="n">
+      <x:c r="C12" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A12,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D12" s="150" t="n">
+      <x:c r="D12" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A12,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E12" s="150" t="n">
+      <x:c r="E12" s="189" t="n">
         <x:f>C12+D12</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F12" s="150" t="n">
+      <x:c r="F12" s="189" t="n">
         <x:f>IF(B12=0,"",B12-E12)</x:f>
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G12" s="131" t="str">
+      <x:c r="G12" s="173" t="str">
         <x:f>IF(B12=0,"No target set",IF(E12=0,"No activity",IF(F12&lt;0,"Over plan","On track")))</x:f>
         <x:v>No activity</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="23" customHeight="1">
-      <x:c r="A13" s="131" t="str">
+      <x:c r="A13" s="173" t="str">
         <x:v>Fuel</x:v>
       </x:c>
-      <x:c r="B13" s="150" t="n">
+      <x:c r="B13" s="189" t="n">
         <x:f>'Support - Budget Inputs'!E25</x:f>
         <x:v>80.76923076923077</x:v>
       </x:c>
-      <x:c r="C13" s="150" t="n">
+      <x:c r="C13" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A13,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>159.14000000000001</x:v>
       </x:c>
-      <x:c r="D13" s="150" t="n">
+      <x:c r="D13" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A13,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E13" s="150" t="n">
+      <x:c r="E13" s="189" t="n">
         <x:f>C13+D13</x:f>
         <x:v>159.14000000000001</x:v>
       </x:c>
-      <x:c r="F13" s="150" t="n">
+      <x:c r="F13" s="189" t="n">
         <x:f>IF(B13=0,"",B13-E13)</x:f>
         <x:v>-78.37076923076924</x:v>
       </x:c>
-      <x:c r="G13" s="131" t="str">
+      <x:c r="G13" s="173" t="str">
         <x:f>IF(B13=0,"No target set",IF(E13=0,"No activity",IF(F13&lt;0,"Over plan","On track")))</x:f>
         <x:v>Over plan</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="23" customHeight="1">
-      <x:c r="A14" s="131" t="str">
+      <x:c r="A14" s="173" t="str">
         <x:v>Pet costs</x:v>
       </x:c>
-      <x:c r="B14" s="150" t="n">
+      <x:c r="B14" s="189" t="n">
         <x:f>'Support - Budget Inputs'!E26</x:f>
         <x:v>47.48076923076923</x:v>
       </x:c>
-      <x:c r="C14" s="150" t="n">
+      <x:c r="C14" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A14,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D14" s="150" t="n">
+      <x:c r="D14" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A14,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E14" s="150" t="n">
+      <x:c r="E14" s="189" t="n">
         <x:f>C14+D14</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F14" s="150" t="n">
+      <x:c r="F14" s="189" t="n">
         <x:f>IF(B14=0,"",B14-E14)</x:f>
         <x:v>47.48076923076923</x:v>
       </x:c>
-      <x:c r="G14" s="131" t="str">
+      <x:c r="G14" s="173" t="str">
         <x:f>IF(B14=0,"No target set",IF(E14=0,"No activity",IF(F14&lt;0,"Over plan","On track")))</x:f>
         <x:v>No activity</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
-      <x:c r="A15" s="131" t="str">
+      <x:c r="A15" s="173" t="str">
         <x:v>Electricity</x:v>
       </x:c>
-      <x:c r="B15" s="150" t="n">
+      <x:c r="B15" s="189" t="n">
         <x:f>'Support - Budget Inputs'!E14</x:f>
         <x:v>15.166153846153845</x:v>
       </x:c>
-      <x:c r="C15" s="150" t="n">
+      <x:c r="C15" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A15,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D15" s="150" t="n">
+      <x:c r="D15" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A15,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" s="150" t="n">
+      <x:c r="E15" s="189" t="n">
         <x:f>C15+D15</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F15" s="150" t="n">
+      <x:c r="F15" s="189" t="n">
         <x:f>IF(B15=0,"",B15-E15)</x:f>
         <x:v>15.166153846153845</x:v>
       </x:c>
-      <x:c r="G15" s="131" t="str">
+      <x:c r="G15" s="173" t="str">
         <x:f>IF(B15=0,"No target set",IF(E15=0,"No activity",IF(F15&lt;0,"Over plan","On track")))</x:f>
         <x:v>No activity</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
-      <x:c r="A16" s="131" t="str">
+      <x:c r="A16" s="173" t="str">
         <x:v>Spectrum internet</x:v>
       </x:c>
-      <x:c r="B16" s="150" t="n">
+      <x:c r="B16" s="189" t="n">
         <x:f>'Support - Budget Inputs'!E16</x:f>
         <x:v>25.51846153846154</x:v>
       </x:c>
-      <x:c r="C16" s="150" t="n">
+      <x:c r="C16" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A16,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D16" s="150" t="n">
+      <x:c r="D16" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A16,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E16" s="150" t="n">
+      <x:c r="E16" s="189" t="n">
         <x:f>C16+D16</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F16" s="150" t="n">
+      <x:c r="F16" s="189" t="n">
         <x:f>IF(B16=0,"",B16-E16)</x:f>
         <x:v>25.51846153846154</x:v>
       </x:c>
-      <x:c r="G16" s="131" t="str">
+      <x:c r="G16" s="173" t="str">
         <x:f>IF(B16=0,"No target set",IF(E16=0,"No activity",IF(F16&lt;0,"Over plan","On track")))</x:f>
         <x:v>No activity</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="23" customHeight="1">
-      <x:c r="A17" s="131" t="str">
+      <x:c r="A17" s="173" t="str">
         <x:v>Phone + Visible</x:v>
       </x:c>
-      <x:c r="B17" s="150" t="n">
+      <x:c r="B17" s="189" t="n">
         <x:f>SUM('Support - Budget Inputs'!E15,'Support - Budget Inputs'!E17)</x:f>
         <x:v>21.692307692307693</x:v>
       </x:c>
-      <x:c r="C17" s="150" t="n">
+      <x:c r="C17" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A17,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D17" s="150" t="n">
+      <x:c r="D17" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A17,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E17" s="150" t="n">
+      <x:c r="E17" s="189" t="n">
         <x:f>C17+D17</x:f>
         <x:v>35</x:v>
       </x:c>
-      <x:c r="F17" s="150" t="n">
+      <x:c r="F17" s="189" t="n">
         <x:f>IF(B17=0,"",B17-E17)</x:f>
         <x:v>-13.307692307692307</x:v>
       </x:c>
-      <x:c r="G17" s="131" t="str">
+      <x:c r="G17" s="173" t="str">
         <x:f>IF(B17=0,"No target set",IF(E17=0,"No activity",IF(F17&lt;0,"Over plan","On track")))</x:f>
         <x:v>Over plan</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="23" customHeight="1">
-      <x:c r="A18" s="131" t="str">
+      <x:c r="A18" s="173" t="str">
         <x:v>Subscriptions</x:v>
       </x:c>
-      <x:c r="B18" s="150" t="n">
+      <x:c r="B18" s="189" t="n">
         <x:f>'Support - Budget Inputs'!E18</x:f>
         <x:v>11.256923076923076</x:v>
       </x:c>
-      <x:c r="C18" s="150" t="n">
+      <x:c r="C18" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A18,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>11.99</x:v>
       </x:c>
-      <x:c r="D18" s="150" t="n">
+      <x:c r="D18" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A18,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E18" s="150" t="n">
+      <x:c r="E18" s="189" t="n">
         <x:f>C18+D18</x:f>
         <x:v>11.99</x:v>
       </x:c>
-      <x:c r="F18" s="150" t="n">
+      <x:c r="F18" s="189" t="n">
         <x:f>IF(B18=0,"",B18-E18)</x:f>
         <x:v>-0.7330769230769238</x:v>
       </x:c>
-      <x:c r="G18" s="131" t="str">
+      <x:c r="G18" s="173" t="str">
         <x:f>IF(B18=0,"No target set",IF(E18=0,"No activity",IF(F18&lt;0,"Over plan","On track")))</x:f>
         <x:v>Over plan</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="23" customHeight="1">
-      <x:c r="A19" s="131" t="str">
+      <x:c r="A19" s="173" t="str">
         <x:v>Automotive</x:v>
       </x:c>
-      <x:c r="B19" s="150" t="n">
+      <x:c r="B19" s="189" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C19" s="150" t="n">
+      <x:c r="C19" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A19,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D19" s="150" t="n">
+      <x:c r="D19" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A19,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>2.5</x:v>
       </x:c>
-      <x:c r="E19" s="150" t="n">
+      <x:c r="E19" s="189" t="n">
         <x:f>C19+D19</x:f>
         <x:v>5.5</x:v>
       </x:c>
-      <x:c r="F19" s="150" t="str">
+      <x:c r="F19" s="189" t="str">
         <x:f>IF(B19=0,"",B19-E19)</x:f>
       </x:c>
-      <x:c r="G19" s="131" t="str">
+      <x:c r="G19" s="173" t="str">
         <x:f>IF(B19=0,"No target set",IF(E19=0,"No activity",IF(F19&lt;0,"Over plan","On track")))</x:f>
         <x:v>No target set</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="23" customHeight="1">
-      <x:c r="A20" s="131" t="str">
+      <x:c r="A20" s="173" t="str">
         <x:v>Travel / cruise</x:v>
       </x:c>
-      <x:c r="B20" s="150" t="n">
+      <x:c r="B20" s="189" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C20" s="150" t="n">
+      <x:c r="C20" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A20,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0.18</x:v>
       </x:c>
-      <x:c r="D20" s="150" t="n">
+      <x:c r="D20" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A20,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E20" s="150" t="n">
+      <x:c r="E20" s="189" t="n">
         <x:f>C20+D20</x:f>
         <x:v>0.18</x:v>
       </x:c>
-      <x:c r="F20" s="150" t="str">
+      <x:c r="F20" s="189" t="str">
         <x:f>IF(B20=0,"",B20-E20)</x:f>
       </x:c>
-      <x:c r="G20" s="131" t="str">
+      <x:c r="G20" s="173" t="str">
         <x:f>IF(B20=0,"No target set",IF(E20=0,"No activity",IF(F20&lt;0,"Over plan","On track")))</x:f>
         <x:v>No target set</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="23" customHeight="1">
-      <x:c r="A21" s="131" t="str">
+      <x:c r="A21" s="173" t="str">
         <x:v>Education / school supplies</x:v>
       </x:c>
-      <x:c r="B21" s="150" t="n">
+      <x:c r="B21" s="189" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C21" s="150" t="n">
+      <x:c r="C21" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A21,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D21" s="150" t="n">
+      <x:c r="D21" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$F$5:$F$304,A21,'Support - Ledger'!$H$5:$H$304,$B$3,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E21" s="150" t="n">
+      <x:c r="E21" s="189" t="n">
         <x:f>C21+D21</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F21" s="150" t="str">
+      <x:c r="F21" s="189" t="str">
         <x:f>IF(B21=0,"",B21-E21)</x:f>
       </x:c>
-      <x:c r="G21" s="131" t="str">
+      <x:c r="G21" s="173" t="str">
         <x:f>IF(B21=0,"No target set",IF(E21=0,"No activity",IF(F21&lt;0,"Over plan","On track")))</x:f>
         <x:v>No target set</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="131"/>
-      <x:c r="B22" s="150"/>
-      <x:c r="C22" s="150"/>
-      <x:c r="D22" s="150"/>
-      <x:c r="E22" s="150"/>
-      <x:c r="F22" s="150"/>
-      <x:c r="G22" s="131"/>
+      <x:c r="A22" s="173"/>
+      <x:c r="B22" s="189"/>
+      <x:c r="C22" s="189"/>
+      <x:c r="D22" s="189"/>
+      <x:c r="E22" s="189"/>
+      <x:c r="F22" s="189"/>
+      <x:c r="G22" s="173"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="195" t="str">
+      <x:c r="A23" s="243" t="str">
         <x:v>All tracked spending</x:v>
       </x:c>
-      <x:c r="B23" s="196" t="n">
+      <x:c r="B23" s="244" t="n">
         <x:f>SUM(B6:B21)</x:f>
         <x:v>476.6607692307693</x:v>
       </x:c>
-      <x:c r="C23" s="196" t="n">
+      <x:c r="C23" s="244" t="n">
         <x:f>SUM(C6:C21)</x:f>
         <x:v>447.99000000000007</x:v>
       </x:c>
-      <x:c r="D23" s="196" t="n">
+      <x:c r="D23" s="244" t="n">
         <x:f>SUM(D6:D21)</x:f>
         <x:v>2.5</x:v>
       </x:c>
-      <x:c r="E23" s="196" t="n">
+      <x:c r="E23" s="244" t="n">
         <x:f>SUM(E6:E21)</x:f>
         <x:v>450.49000000000007</x:v>
       </x:c>
-      <x:c r="F23" s="196" t="n">
+      <x:c r="F23" s="244" t="n">
         <x:f>B23-E23</x:f>
         <x:v>26.170769230769224</x:v>
       </x:c>
-      <x:c r="G23" s="195"/>
+      <x:c r="G23" s="243"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="131"/>
-      <x:c r="B24" s="131"/>
-      <x:c r="C24" s="131"/>
-      <x:c r="D24" s="131"/>
-      <x:c r="E24" s="131"/>
-      <x:c r="F24" s="131"/>
-      <x:c r="G24" s="131"/>
+      <x:c r="A24" s="173"/>
+      <x:c r="B24" s="173"/>
+      <x:c r="C24" s="173"/>
+      <x:c r="D24" s="173"/>
+      <x:c r="E24" s="173"/>
+      <x:c r="F24" s="173"/>
+      <x:c r="G24" s="173"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="197" t="str">
+      <x:c r="A25" s="245" t="str">
         <x:v>Transfer confirmation belongs in History after the following Tuesday’s account screens arrive. Keeping it out of this sheet makes this page one thing only: this Tuesday–Monday’s new-purchase limits.</x:v>
       </x:c>
-      <x:c r="B25" s="197"/>
-      <x:c r="C25" s="197"/>
-      <x:c r="D25" s="197"/>
-      <x:c r="E25" s="197"/>
-      <x:c r="F25" s="197"/>
-      <x:c r="G25" s="197"/>
+      <x:c r="B25" s="245"/>
+      <x:c r="C25" s="245"/>
+      <x:c r="D25" s="245"/>
+      <x:c r="E25" s="245"/>
+      <x:c r="F25" s="245"/>
+      <x:c r="G25" s="245"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="197"/>
-      <x:c r="B26" s="197"/>
-      <x:c r="C26" s="197"/>
-      <x:c r="D26" s="197"/>
-      <x:c r="E26" s="197"/>
-      <x:c r="F26" s="197"/>
-      <x:c r="G26" s="197"/>
+      <x:c r="A26" s="245"/>
+      <x:c r="B26" s="245"/>
+      <x:c r="C26" s="245"/>
+      <x:c r="D26" s="245"/>
+      <x:c r="E26" s="245"/>
+      <x:c r="F26" s="245"/>
+      <x:c r="G26" s="245"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5189,12 +5346,12 @@
     <x:mergeCell ref="A25:G26"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="F6:F23">
-    <x:cfRule type="cellIs" dxfId="11" priority="1" operator="lessThan">
+    <x:cfRule type="cellIs" dxfId="15" priority="1" operator="lessThan">
       <x:formula>0</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="G6:G21">
-    <x:cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="Over plan"/>
+    <x:cfRule type="containsText" dxfId="16" priority="2" operator="containsText" text="Over plan"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -5258,17 +5415,17 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="36" t="str">
-        <x:v>Rent reserve to Wealthfront</x:v>
+        <x:v>Rent reserve — maximum</x:v>
       </x:c>
       <x:c r="B5" s="42" t="n">
         <x:f>'Support - Budget Inputs'!E12</x:f>
         <x:v>300</x:v>
       </x:c>
       <x:c r="C5" s="36" t="str">
-        <x:v>Fund the four Tuesdays after rent is paid</x:v>
+        <x:v>Use only verified Wells capacity after required actions</x:v>
       </x:c>
       <x:c r="D5" s="36" t="str">
-        <x:v>Rent-payment Tuesday: $0; then four $300 deposits</x:v>
+        <x:v>Actual contribution is recorded in Savings &amp; Debt; no catch-up is assumed</x:v>
       </x:c>
       <x:c r="E5" s="36"/>
       <x:c r="F5" s="36"/>
@@ -5597,28 +5754,28 @@
       <x:c r="F25" s="36"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="167" t="str">
+      <x:c r="A26" s="216" t="str">
         <x:v>Personal-safe income — included in household total</x:v>
       </x:c>
-      <x:c r="B26" s="168" t="n">
+      <x:c r="B26" s="217" t="n">
         <x:f>'Support - Budget Inputs'!D7</x:f>
         <x:v>60</x:v>
       </x:c>
-      <x:c r="C26" s="167"/>
-      <x:c r="D26" s="167"/>
+      <x:c r="C26" s="216"/>
+      <x:c r="D26" s="216"/>
       <x:c r="E26" s="36"/>
       <x:c r="F26" s="36"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="169" t="str">
+      <x:c r="A27" s="218" t="str">
         <x:v>Banking income available for Wells plan</x:v>
       </x:c>
-      <x:c r="B27" s="170" t="n">
+      <x:c r="B27" s="219" t="n">
         <x:f>B25-B26</x:f>
         <x:v>1343.37</x:v>
       </x:c>
-      <x:c r="C27" s="169"/>
-      <x:c r="D27" s="169"/>
+      <x:c r="C27" s="218"/>
+      <x:c r="D27" s="218"/>
       <x:c r="E27" s="36"/>
       <x:c r="F27" s="36"/>
     </x:row>
@@ -5654,52 +5811,52 @@
       <x:c r="F30" s="37"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="164" t="str">
+      <x:c r="A31" s="213" t="str">
         <x:v>1. Fund the plan</x:v>
       </x:c>
-      <x:c r="B31" s="158" t="str">
+      <x:c r="B31" s="117" t="str">
         <x:v>The allocation is the weekly funding guide; it is not a list of immediate bills due.</x:v>
       </x:c>
-      <x:c r="C31" s="158"/>
-      <x:c r="D31" s="158"/>
-      <x:c r="E31" s="158"/>
-      <x:c r="F31" s="159"/>
+      <x:c r="C31" s="117"/>
+      <x:c r="D31" s="117"/>
+      <x:c r="E31" s="117"/>
+      <x:c r="F31" s="118"/>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="165" t="str">
+      <x:c r="A32" s="214" t="str">
         <x:v>2. Spend within limits</x:v>
       </x:c>
-      <x:c r="B32" s="160" t="str">
+      <x:c r="B32" s="120" t="str">
         <x:v>Use This Week for actual purchases and pending charges.</x:v>
       </x:c>
-      <x:c r="C32" s="160"/>
-      <x:c r="D32" s="160"/>
-      <x:c r="E32" s="160"/>
-      <x:c r="F32" s="161"/>
+      <x:c r="C32" s="120"/>
+      <x:c r="D32" s="120"/>
+      <x:c r="E32" s="120"/>
+      <x:c r="F32" s="121"/>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="165" t="str">
+      <x:c r="A33" s="214" t="str">
         <x:v>3. Execute payments</x:v>
       </x:c>
-      <x:c r="B33" s="160" t="str">
+      <x:c r="B33" s="120" t="str">
         <x:v>Create or replace Tuesday Review when the next payment plan is due.</x:v>
       </x:c>
-      <x:c r="C33" s="160"/>
-      <x:c r="D33" s="160"/>
-      <x:c r="E33" s="160"/>
-      <x:c r="F33" s="161"/>
+      <x:c r="C33" s="120"/>
+      <x:c r="D33" s="120"/>
+      <x:c r="E33" s="120"/>
+      <x:c r="F33" s="121"/>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="166" t="str">
+      <x:c r="A34" s="215" t="str">
         <x:v>4. Preserve history</x:v>
       </x:c>
-      <x:c r="B34" s="162" t="str">
+      <x:c r="B34" s="123" t="str">
         <x:v>History receives the verified weekly result; do not overwrite prior weeks.</x:v>
       </x:c>
-      <x:c r="C34" s="162"/>
-      <x:c r="D34" s="162"/>
-      <x:c r="E34" s="162"/>
-      <x:c r="F34" s="163"/>
+      <x:c r="C34" s="123"/>
+      <x:c r="D34" s="123"/>
+      <x:c r="E34" s="123"/>
+      <x:c r="F34" s="124"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="36"/>
@@ -5776,7 +5933,7 @@
     <x:mergeCell ref="B34:F34"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="B28:B28">
-    <x:cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
+    <x:cfRule type="cellIs" dxfId="9" priority="1" operator="lessThan">
       <x:formula>0</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
@@ -5788,284 +5945,620 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="31" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="21" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="31" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="21" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="29" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="129" t="str">
+      <x:c r="A1" s="171" t="str">
         <x:v>Savings &amp; Debt</x:v>
       </x:c>
-      <x:c r="B1" s="129"/>
-      <x:c r="C1" s="129"/>
-      <x:c r="D1" s="129"/>
+      <x:c r="B1" s="171"/>
+      <x:c r="C1" s="171"/>
+      <x:c r="D1" s="171"/>
+      <x:c r="E1" s="171"/>
+      <x:c r="F1" s="171"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="130" t="str">
-        <x:v>Read this as three questions: Is savings protected? Is next month’s rent funded? Are the priority debts on track?</x:v>
-      </x:c>
-      <x:c r="B2" s="130"/>
-      <x:c r="C2" s="130"/>
-      <x:c r="D2" s="130"/>
+      <x:c r="A2" s="172" t="str">
+        <x:v>Read this as three questions: Is savings protected? Is next month’s rent funded from real cash? Are the priority debts on track?</x:v>
+      </x:c>
+      <x:c r="B2" s="172"/>
+      <x:c r="C2" s="172"/>
+      <x:c r="D2" s="172"/>
+      <x:c r="E2" s="172"/>
+      <x:c r="F2" s="172"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="131"/>
-      <x:c r="B3" s="131"/>
-      <x:c r="C3" s="131"/>
-      <x:c r="D3" s="131"/>
+      <x:c r="A3" s="173"/>
+      <x:c r="B3" s="173"/>
+      <x:c r="C3" s="173"/>
+      <x:c r="D3" s="173"/>
+      <x:c r="E3" s="173"/>
+      <x:c r="F3" s="173"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="132" t="str">
+      <x:c r="A4" s="174" t="str">
         <x:v>Savings health</x:v>
       </x:c>
-      <x:c r="B4" s="132"/>
-      <x:c r="C4" s="132"/>
-      <x:c r="D4" s="132"/>
+      <x:c r="B4" s="174"/>
+      <x:c r="C4" s="174"/>
+      <x:c r="D4" s="174"/>
+      <x:c r="E4" s="174"/>
+      <x:c r="F4" s="174"/>
     </x:row>
     <x:row r="5" ht="29" customHeight="1">
-      <x:c r="A5" s="133" t="str">
+      <x:c r="A5" s="175" t="str">
         <x:v>Wealthfront available now</x:v>
       </x:c>
-      <x:c r="B5" s="134" t="n">
+      <x:c r="B5" s="167" t="n">
         <x:f>'Support - Account Snapshots'!F6</x:f>
         <x:v>11847.64</x:v>
       </x:c>
-      <x:c r="C5" s="135" t="str">
-        <x:v>Next rent reserve</x:v>
-      </x:c>
-      <x:c r="D5" s="136" t="n">
-        <x:f>'Support - Budget Inputs'!E12*4</x:f>
-        <x:v>1200</x:v>
-      </x:c>
+      <x:c r="C5" s="176" t="str">
+        <x:v>Next rent due</x:v>
+      </x:c>
+      <x:c r="D5" s="177" t="n">
+        <x:f>B34</x:f>
+        <x:v>46296</x:v>
+      </x:c>
+      <x:c r="E5" s="173"/>
+      <x:c r="F5" s="173"/>
     </x:row>
     <x:row r="6" ht="29" customHeight="1">
-      <x:c r="A6" s="137" t="str">
+      <x:c r="A6" s="178" t="str">
         <x:v>Personal safe cash</x:v>
       </x:c>
-      <x:c r="B6" s="138" t="n">
+      <x:c r="B6" s="169" t="n">
         <x:f>'Support - Account Snapshots'!F7</x:f>
         <x:v>60</x:v>
       </x:c>
-      <x:c r="C6" s="137" t="str">
-        <x:v>Rent cushion after 4 deposits</x:v>
-      </x:c>
-      <x:c r="D6" s="138" t="n">
-        <x:f>D5-'2. Tuesday Review'!D14</x:f>
-        <x:v>1027.7376923076922</x:v>
-      </x:c>
+      <x:c r="C6" s="178" t="str">
+        <x:v>Rent due estimate</x:v>
+      </x:c>
+      <x:c r="D6" s="169" t="n">
+        <x:f>B35</x:f>
+        <x:v>1169.46</x:v>
+      </x:c>
+      <x:c r="E6" s="173"/>
+      <x:c r="F6" s="173"/>
     </x:row>
     <x:row r="7" ht="29" customHeight="1">
-      <x:c r="A7" s="139" t="str">
+      <x:c r="A7" s="179" t="str">
         <x:v>Confirmed liquid savings</x:v>
       </x:c>
-      <x:c r="B7" s="140" t="n">
+      <x:c r="B7" s="180" t="n">
         <x:f>SUM(B5:B6)</x:f>
         <x:v>11907.64</x:v>
       </x:c>
-      <x:c r="C7" s="141" t="str">
-        <x:v>Actual Wealthfront transfer — Sep 2</x:v>
-      </x:c>
-      <x:c r="D7" s="142" t="n">
-        <x:f>'2. Tuesday Review'!E23</x:f>
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="C7" s="178" t="str">
+        <x:v>Tagged rent reserve</x:v>
+      </x:c>
+      <x:c r="D7" s="169" t="n">
+        <x:f>B39</x:f>
+        <x:v>178.49169230769235</x:v>
+      </x:c>
+      <x:c r="E7" s="173"/>
+      <x:c r="F7" s="173"/>
     </x:row>
     <x:row r="8" ht="29" customHeight="1">
-      <x:c r="A8" s="141" t="str">
+      <x:c r="A8" s="181" t="str">
         <x:v>13-week core-needs benchmark</x:v>
       </x:c>
-      <x:c r="B8" s="142" t="n">
+      <x:c r="B8" s="182" t="n">
         <x:f>SUM('Support - Budget Inputs'!E12:E17,'Support - Budget Inputs'!E20:E23,'Support - Budget Inputs'!E25:E26)*13</x:f>
         <x:v>11985.970700000002</x:v>
       </x:c>
-      <x:c r="C8" s="137" t="str">
-        <x:v>Target Wells remainder — Sep 2</x:v>
-      </x:c>
-      <x:c r="D8" s="138" t="n">
-        <x:f>'2. Tuesday Review'!E24</x:f>
-        <x:v>121.50830769230765</x:v>
-      </x:c>
+      <x:c r="C8" s="178" t="str">
+        <x:v>Emergency draw if no more funding</x:v>
+      </x:c>
+      <x:c r="D8" s="169" t="n">
+        <x:f>E36</x:f>
+        <x:v>1021.5083076923077</x:v>
+      </x:c>
+      <x:c r="E8" s="173"/>
+      <x:c r="F8" s="173"/>
     </x:row>
     <x:row r="9" ht="29" customHeight="1">
-      <x:c r="A9" s="143" t="str">
+      <x:c r="A9" s="183" t="str">
         <x:v>Gap to core-needs benchmark</x:v>
       </x:c>
-      <x:c r="B9" s="144" t="n">
+      <x:c r="B9" s="170" t="n">
         <x:f>B7-B8</x:f>
         <x:v>-78.33070000000225</x:v>
       </x:c>
-      <x:c r="C9" s="143" t="str">
-        <x:v>PayPal promo target this week</x:v>
-      </x:c>
-      <x:c r="D9" s="144" t="n">
+      <x:c r="C9" s="183" t="str">
+        <x:v>Confirmed funding vs. monthly plan</x:v>
+      </x:c>
+      <x:c r="D9" s="170" t="n">
+        <x:f>E34</x:f>
+        <x:v>-1021.5083076923077</x:v>
+      </x:c>
+      <x:c r="E9" s="173"/>
+      <x:c r="F9" s="173"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="173"/>
+      <x:c r="B10" s="173"/>
+      <x:c r="C10" s="173"/>
+      <x:c r="D10" s="173"/>
+      <x:c r="E10" s="173"/>
+      <x:c r="F10" s="173"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="174" t="str">
+        <x:v>Automatic savings — weekly transfers</x:v>
+      </x:c>
+      <x:c r="B11" s="174"/>
+      <x:c r="C11" s="174"/>
+      <x:c r="D11" s="174"/>
+      <x:c r="E11" s="173"/>
+      <x:c r="F11" s="173"/>
+    </x:row>
+    <x:row r="12" ht="25" customHeight="1">
+      <x:c r="A12" s="184" t="str">
+        <x:v>Item</x:v>
+      </x:c>
+      <x:c r="B12" s="185" t="str">
+        <x:v>Weekly amount</x:v>
+      </x:c>
+      <x:c r="C12" s="185" t="str">
+        <x:v>Weeks confirmed</x:v>
+      </x:c>
+      <x:c r="D12" s="186" t="str">
+        <x:v>Saved since tracker began</x:v>
+      </x:c>
+      <x:c r="E12" s="173"/>
+      <x:c r="F12" s="173"/>
+    </x:row>
+    <x:row r="13" ht="25" customHeight="1">
+      <x:c r="A13" s="173" t="str">
+        <x:v>Fidelity 401(k)</x:v>
+      </x:c>
+      <x:c r="B13" s="187" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C13" s="188" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D13" s="189" t="n">
+        <x:f>B13*C13</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E13" s="173"/>
+      <x:c r="F13" s="173"/>
+    </x:row>
+    <x:row r="14" ht="25" customHeight="1">
+      <x:c r="A14" s="173" t="str">
+        <x:v>PayPal cruise fund</x:v>
+      </x:c>
+      <x:c r="B14" s="187" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C14" s="188" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D14" s="189" t="n">
+        <x:f>B14*C14</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E14" s="173"/>
+      <x:c r="F14" s="173"/>
+    </x:row>
+    <x:row r="15" ht="25" customHeight="1">
+      <x:c r="A15" s="173" t="str">
+        <x:v>Del Mar tuition savings</x:v>
+      </x:c>
+      <x:c r="B15" s="187" t="n">
+        <x:v>193.36</x:v>
+      </x:c>
+      <x:c r="C15" s="188" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" s="189" t="n">
+        <x:f>B15*C15</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E15" s="173"/>
+      <x:c r="F15" s="173"/>
+    </x:row>
+    <x:row r="16" ht="25" customHeight="1">
+      <x:c r="A16" s="173" t="str">
+        <x:v>Future-expenses fund</x:v>
+      </x:c>
+      <x:c r="B16" s="187" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C16" s="188" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D16" s="189" t="n">
+        <x:f>B16*C16</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E16" s="173"/>
+      <x:c r="F16" s="173"/>
+    </x:row>
+    <x:row r="17" ht="25" customHeight="1">
+      <x:c r="A17" s="190" t="str">
+        <x:v>Total automatic savings</x:v>
+      </x:c>
+      <x:c r="B17" s="191" t="n">
+        <x:f>SUM(B13:B16)</x:f>
+        <x:v>403.36</x:v>
+      </x:c>
+      <x:c r="C17" s="191"/>
+      <x:c r="D17" s="191" t="n">
+        <x:f>SUM(D13:D16)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E17" s="173"/>
+      <x:c r="F17" s="173"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="173"/>
+      <x:c r="B18" s="173"/>
+      <x:c r="C18" s="173"/>
+      <x:c r="D18" s="173"/>
+      <x:c r="E18" s="173"/>
+      <x:c r="F18" s="173"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="174" t="str">
+        <x:v>Priority debt payoff</x:v>
+      </x:c>
+      <x:c r="B19" s="174"/>
+      <x:c r="C19" s="174"/>
+      <x:c r="D19" s="174"/>
+      <x:c r="E19" s="173"/>
+      <x:c r="F19" s="173"/>
+    </x:row>
+    <x:row r="20" ht="27" customHeight="1">
+      <x:c r="A20" s="175" t="str">
+        <x:v>Active PayPal promo balance</x:v>
+      </x:c>
+      <x:c r="B20" s="167" t="n">
+        <x:f>'Support - Promo Detail'!C11</x:f>
+        <x:v>1318.93</x:v>
+      </x:c>
+      <x:c r="C20" s="192" t="str">
+        <x:v>The weekly payoff is an expense paid from Wells, not savings. The detailed promo schedule is on Support - Promo Detail.</x:v>
+      </x:c>
+      <x:c r="D20" s="192"/>
+      <x:c r="E20" s="173"/>
+      <x:c r="F20" s="173"/>
+    </x:row>
+    <x:row r="21" ht="27" customHeight="1">
+      <x:c r="A21" s="178" t="str">
+        <x:v>Weekly payoff target</x:v>
+      </x:c>
+      <x:c r="B21" s="169" t="n">
         <x:f>'Support - Promo Detail'!F12</x:f>
         <x:v>148.616</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="131"/>
-      <x:c r="B10" s="131"/>
-      <x:c r="C10" s="131"/>
-      <x:c r="D10" s="131"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="132" t="str">
-        <x:v>Automatic savings — weekly transfers</x:v>
-      </x:c>
-      <x:c r="B11" s="132"/>
-      <x:c r="C11" s="132"/>
-      <x:c r="D11" s="132"/>
-    </x:row>
-    <x:row r="12" ht="25" customHeight="1">
-      <x:c r="A12" s="145" t="str">
-        <x:v>Item</x:v>
-      </x:c>
-      <x:c r="B12" s="146" t="str">
-        <x:v>Weekly amount</x:v>
-      </x:c>
-      <x:c r="C12" s="146" t="str">
-        <x:v>Weeks confirmed</x:v>
-      </x:c>
-      <x:c r="D12" s="147" t="str">
-        <x:v>Saved since tracker began</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="25" customHeight="1">
-      <x:c r="A13" s="131" t="str">
-        <x:v>Fidelity 401(k)</x:v>
-      </x:c>
-      <x:c r="B13" s="148" t="n">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C13" s="149" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D13" s="150" t="n">
-        <x:f>B13*C13</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="25" customHeight="1">
-      <x:c r="A14" s="131" t="str">
-        <x:v>PayPal cruise fund</x:v>
-      </x:c>
-      <x:c r="B14" s="148" t="n">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C14" s="149" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D14" s="150" t="n">
-        <x:f>B14*C14</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="25" customHeight="1">
-      <x:c r="A15" s="131" t="str">
-        <x:v>Del Mar tuition savings</x:v>
-      </x:c>
-      <x:c r="B15" s="148" t="n">
-        <x:v>193.36</x:v>
-      </x:c>
-      <x:c r="C15" s="149" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D15" s="150" t="n">
-        <x:f>B15*C15</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="25" customHeight="1">
-      <x:c r="A16" s="131" t="str">
-        <x:v>Future-expenses fund</x:v>
-      </x:c>
-      <x:c r="B16" s="148" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C16" s="149" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D16" s="150" t="n">
-        <x:f>B16*C16</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="25" customHeight="1">
-      <x:c r="A17" s="151" t="str">
-        <x:v>Total automatic savings</x:v>
-      </x:c>
-      <x:c r="B17" s="152" t="n">
-        <x:f>SUM(B13:B16)</x:f>
-        <x:v>403.36</x:v>
-      </x:c>
-      <x:c r="C17" s="152"/>
-      <x:c r="D17" s="152" t="n">
-        <x:f>SUM(D13:D16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="131"/>
-      <x:c r="B18" s="131"/>
-      <x:c r="C18" s="131"/>
-      <x:c r="D18" s="131"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="132" t="str">
-        <x:v>Priority debt payoff</x:v>
-      </x:c>
-      <x:c r="B19" s="132"/>
-      <x:c r="C19" s="132"/>
-      <x:c r="D19" s="132"/>
-    </x:row>
-    <x:row r="20" ht="27" customHeight="1">
-      <x:c r="A20" s="133" t="str">
-        <x:v>Active PayPal promo balance</x:v>
-      </x:c>
-      <x:c r="B20" s="134" t="n">
-        <x:f>'Support - Promo Detail'!C11</x:f>
-        <x:v>1318.93</x:v>
-      </x:c>
-      <x:c r="C20" s="153" t="str">
-        <x:v>The weekly payoff is an expense paid from Wells, not savings. The detailed promo schedule is on Support - Promo Detail.</x:v>
-      </x:c>
-      <x:c r="D20" s="153"/>
-    </x:row>
-    <x:row r="21" ht="27" customHeight="1">
-      <x:c r="A21" s="137" t="str">
-        <x:v>Weekly payoff target</x:v>
-      </x:c>
-      <x:c r="B21" s="138" t="n">
-        <x:f>'Support - Promo Detail'!F12</x:f>
-        <x:v>148.616</x:v>
-      </x:c>
-      <x:c r="C21" s="153"/>
-      <x:c r="D21" s="153"/>
+      <x:c r="C21" s="192"/>
+      <x:c r="D21" s="192"/>
+      <x:c r="E21" s="173"/>
+      <x:c r="F21" s="173"/>
     </x:row>
     <x:row r="22" ht="27" customHeight="1">
-      <x:c r="A22" s="143" t="str">
+      <x:c r="A22" s="183" t="str">
         <x:v>First promo deadline</x:v>
       </x:c>
-      <x:c r="B22" s="154" t="n">
+      <x:c r="B22" s="193" t="n">
         <x:f>'Support - Promo Detail'!B6</x:f>
         <x:v>46305</x:v>
       </x:c>
-      <x:c r="C22" s="153"/>
-      <x:c r="D22" s="153"/>
+      <x:c r="C22" s="192"/>
+      <x:c r="D22" s="192"/>
+      <x:c r="E22" s="173"/>
+      <x:c r="F22" s="173"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="173"/>
+      <x:c r="B23" s="173"/>
+      <x:c r="C23" s="173"/>
+      <x:c r="D23" s="173"/>
+      <x:c r="E23" s="173"/>
+      <x:c r="F23" s="173"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="174" t="str">
+        <x:v>Rent reserve — October</x:v>
+      </x:c>
+      <x:c r="B24" s="174"/>
+      <x:c r="C24" s="174"/>
+      <x:c r="D24" s="174"/>
+      <x:c r="E24" s="174"/>
+      <x:c r="F24" s="174"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="184" t="str">
+        <x:v>Tuesday</x:v>
+      </x:c>
+      <x:c r="B25" s="185" t="str">
+        <x:v>Normal cap</x:v>
+      </x:c>
+      <x:c r="C25" s="185" t="str">
+        <x:v>Actual funded</x:v>
+      </x:c>
+      <x:c r="D25" s="185" t="str">
+        <x:v>Variance</x:v>
+      </x:c>
+      <x:c r="E25" s="185" t="str">
+        <x:v>Funding source</x:v>
+      </x:c>
+      <x:c r="F25" s="186" t="str">
+        <x:v>Note</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="28" customHeight="1">
+      <x:c r="A26" s="194" t="n">
+        <x:v>46274</x:v>
+      </x:c>
+      <x:c r="B26" s="195" t="n">
+        <x:f>'Support - Budget Inputs'!$E$12</x:f>
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="C26" s="196" t="n">
+        <x:f>'2. Tuesday Review'!D13</x:f>
+        <x:v>178.49169230769235</x:v>
+      </x:c>
+      <x:c r="D26" s="195" t="n">
+        <x:f>C26-B26</x:f>
+        <x:v>-121.50830769230765</x:v>
+      </x:c>
+      <x:c r="E26" s="197" t="str">
+        <x:v>Wells cash capacity</x:v>
+      </x:c>
+      <x:c r="F26" s="198" t="str">
+        <x:v>Calculated from verified Tuesday plan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="28" customHeight="1">
+      <x:c r="A27" s="199" t="n">
+        <x:v>46281</x:v>
+      </x:c>
+      <x:c r="B27" s="200" t="n">
+        <x:f>'Support - Budget Inputs'!$E$12</x:f>
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="C27" s="201"/>
+      <x:c r="D27" s="200" t="n">
+        <x:f>C27-B27</x:f>
+        <x:v>-300</x:v>
+      </x:c>
+      <x:c r="E27" s="202" t="str">
+        <x:v>Enter after review</x:v>
+      </x:c>
+      <x:c r="F27" s="203" t="str">
+        <x:v>No catch-up assumed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="28" customHeight="1">
+      <x:c r="A28" s="199" t="n">
+        <x:v>46288</x:v>
+      </x:c>
+      <x:c r="B28" s="200" t="n">
+        <x:f>'Support - Budget Inputs'!$E$12</x:f>
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="C28" s="201"/>
+      <x:c r="D28" s="200" t="n">
+        <x:f>C28-B28</x:f>
+        <x:v>-300</x:v>
+      </x:c>
+      <x:c r="E28" s="202" t="str">
+        <x:v>Enter after review</x:v>
+      </x:c>
+      <x:c r="F28" s="203" t="str">
+        <x:v>No catch-up assumed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="28" customHeight="1">
+      <x:c r="A29" s="204" t="n">
+        <x:v>46295</x:v>
+      </x:c>
+      <x:c r="B29" s="205" t="n">
+        <x:f>'Support - Budget Inputs'!$E$12</x:f>
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="C29" s="206"/>
+      <x:c r="D29" s="205" t="n">
+        <x:f>C29-B29</x:f>
+        <x:v>-300</x:v>
+      </x:c>
+      <x:c r="E29" s="207" t="str">
+        <x:v>Enter after review</x:v>
+      </x:c>
+      <x:c r="F29" s="208" t="str">
+        <x:v>No catch-up assumed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="28" customHeight="1">
+      <x:c r="A30" s="190" t="str">
+        <x:v>Total before October rent</x:v>
+      </x:c>
+      <x:c r="B30" s="191" t="n">
+        <x:f>SUM(B26:B29)</x:f>
+        <x:v>1200</x:v>
+      </x:c>
+      <x:c r="C30" s="191" t="n">
+        <x:f>SUM(C26:C29)</x:f>
+        <x:v>178.49169230769235</x:v>
+      </x:c>
+      <x:c r="D30" s="191" t="n">
+        <x:f>C30-B30</x:f>
+        <x:v>-1021.5083076923077</x:v>
+      </x:c>
+      <x:c r="E30" s="190"/>
+      <x:c r="F30" s="190"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="173"/>
+      <x:c r="B31" s="173"/>
+      <x:c r="C31" s="173"/>
+      <x:c r="D31" s="173"/>
+      <x:c r="E31" s="173"/>
+      <x:c r="F31" s="173"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="174" t="str">
+        <x:v>Rent reserve forecast</x:v>
+      </x:c>
+      <x:c r="B32" s="174"/>
+      <x:c r="C32" s="174"/>
+      <x:c r="D32" s="174"/>
+      <x:c r="E32" s="174"/>
+      <x:c r="F32" s="174"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="173"/>
+      <x:c r="B33" s="173"/>
+      <x:c r="C33" s="173"/>
+      <x:c r="D33" s="173"/>
+      <x:c r="E33" s="173"/>
+      <x:c r="F33" s="173"/>
+    </x:row>
+    <x:row r="34" ht="28" customHeight="1">
+      <x:c r="A34" s="175" t="str">
+        <x:v>Next rent due</x:v>
+      </x:c>
+      <x:c r="B34" s="209" t="n">
+        <x:v>46296</x:v>
+      </x:c>
+      <x:c r="C34" s="173"/>
+      <x:c r="D34" s="175" t="str">
+        <x:v>Confirmed funding vs. monthly plan</x:v>
+      </x:c>
+      <x:c r="E34" s="167" t="n">
+        <x:f>D30</x:f>
+        <x:v>-1021.5083076923077</x:v>
+      </x:c>
+      <x:c r="F34" s="173"/>
+    </x:row>
+    <x:row r="35" ht="28" customHeight="1">
+      <x:c r="A35" s="178" t="str">
+        <x:v>Rent due estimate</x:v>
+      </x:c>
+      <x:c r="B35" s="168" t="n">
+        <x:v>1169.46</x:v>
+      </x:c>
+      <x:c r="C35" s="173"/>
+      <x:c r="D35" s="178" t="str">
+        <x:v>Remaining rent funding gap</x:v>
+      </x:c>
+      <x:c r="E35" s="169" t="n">
+        <x:f>MAX(0,$B$38-$B$39)</x:f>
+        <x:v>1021.5083076923077</x:v>
+      </x:c>
+      <x:c r="F35" s="173"/>
+    </x:row>
+    <x:row r="36" ht="28" customHeight="1">
+      <x:c r="A36" s="178" t="str">
+        <x:v>Opening tagged rent reserve</x:v>
+      </x:c>
+      <x:c r="B36" s="168" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C36" s="173"/>
+      <x:c r="D36" s="178" t="str">
+        <x:v>Emergency draw if no more funding</x:v>
+      </x:c>
+      <x:c r="E36" s="169" t="n">
+        <x:f>E35</x:f>
+        <x:v>1021.5083076923077</x:v>
+      </x:c>
+      <x:c r="F36" s="173"/>
+    </x:row>
+    <x:row r="37" ht="28" customHeight="1">
+      <x:c r="A37" s="178" t="str">
+        <x:v>Confirmed future rent funding</x:v>
+      </x:c>
+      <x:c r="B37" s="168" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C37" s="173"/>
+      <x:c r="D37" s="178" t="str">
+        <x:v>Cushion if rent paid today</x:v>
+      </x:c>
+      <x:c r="E37" s="169" t="n">
+        <x:f>MAX(0,$B$39-$B$35)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F37" s="173"/>
+    </x:row>
+    <x:row r="38" ht="28" customHeight="1">
+      <x:c r="A38" s="178" t="str">
+        <x:v>Target rent reserve</x:v>
+      </x:c>
+      <x:c r="B38" s="169" t="n">
+        <x:f>MAX(B35,B30)</x:f>
+        <x:v>1200</x:v>
+      </x:c>
+      <x:c r="C38" s="173"/>
+      <x:c r="D38" s="183" t="str">
+        <x:v>Next Tuesday rent cap</x:v>
+      </x:c>
+      <x:c r="E38" s="170" t="n">
+        <x:f>B27</x:f>
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="F38" s="173"/>
+    </x:row>
+    <x:row r="39" ht="28" customHeight="1">
+      <x:c r="A39" s="183" t="str">
+        <x:v>Tagged reserve before rent</x:v>
+      </x:c>
+      <x:c r="B39" s="170" t="n">
+        <x:f>B36+C30+B37</x:f>
+        <x:v>178.49169230769235</x:v>
+      </x:c>
+      <x:c r="C39" s="173"/>
+      <x:c r="D39" s="192" t="str">
+        <x:v>No catch-up is assumed. Enter future funding only after it is real or truly arranged.</x:v>
+      </x:c>
+      <x:c r="E39" s="192"/>
+      <x:c r="F39" s="192"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:D1"/>
-    <x:mergeCell ref="A2:D2"/>
-    <x:mergeCell ref="A4:D4"/>
+    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A2:F2"/>
+    <x:mergeCell ref="A4:F4"/>
     <x:mergeCell ref="A11:D11"/>
     <x:mergeCell ref="A19:D19"/>
     <x:mergeCell ref="C20:D22"/>
+    <x:mergeCell ref="A24:F24"/>
+    <x:mergeCell ref="A32:F32"/>
+    <x:mergeCell ref="D39:F39"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="B9:B9">
     <x:cfRule type="cellIs" dxfId="4" priority="1" operator="lessThan">
+      <x:formula>0</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="D8:D8">
+    <x:cfRule type="cellIs" dxfId="5" priority="2" operator="greaterThan">
+      <x:formula>0</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="D9:D9">
+    <x:cfRule type="cellIs" dxfId="6" priority="3" operator="lessThan">
+      <x:formula>0</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="D26:D30">
+    <x:cfRule type="cellIs" dxfId="7" priority="4" operator="lessThan">
+      <x:formula>0</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="E35:E36">
+    <x:cfRule type="cellIs" dxfId="8" priority="5" operator="greaterThan">
       <x:formula>0</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
@@ -6093,998 +6586,998 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="199" t="str">
+      <x:c r="A1" s="247" t="str">
         <x:v>History — Closed Weeks</x:v>
       </x:c>
-      <x:c r="B1" s="199"/>
-      <x:c r="C1" s="199"/>
-      <x:c r="D1" s="199"/>
-      <x:c r="E1" s="199"/>
-      <x:c r="F1" s="199"/>
-      <x:c r="G1" s="199"/>
-      <x:c r="H1" s="199"/>
-      <x:c r="I1" s="199"/>
-      <x:c r="J1" s="199"/>
-      <x:c r="K1" s="199"/>
-      <x:c r="L1" s="199"/>
-      <x:c r="M1" s="199"/>
+      <x:c r="B1" s="247"/>
+      <x:c r="C1" s="247"/>
+      <x:c r="D1" s="247"/>
+      <x:c r="E1" s="247"/>
+      <x:c r="F1" s="247"/>
+      <x:c r="G1" s="247"/>
+      <x:c r="H1" s="247"/>
+      <x:c r="I1" s="247"/>
+      <x:c r="J1" s="247"/>
+      <x:c r="K1" s="247"/>
+      <x:c r="L1" s="247"/>
+      <x:c r="M1" s="247"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="130" t="str">
+      <x:c r="A2" s="172" t="str">
         <x:v>This is the historical record. A settlement Tuesday pays the prior Tuesday–Monday’s purchases; its Wells balance is therefore never treated as money available for the new purchase week. At the following Tuesday review, mark the execution check and reconcile transfers/screenshots.</x:v>
       </x:c>
-      <x:c r="B2" s="130"/>
-      <x:c r="C2" s="130"/>
-      <x:c r="D2" s="130"/>
-      <x:c r="E2" s="130"/>
-      <x:c r="F2" s="130"/>
-      <x:c r="G2" s="130"/>
-      <x:c r="H2" s="130"/>
-      <x:c r="I2" s="130"/>
-      <x:c r="J2" s="130"/>
-      <x:c r="K2" s="130"/>
-      <x:c r="L2" s="130"/>
-      <x:c r="M2" s="130"/>
+      <x:c r="B2" s="172"/>
+      <x:c r="C2" s="172"/>
+      <x:c r="D2" s="172"/>
+      <x:c r="E2" s="172"/>
+      <x:c r="F2" s="172"/>
+      <x:c r="G2" s="172"/>
+      <x:c r="H2" s="172"/>
+      <x:c r="I2" s="172"/>
+      <x:c r="J2" s="172"/>
+      <x:c r="K2" s="172"/>
+      <x:c r="L2" s="172"/>
+      <x:c r="M2" s="172"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="131"/>
-      <x:c r="B3" s="131"/>
-      <x:c r="C3" s="131"/>
-      <x:c r="D3" s="131"/>
-      <x:c r="E3" s="131"/>
-      <x:c r="F3" s="131"/>
-      <x:c r="G3" s="131"/>
-      <x:c r="H3" s="131"/>
-      <x:c r="I3" s="131"/>
-      <x:c r="J3" s="131"/>
-      <x:c r="K3" s="131"/>
-      <x:c r="L3" s="131"/>
-      <x:c r="M3" s="131"/>
+      <x:c r="A3" s="173"/>
+      <x:c r="B3" s="173"/>
+      <x:c r="C3" s="173"/>
+      <x:c r="D3" s="173"/>
+      <x:c r="E3" s="173"/>
+      <x:c r="F3" s="173"/>
+      <x:c r="G3" s="173"/>
+      <x:c r="H3" s="173"/>
+      <x:c r="I3" s="173"/>
+      <x:c r="J3" s="173"/>
+      <x:c r="K3" s="173"/>
+      <x:c r="L3" s="173"/>
+      <x:c r="M3" s="173"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="145" t="str">
+      <x:c r="A4" s="184" t="str">
         <x:v>Review Tuesday</x:v>
       </x:c>
-      <x:c r="B4" s="146" t="str">
+      <x:c r="B4" s="185" t="str">
         <x:v>Purchase week start</x:v>
       </x:c>
-      <x:c r="C4" s="146" t="str">
+      <x:c r="C4" s="185" t="str">
         <x:v>Purchase week end</x:v>
       </x:c>
-      <x:c r="D4" s="146" t="str">
+      <x:c r="D4" s="185" t="str">
         <x:v>Wells available at review</x:v>
       </x:c>
-      <x:c r="E4" s="146" t="str">
+      <x:c r="E4" s="185" t="str">
         <x:v>Wealthfront rent transfer</x:v>
       </x:c>
-      <x:c r="F4" s="146" t="str">
+      <x:c r="F4" s="185" t="str">
         <x:v>Total Wells plan</x:v>
       </x:c>
-      <x:c r="G4" s="146" t="str">
+      <x:c r="G4" s="185" t="str">
         <x:v>Execution check</x:v>
       </x:c>
-      <x:c r="H4" s="146" t="str">
+      <x:c r="H4" s="185" t="str">
         <x:v>Purchase budget</x:v>
       </x:c>
-      <x:c r="I4" s="146" t="str">
+      <x:c r="I4" s="185" t="str">
         <x:v>Posted spend</x:v>
       </x:c>
-      <x:c r="J4" s="146" t="str">
+      <x:c r="J4" s="185" t="str">
         <x:v>Pending spend</x:v>
       </x:c>
-      <x:c r="K4" s="146" t="str">
+      <x:c r="K4" s="185" t="str">
         <x:v>Committed spend</x:v>
       </x:c>
-      <x:c r="L4" s="146" t="str">
+      <x:c r="L4" s="185" t="str">
         <x:v>Remaining / over</x:v>
       </x:c>
-      <x:c r="M4" s="147" t="str">
+      <x:c r="M4" s="186" t="str">
         <x:v>Notes</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
-      <x:c r="A5" s="194" t="n">
+      <x:c r="A5" s="242" t="n">
         <x:v>46266</x:v>
       </x:c>
-      <x:c r="B5" s="194" t="n">
+      <x:c r="B5" s="242" t="n">
         <x:f>A5-7</x:f>
         <x:v>46259</x:v>
       </x:c>
-      <x:c r="C5" s="194" t="n">
+      <x:c r="C5" s="242" t="n">
         <x:f>A5-1</x:f>
         <x:v>46265</x:v>
       </x:c>
-      <x:c r="D5" s="150" t="n">
+      <x:c r="D5" s="189" t="n">
         <x:v>1583.08</x:v>
       </x:c>
-      <x:c r="E5" s="150" t="n">
+      <x:c r="E5" s="189" t="n">
         <x:v>631.34</x:v>
       </x:c>
-      <x:c r="F5" s="150" t="n">
+      <x:c r="F5" s="189" t="n">
         <x:v>2194.42</x:v>
       </x:c>
-      <x:c r="G5" s="149" t="str">
+      <x:c r="G5" s="188" t="str">
         <x:v>Legacy — not source-audited</x:v>
       </x:c>
-      <x:c r="H5" s="150" t="n">
+      <x:c r="H5" s="189" t="n">
         <x:v>435.52</x:v>
       </x:c>
-      <x:c r="I5" s="150" t="n">
+      <x:c r="I5" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B5,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>1647.9600000000003</x:v>
       </x:c>
-      <x:c r="J5" s="150" t="n">
+      <x:c r="J5" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B5,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>11.629999999999999</x:v>
       </x:c>
-      <x:c r="K5" s="150" t="n">
+      <x:c r="K5" s="189" t="n">
         <x:f>I5+J5</x:f>
         <x:v>1659.5900000000004</x:v>
       </x:c>
-      <x:c r="L5" s="150" t="n">
+      <x:c r="L5" s="189" t="n">
         <x:f>IF(H5="","",H5-K5)</x:f>
         <x:v>-1224.0700000000004</x:v>
       </x:c>
-      <x:c r="M5" s="149" t="str">
+      <x:c r="M5" s="188" t="str">
         <x:v>Legacy baseline: no full line-level source archive existed before the Sep. 9 audit. Do not treat this row as source-certified.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
-      <x:c r="A6" s="194" t="n">
+      <x:c r="A6" s="242" t="n">
         <x:v>46273</x:v>
       </x:c>
-      <x:c r="B6" s="194" t="n">
+      <x:c r="B6" s="242" t="n">
         <x:f>A6-7</x:f>
         <x:v>46266</x:v>
       </x:c>
-      <x:c r="C6" s="194" t="n">
+      <x:c r="C6" s="242" t="n">
         <x:f>A6-1</x:f>
         <x:v>46272</x:v>
       </x:c>
-      <x:c r="D6" s="150"/>
-      <x:c r="E6" s="150"/>
-      <x:c r="F6" s="150"/>
-      <x:c r="G6" s="149" t="str">
+      <x:c r="D6" s="189"/>
+      <x:c r="E6" s="189"/>
+      <x:c r="F6" s="189"/>
+      <x:c r="G6" s="188" t="str">
         <x:v>Data verified — Sep 9</x:v>
       </x:c>
-      <x:c r="H6" s="150" t="n">
+      <x:c r="H6" s="189" t="n">
         <x:v>476.6607692307693</x:v>
       </x:c>
-      <x:c r="I6" s="150" t="n">
+      <x:c r="I6" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B6,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>447.99</x:v>
       </x:c>
-      <x:c r="J6" s="150" t="n">
+      <x:c r="J6" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B6,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>2.5</x:v>
       </x:c>
-      <x:c r="K6" s="150" t="n">
+      <x:c r="K6" s="189" t="n">
         <x:f>I6+J6</x:f>
         <x:v>450.49</x:v>
       </x:c>
-      <x:c r="L6" s="150" t="n">
+      <x:c r="L6" s="189" t="n">
         <x:f>IF(H6="","",H6-K6)</x:f>
         <x:v>26.17076923076928</x:v>
       </x:c>
-      <x:c r="M6" s="149" t="str">
+      <x:c r="M6" s="188" t="str">
         <x:v>Reviewed Wed Sep. 9 because of the holiday delay. Source-controlled import includes the Citi activity correction.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
-      <x:c r="A7" s="194" t="n">
+      <x:c r="A7" s="242" t="n">
         <x:v>46280</x:v>
       </x:c>
-      <x:c r="B7" s="194" t="n">
+      <x:c r="B7" s="242" t="n">
         <x:f>A7-7</x:f>
         <x:v>46273</x:v>
       </x:c>
-      <x:c r="C7" s="194" t="n">
+      <x:c r="C7" s="242" t="n">
         <x:f>A7-1</x:f>
         <x:v>46279</x:v>
       </x:c>
-      <x:c r="D7" s="148"/>
-      <x:c r="E7" s="148"/>
-      <x:c r="F7" s="148"/>
-      <x:c r="G7" s="149"/>
-      <x:c r="H7" s="148"/>
-      <x:c r="I7" s="150" t="n">
+      <x:c r="D7" s="187"/>
+      <x:c r="E7" s="187"/>
+      <x:c r="F7" s="187"/>
+      <x:c r="G7" s="188"/>
+      <x:c r="H7" s="187"/>
+      <x:c r="I7" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B7,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J7" s="150" t="n">
+      <x:c r="J7" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B7,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>74.49000000000001</x:v>
       </x:c>
-      <x:c r="K7" s="150" t="n">
+      <x:c r="K7" s="189" t="n">
         <x:f>I7+J7</x:f>
         <x:v>74.49000000000001</x:v>
       </x:c>
-      <x:c r="L7" s="150" t="str">
+      <x:c r="L7" s="189" t="str">
         <x:f>IF(H7="","",H7-K7)</x:f>
       </x:c>
-      <x:c r="M7" s="149"/>
+      <x:c r="M7" s="188"/>
     </x:row>
     <x:row r="8" ht="24" customHeight="1">
-      <x:c r="A8" s="194" t="n">
+      <x:c r="A8" s="242" t="n">
         <x:v>46287</x:v>
       </x:c>
-      <x:c r="B8" s="194" t="n">
+      <x:c r="B8" s="242" t="n">
         <x:f>A8-7</x:f>
         <x:v>46280</x:v>
       </x:c>
-      <x:c r="C8" s="194" t="n">
+      <x:c r="C8" s="242" t="n">
         <x:f>A8-1</x:f>
         <x:v>46286</x:v>
       </x:c>
-      <x:c r="D8" s="148"/>
-      <x:c r="E8" s="148"/>
-      <x:c r="F8" s="148"/>
-      <x:c r="G8" s="149"/>
-      <x:c r="H8" s="148"/>
-      <x:c r="I8" s="150" t="n">
+      <x:c r="D8" s="187"/>
+      <x:c r="E8" s="187"/>
+      <x:c r="F8" s="187"/>
+      <x:c r="G8" s="188"/>
+      <x:c r="H8" s="187"/>
+      <x:c r="I8" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B8,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J8" s="150" t="n">
+      <x:c r="J8" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B8,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K8" s="150" t="n">
+      <x:c r="K8" s="189" t="n">
         <x:f>I8+J8</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L8" s="150" t="str">
+      <x:c r="L8" s="189" t="str">
         <x:f>IF(H8="","",H8-K8)</x:f>
       </x:c>
-      <x:c r="M8" s="149"/>
+      <x:c r="M8" s="188"/>
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
-      <x:c r="A9" s="194" t="n">
+      <x:c r="A9" s="242" t="n">
         <x:v>46294</x:v>
       </x:c>
-      <x:c r="B9" s="194" t="n">
+      <x:c r="B9" s="242" t="n">
         <x:f>A9-7</x:f>
         <x:v>46287</x:v>
       </x:c>
-      <x:c r="C9" s="194" t="n">
+      <x:c r="C9" s="242" t="n">
         <x:f>A9-1</x:f>
         <x:v>46293</x:v>
       </x:c>
-      <x:c r="D9" s="148"/>
-      <x:c r="E9" s="148"/>
-      <x:c r="F9" s="148"/>
-      <x:c r="G9" s="149"/>
-      <x:c r="H9" s="148"/>
-      <x:c r="I9" s="150" t="n">
+      <x:c r="D9" s="187"/>
+      <x:c r="E9" s="187"/>
+      <x:c r="F9" s="187"/>
+      <x:c r="G9" s="188"/>
+      <x:c r="H9" s="187"/>
+      <x:c r="I9" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B9,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J9" s="150" t="n">
+      <x:c r="J9" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B9,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K9" s="150" t="n">
+      <x:c r="K9" s="189" t="n">
         <x:f>I9+J9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L9" s="150" t="str">
+      <x:c r="L9" s="189" t="str">
         <x:f>IF(H9="","",H9-K9)</x:f>
       </x:c>
-      <x:c r="M9" s="149"/>
+      <x:c r="M9" s="188"/>
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
-      <x:c r="A10" s="194" t="n">
+      <x:c r="A10" s="242" t="n">
         <x:v>46301</x:v>
       </x:c>
-      <x:c r="B10" s="194" t="n">
+      <x:c r="B10" s="242" t="n">
         <x:f>A10-7</x:f>
         <x:v>46294</x:v>
       </x:c>
-      <x:c r="C10" s="194" t="n">
+      <x:c r="C10" s="242" t="n">
         <x:f>A10-1</x:f>
         <x:v>46300</x:v>
       </x:c>
-      <x:c r="D10" s="148"/>
-      <x:c r="E10" s="148"/>
-      <x:c r="F10" s="148"/>
-      <x:c r="G10" s="149"/>
-      <x:c r="H10" s="148"/>
-      <x:c r="I10" s="150" t="n">
+      <x:c r="D10" s="187"/>
+      <x:c r="E10" s="187"/>
+      <x:c r="F10" s="187"/>
+      <x:c r="G10" s="188"/>
+      <x:c r="H10" s="187"/>
+      <x:c r="I10" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B10,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J10" s="150" t="n">
+      <x:c r="J10" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B10,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K10" s="150" t="n">
+      <x:c r="K10" s="189" t="n">
         <x:f>I10+J10</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L10" s="150" t="str">
+      <x:c r="L10" s="189" t="str">
         <x:f>IF(H10="","",H10-K10)</x:f>
       </x:c>
-      <x:c r="M10" s="149"/>
+      <x:c r="M10" s="188"/>
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
-      <x:c r="A11" s="194" t="n">
+      <x:c r="A11" s="242" t="n">
         <x:v>46308</x:v>
       </x:c>
-      <x:c r="B11" s="194" t="n">
+      <x:c r="B11" s="242" t="n">
         <x:f>A11-7</x:f>
         <x:v>46301</x:v>
       </x:c>
-      <x:c r="C11" s="194" t="n">
+      <x:c r="C11" s="242" t="n">
         <x:f>A11-1</x:f>
         <x:v>46307</x:v>
       </x:c>
-      <x:c r="D11" s="148"/>
-      <x:c r="E11" s="148"/>
-      <x:c r="F11" s="148"/>
-      <x:c r="G11" s="149"/>
-      <x:c r="H11" s="148"/>
-      <x:c r="I11" s="150" t="n">
+      <x:c r="D11" s="187"/>
+      <x:c r="E11" s="187"/>
+      <x:c r="F11" s="187"/>
+      <x:c r="G11" s="188"/>
+      <x:c r="H11" s="187"/>
+      <x:c r="I11" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B11,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J11" s="150" t="n">
+      <x:c r="J11" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B11,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K11" s="150" t="n">
+      <x:c r="K11" s="189" t="n">
         <x:f>I11+J11</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L11" s="150" t="str">
+      <x:c r="L11" s="189" t="str">
         <x:f>IF(H11="","",H11-K11)</x:f>
       </x:c>
-      <x:c r="M11" s="149"/>
+      <x:c r="M11" s="188"/>
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
-      <x:c r="A12" s="194" t="n">
+      <x:c r="A12" s="242" t="n">
         <x:v>46315</x:v>
       </x:c>
-      <x:c r="B12" s="194" t="n">
+      <x:c r="B12" s="242" t="n">
         <x:f>A12-7</x:f>
         <x:v>46308</x:v>
       </x:c>
-      <x:c r="C12" s="194" t="n">
+      <x:c r="C12" s="242" t="n">
         <x:f>A12-1</x:f>
         <x:v>46314</x:v>
       </x:c>
-      <x:c r="D12" s="148"/>
-      <x:c r="E12" s="148"/>
-      <x:c r="F12" s="148"/>
-      <x:c r="G12" s="149"/>
-      <x:c r="H12" s="148"/>
-      <x:c r="I12" s="150" t="n">
+      <x:c r="D12" s="187"/>
+      <x:c r="E12" s="187"/>
+      <x:c r="F12" s="187"/>
+      <x:c r="G12" s="188"/>
+      <x:c r="H12" s="187"/>
+      <x:c r="I12" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B12,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J12" s="150" t="n">
+      <x:c r="J12" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B12,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K12" s="150" t="n">
+      <x:c r="K12" s="189" t="n">
         <x:f>I12+J12</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L12" s="150" t="str">
+      <x:c r="L12" s="189" t="str">
         <x:f>IF(H12="","",H12-K12)</x:f>
       </x:c>
-      <x:c r="M12" s="149"/>
+      <x:c r="M12" s="188"/>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
-      <x:c r="A13" s="194" t="n">
+      <x:c r="A13" s="242" t="n">
         <x:v>46322</x:v>
       </x:c>
-      <x:c r="B13" s="194" t="n">
+      <x:c r="B13" s="242" t="n">
         <x:f>A13-7</x:f>
         <x:v>46315</x:v>
       </x:c>
-      <x:c r="C13" s="194" t="n">
+      <x:c r="C13" s="242" t="n">
         <x:f>A13-1</x:f>
         <x:v>46321</x:v>
       </x:c>
-      <x:c r="D13" s="148"/>
-      <x:c r="E13" s="148"/>
-      <x:c r="F13" s="148"/>
-      <x:c r="G13" s="149"/>
-      <x:c r="H13" s="148"/>
-      <x:c r="I13" s="150" t="n">
+      <x:c r="D13" s="187"/>
+      <x:c r="E13" s="187"/>
+      <x:c r="F13" s="187"/>
+      <x:c r="G13" s="188"/>
+      <x:c r="H13" s="187"/>
+      <x:c r="I13" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B13,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J13" s="150" t="n">
+      <x:c r="J13" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B13,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K13" s="150" t="n">
+      <x:c r="K13" s="189" t="n">
         <x:f>I13+J13</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L13" s="150" t="str">
+      <x:c r="L13" s="189" t="str">
         <x:f>IF(H13="","",H13-K13)</x:f>
       </x:c>
-      <x:c r="M13" s="149"/>
+      <x:c r="M13" s="188"/>
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
-      <x:c r="A14" s="194" t="n">
+      <x:c r="A14" s="242" t="n">
         <x:v>46329</x:v>
       </x:c>
-      <x:c r="B14" s="194" t="n">
+      <x:c r="B14" s="242" t="n">
         <x:f>A14-7</x:f>
         <x:v>46322</x:v>
       </x:c>
-      <x:c r="C14" s="194" t="n">
+      <x:c r="C14" s="242" t="n">
         <x:f>A14-1</x:f>
         <x:v>46328</x:v>
       </x:c>
-      <x:c r="D14" s="148"/>
-      <x:c r="E14" s="148"/>
-      <x:c r="F14" s="148"/>
-      <x:c r="G14" s="149"/>
-      <x:c r="H14" s="148"/>
-      <x:c r="I14" s="150" t="n">
+      <x:c r="D14" s="187"/>
+      <x:c r="E14" s="187"/>
+      <x:c r="F14" s="187"/>
+      <x:c r="G14" s="188"/>
+      <x:c r="H14" s="187"/>
+      <x:c r="I14" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B14,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J14" s="150" t="n">
+      <x:c r="J14" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B14,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K14" s="150" t="n">
+      <x:c r="K14" s="189" t="n">
         <x:f>I14+J14</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L14" s="150" t="str">
+      <x:c r="L14" s="189" t="str">
         <x:f>IF(H14="","",H14-K14)</x:f>
       </x:c>
-      <x:c r="M14" s="149"/>
+      <x:c r="M14" s="188"/>
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
-      <x:c r="A15" s="194" t="n">
+      <x:c r="A15" s="242" t="n">
         <x:v>46336</x:v>
       </x:c>
-      <x:c r="B15" s="194" t="n">
+      <x:c r="B15" s="242" t="n">
         <x:f>A15-7</x:f>
         <x:v>46329</x:v>
       </x:c>
-      <x:c r="C15" s="194" t="n">
+      <x:c r="C15" s="242" t="n">
         <x:f>A15-1</x:f>
         <x:v>46335</x:v>
       </x:c>
-      <x:c r="D15" s="148"/>
-      <x:c r="E15" s="148"/>
-      <x:c r="F15" s="148"/>
-      <x:c r="G15" s="149"/>
-      <x:c r="H15" s="148"/>
-      <x:c r="I15" s="150" t="n">
+      <x:c r="D15" s="187"/>
+      <x:c r="E15" s="187"/>
+      <x:c r="F15" s="187"/>
+      <x:c r="G15" s="188"/>
+      <x:c r="H15" s="187"/>
+      <x:c r="I15" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B15,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J15" s="150" t="n">
+      <x:c r="J15" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B15,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K15" s="150" t="n">
+      <x:c r="K15" s="189" t="n">
         <x:f>I15+J15</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L15" s="150" t="str">
+      <x:c r="L15" s="189" t="str">
         <x:f>IF(H15="","",H15-K15)</x:f>
       </x:c>
-      <x:c r="M15" s="149"/>
+      <x:c r="M15" s="188"/>
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
-      <x:c r="A16" s="194" t="n">
+      <x:c r="A16" s="242" t="n">
         <x:v>46343</x:v>
       </x:c>
-      <x:c r="B16" s="194" t="n">
+      <x:c r="B16" s="242" t="n">
         <x:f>A16-7</x:f>
         <x:v>46336</x:v>
       </x:c>
-      <x:c r="C16" s="194" t="n">
+      <x:c r="C16" s="242" t="n">
         <x:f>A16-1</x:f>
         <x:v>46342</x:v>
       </x:c>
-      <x:c r="D16" s="148"/>
-      <x:c r="E16" s="148"/>
-      <x:c r="F16" s="148"/>
-      <x:c r="G16" s="149"/>
-      <x:c r="H16" s="148"/>
-      <x:c r="I16" s="150" t="n">
+      <x:c r="D16" s="187"/>
+      <x:c r="E16" s="187"/>
+      <x:c r="F16" s="187"/>
+      <x:c r="G16" s="188"/>
+      <x:c r="H16" s="187"/>
+      <x:c r="I16" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B16,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J16" s="150" t="n">
+      <x:c r="J16" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B16,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K16" s="150" t="n">
+      <x:c r="K16" s="189" t="n">
         <x:f>I16+J16</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L16" s="150" t="str">
+      <x:c r="L16" s="189" t="str">
         <x:f>IF(H16="","",H16-K16)</x:f>
       </x:c>
-      <x:c r="M16" s="149"/>
+      <x:c r="M16" s="188"/>
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
-      <x:c r="A17" s="194" t="n">
+      <x:c r="A17" s="242" t="n">
         <x:v>46350</x:v>
       </x:c>
-      <x:c r="B17" s="194" t="n">
+      <x:c r="B17" s="242" t="n">
         <x:f>A17-7</x:f>
         <x:v>46343</x:v>
       </x:c>
-      <x:c r="C17" s="194" t="n">
+      <x:c r="C17" s="242" t="n">
         <x:f>A17-1</x:f>
         <x:v>46349</x:v>
       </x:c>
-      <x:c r="D17" s="148"/>
-      <x:c r="E17" s="148"/>
-      <x:c r="F17" s="148"/>
-      <x:c r="G17" s="149"/>
-      <x:c r="H17" s="148"/>
-      <x:c r="I17" s="150" t="n">
+      <x:c r="D17" s="187"/>
+      <x:c r="E17" s="187"/>
+      <x:c r="F17" s="187"/>
+      <x:c r="G17" s="188"/>
+      <x:c r="H17" s="187"/>
+      <x:c r="I17" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B17,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J17" s="150" t="n">
+      <x:c r="J17" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B17,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K17" s="150" t="n">
+      <x:c r="K17" s="189" t="n">
         <x:f>I17+J17</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L17" s="150" t="str">
+      <x:c r="L17" s="189" t="str">
         <x:f>IF(H17="","",H17-K17)</x:f>
       </x:c>
-      <x:c r="M17" s="149"/>
+      <x:c r="M17" s="188"/>
     </x:row>
     <x:row r="18" ht="24" customHeight="1">
-      <x:c r="A18" s="194" t="n">
+      <x:c r="A18" s="242" t="n">
         <x:v>46357</x:v>
       </x:c>
-      <x:c r="B18" s="194" t="n">
+      <x:c r="B18" s="242" t="n">
         <x:f>A18-7</x:f>
         <x:v>46350</x:v>
       </x:c>
-      <x:c r="C18" s="194" t="n">
+      <x:c r="C18" s="242" t="n">
         <x:f>A18-1</x:f>
         <x:v>46356</x:v>
       </x:c>
-      <x:c r="D18" s="148"/>
-      <x:c r="E18" s="148"/>
-      <x:c r="F18" s="148"/>
-      <x:c r="G18" s="149"/>
-      <x:c r="H18" s="148"/>
-      <x:c r="I18" s="150" t="n">
+      <x:c r="D18" s="187"/>
+      <x:c r="E18" s="187"/>
+      <x:c r="F18" s="187"/>
+      <x:c r="G18" s="188"/>
+      <x:c r="H18" s="187"/>
+      <x:c r="I18" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B18,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J18" s="150" t="n">
+      <x:c r="J18" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B18,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K18" s="150" t="n">
+      <x:c r="K18" s="189" t="n">
         <x:f>I18+J18</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L18" s="150" t="str">
+      <x:c r="L18" s="189" t="str">
         <x:f>IF(H18="","",H18-K18)</x:f>
       </x:c>
-      <x:c r="M18" s="149"/>
+      <x:c r="M18" s="188"/>
     </x:row>
     <x:row r="19" ht="24" customHeight="1">
-      <x:c r="A19" s="194" t="n">
+      <x:c r="A19" s="242" t="n">
         <x:v>46364</x:v>
       </x:c>
-      <x:c r="B19" s="194" t="n">
+      <x:c r="B19" s="242" t="n">
         <x:f>A19-7</x:f>
         <x:v>46357</x:v>
       </x:c>
-      <x:c r="C19" s="194" t="n">
+      <x:c r="C19" s="242" t="n">
         <x:f>A19-1</x:f>
         <x:v>46363</x:v>
       </x:c>
-      <x:c r="D19" s="148"/>
-      <x:c r="E19" s="148"/>
-      <x:c r="F19" s="148"/>
-      <x:c r="G19" s="149"/>
-      <x:c r="H19" s="148"/>
-      <x:c r="I19" s="150" t="n">
+      <x:c r="D19" s="187"/>
+      <x:c r="E19" s="187"/>
+      <x:c r="F19" s="187"/>
+      <x:c r="G19" s="188"/>
+      <x:c r="H19" s="187"/>
+      <x:c r="I19" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B19,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J19" s="150" t="n">
+      <x:c r="J19" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B19,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K19" s="150" t="n">
+      <x:c r="K19" s="189" t="n">
         <x:f>I19+J19</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L19" s="150" t="str">
+      <x:c r="L19" s="189" t="str">
         <x:f>IF(H19="","",H19-K19)</x:f>
       </x:c>
-      <x:c r="M19" s="149"/>
+      <x:c r="M19" s="188"/>
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
-      <x:c r="A20" s="194" t="n">
+      <x:c r="A20" s="242" t="n">
         <x:v>46371</x:v>
       </x:c>
-      <x:c r="B20" s="194" t="n">
+      <x:c r="B20" s="242" t="n">
         <x:f>A20-7</x:f>
         <x:v>46364</x:v>
       </x:c>
-      <x:c r="C20" s="194" t="n">
+      <x:c r="C20" s="242" t="n">
         <x:f>A20-1</x:f>
         <x:v>46370</x:v>
       </x:c>
-      <x:c r="D20" s="148"/>
-      <x:c r="E20" s="148"/>
-      <x:c r="F20" s="148"/>
-      <x:c r="G20" s="149"/>
-      <x:c r="H20" s="148"/>
-      <x:c r="I20" s="150" t="n">
+      <x:c r="D20" s="187"/>
+      <x:c r="E20" s="187"/>
+      <x:c r="F20" s="187"/>
+      <x:c r="G20" s="188"/>
+      <x:c r="H20" s="187"/>
+      <x:c r="I20" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B20,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J20" s="150" t="n">
+      <x:c r="J20" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B20,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K20" s="150" t="n">
+      <x:c r="K20" s="189" t="n">
         <x:f>I20+J20</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L20" s="150" t="str">
+      <x:c r="L20" s="189" t="str">
         <x:f>IF(H20="","",H20-K20)</x:f>
       </x:c>
-      <x:c r="M20" s="149"/>
+      <x:c r="M20" s="188"/>
     </x:row>
     <x:row r="21" ht="24" customHeight="1">
-      <x:c r="A21" s="194" t="n">
+      <x:c r="A21" s="242" t="n">
         <x:v>46378</x:v>
       </x:c>
-      <x:c r="B21" s="194" t="n">
+      <x:c r="B21" s="242" t="n">
         <x:f>A21-7</x:f>
         <x:v>46371</x:v>
       </x:c>
-      <x:c r="C21" s="194" t="n">
+      <x:c r="C21" s="242" t="n">
         <x:f>A21-1</x:f>
         <x:v>46377</x:v>
       </x:c>
-      <x:c r="D21" s="148"/>
-      <x:c r="E21" s="148"/>
-      <x:c r="F21" s="148"/>
-      <x:c r="G21" s="149"/>
-      <x:c r="H21" s="148"/>
-      <x:c r="I21" s="150" t="n">
+      <x:c r="D21" s="187"/>
+      <x:c r="E21" s="187"/>
+      <x:c r="F21" s="187"/>
+      <x:c r="G21" s="188"/>
+      <x:c r="H21" s="187"/>
+      <x:c r="I21" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B21,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J21" s="150" t="n">
+      <x:c r="J21" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B21,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K21" s="150" t="n">
+      <x:c r="K21" s="189" t="n">
         <x:f>I21+J21</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L21" s="150" t="str">
+      <x:c r="L21" s="189" t="str">
         <x:f>IF(H21="","",H21-K21)</x:f>
       </x:c>
-      <x:c r="M21" s="149"/>
+      <x:c r="M21" s="188"/>
     </x:row>
     <x:row r="22" ht="24" customHeight="1">
-      <x:c r="A22" s="194" t="n">
+      <x:c r="A22" s="242" t="n">
         <x:v>46385</x:v>
       </x:c>
-      <x:c r="B22" s="194" t="n">
+      <x:c r="B22" s="242" t="n">
         <x:f>A22-7</x:f>
         <x:v>46378</x:v>
       </x:c>
-      <x:c r="C22" s="194" t="n">
+      <x:c r="C22" s="242" t="n">
         <x:f>A22-1</x:f>
         <x:v>46384</x:v>
       </x:c>
-      <x:c r="D22" s="148"/>
-      <x:c r="E22" s="148"/>
-      <x:c r="F22" s="148"/>
-      <x:c r="G22" s="149"/>
-      <x:c r="H22" s="148"/>
-      <x:c r="I22" s="150" t="n">
+      <x:c r="D22" s="187"/>
+      <x:c r="E22" s="187"/>
+      <x:c r="F22" s="187"/>
+      <x:c r="G22" s="188"/>
+      <x:c r="H22" s="187"/>
+      <x:c r="I22" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B22,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J22" s="150" t="n">
+      <x:c r="J22" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B22,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K22" s="150" t="n">
+      <x:c r="K22" s="189" t="n">
         <x:f>I22+J22</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L22" s="150" t="str">
+      <x:c r="L22" s="189" t="str">
         <x:f>IF(H22="","",H22-K22)</x:f>
       </x:c>
-      <x:c r="M22" s="149"/>
+      <x:c r="M22" s="188"/>
     </x:row>
     <x:row r="23" ht="24" customHeight="1">
-      <x:c r="A23" s="194" t="n">
+      <x:c r="A23" s="242" t="n">
         <x:v>46392</x:v>
       </x:c>
-      <x:c r="B23" s="194" t="n">
+      <x:c r="B23" s="242" t="n">
         <x:f>A23-7</x:f>
         <x:v>46385</x:v>
       </x:c>
-      <x:c r="C23" s="194" t="n">
+      <x:c r="C23" s="242" t="n">
         <x:f>A23-1</x:f>
         <x:v>46391</x:v>
       </x:c>
-      <x:c r="D23" s="148"/>
-      <x:c r="E23" s="148"/>
-      <x:c r="F23" s="148"/>
-      <x:c r="G23" s="149"/>
-      <x:c r="H23" s="148"/>
-      <x:c r="I23" s="150" t="n">
+      <x:c r="D23" s="187"/>
+      <x:c r="E23" s="187"/>
+      <x:c r="F23" s="187"/>
+      <x:c r="G23" s="188"/>
+      <x:c r="H23" s="187"/>
+      <x:c r="I23" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B23,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J23" s="150" t="n">
+      <x:c r="J23" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B23,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K23" s="150" t="n">
+      <x:c r="K23" s="189" t="n">
         <x:f>I23+J23</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L23" s="150" t="str">
+      <x:c r="L23" s="189" t="str">
         <x:f>IF(H23="","",H23-K23)</x:f>
       </x:c>
-      <x:c r="M23" s="149"/>
+      <x:c r="M23" s="188"/>
     </x:row>
     <x:row r="24" ht="24" customHeight="1">
-      <x:c r="A24" s="194" t="n">
+      <x:c r="A24" s="242" t="n">
         <x:v>46399</x:v>
       </x:c>
-      <x:c r="B24" s="194" t="n">
+      <x:c r="B24" s="242" t="n">
         <x:f>A24-7</x:f>
         <x:v>46392</x:v>
       </x:c>
-      <x:c r="C24" s="194" t="n">
+      <x:c r="C24" s="242" t="n">
         <x:f>A24-1</x:f>
         <x:v>46398</x:v>
       </x:c>
-      <x:c r="D24" s="148"/>
-      <x:c r="E24" s="148"/>
-      <x:c r="F24" s="148"/>
-      <x:c r="G24" s="149"/>
-      <x:c r="H24" s="148"/>
-      <x:c r="I24" s="150" t="n">
+      <x:c r="D24" s="187"/>
+      <x:c r="E24" s="187"/>
+      <x:c r="F24" s="187"/>
+      <x:c r="G24" s="188"/>
+      <x:c r="H24" s="187"/>
+      <x:c r="I24" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B24,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J24" s="150" t="n">
+      <x:c r="J24" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B24,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K24" s="150" t="n">
+      <x:c r="K24" s="189" t="n">
         <x:f>I24+J24</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L24" s="150" t="str">
+      <x:c r="L24" s="189" t="str">
         <x:f>IF(H24="","",H24-K24)</x:f>
       </x:c>
-      <x:c r="M24" s="149"/>
+      <x:c r="M24" s="188"/>
     </x:row>
     <x:row r="25" ht="24" customHeight="1">
-      <x:c r="A25" s="194" t="n">
+      <x:c r="A25" s="242" t="n">
         <x:v>46406</x:v>
       </x:c>
-      <x:c r="B25" s="194" t="n">
+      <x:c r="B25" s="242" t="n">
         <x:f>A25-7</x:f>
         <x:v>46399</x:v>
       </x:c>
-      <x:c r="C25" s="194" t="n">
+      <x:c r="C25" s="242" t="n">
         <x:f>A25-1</x:f>
         <x:v>46405</x:v>
       </x:c>
-      <x:c r="D25" s="148"/>
-      <x:c r="E25" s="148"/>
-      <x:c r="F25" s="148"/>
-      <x:c r="G25" s="149"/>
-      <x:c r="H25" s="148"/>
-      <x:c r="I25" s="150" t="n">
+      <x:c r="D25" s="187"/>
+      <x:c r="E25" s="187"/>
+      <x:c r="F25" s="187"/>
+      <x:c r="G25" s="188"/>
+      <x:c r="H25" s="187"/>
+      <x:c r="I25" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B25,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J25" s="150" t="n">
+      <x:c r="J25" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B25,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K25" s="150" t="n">
+      <x:c r="K25" s="189" t="n">
         <x:f>I25+J25</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L25" s="150" t="str">
+      <x:c r="L25" s="189" t="str">
         <x:f>IF(H25="","",H25-K25)</x:f>
       </x:c>
-      <x:c r="M25" s="149"/>
+      <x:c r="M25" s="188"/>
     </x:row>
     <x:row r="26" ht="24" customHeight="1">
-      <x:c r="A26" s="194" t="n">
+      <x:c r="A26" s="242" t="n">
         <x:v>46413</x:v>
       </x:c>
-      <x:c r="B26" s="194" t="n">
+      <x:c r="B26" s="242" t="n">
         <x:f>A26-7</x:f>
         <x:v>46406</x:v>
       </x:c>
-      <x:c r="C26" s="194" t="n">
+      <x:c r="C26" s="242" t="n">
         <x:f>A26-1</x:f>
         <x:v>46412</x:v>
       </x:c>
-      <x:c r="D26" s="148"/>
-      <x:c r="E26" s="148"/>
-      <x:c r="F26" s="148"/>
-      <x:c r="G26" s="149"/>
-      <x:c r="H26" s="148"/>
-      <x:c r="I26" s="150" t="n">
+      <x:c r="D26" s="187"/>
+      <x:c r="E26" s="187"/>
+      <x:c r="F26" s="187"/>
+      <x:c r="G26" s="188"/>
+      <x:c r="H26" s="187"/>
+      <x:c r="I26" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B26,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J26" s="150" t="n">
+      <x:c r="J26" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B26,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K26" s="150" t="n">
+      <x:c r="K26" s="189" t="n">
         <x:f>I26+J26</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L26" s="150" t="str">
+      <x:c r="L26" s="189" t="str">
         <x:f>IF(H26="","",H26-K26)</x:f>
       </x:c>
-      <x:c r="M26" s="149"/>
+      <x:c r="M26" s="188"/>
     </x:row>
     <x:row r="27" ht="24" customHeight="1">
-      <x:c r="A27" s="194" t="n">
+      <x:c r="A27" s="242" t="n">
         <x:v>46420</x:v>
       </x:c>
-      <x:c r="B27" s="194" t="n">
+      <x:c r="B27" s="242" t="n">
         <x:f>A27-7</x:f>
         <x:v>46413</x:v>
       </x:c>
-      <x:c r="C27" s="194" t="n">
+      <x:c r="C27" s="242" t="n">
         <x:f>A27-1</x:f>
         <x:v>46419</x:v>
       </x:c>
-      <x:c r="D27" s="148"/>
-      <x:c r="E27" s="148"/>
-      <x:c r="F27" s="148"/>
-      <x:c r="G27" s="149"/>
-      <x:c r="H27" s="148"/>
-      <x:c r="I27" s="150" t="n">
+      <x:c r="D27" s="187"/>
+      <x:c r="E27" s="187"/>
+      <x:c r="F27" s="187"/>
+      <x:c r="G27" s="188"/>
+      <x:c r="H27" s="187"/>
+      <x:c r="I27" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B27,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J27" s="150" t="n">
+      <x:c r="J27" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B27,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K27" s="150" t="n">
+      <x:c r="K27" s="189" t="n">
         <x:f>I27+J27</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L27" s="150" t="str">
+      <x:c r="L27" s="189" t="str">
         <x:f>IF(H27="","",H27-K27)</x:f>
       </x:c>
-      <x:c r="M27" s="149"/>
+      <x:c r="M27" s="188"/>
     </x:row>
     <x:row r="28" ht="24" customHeight="1">
-      <x:c r="A28" s="194" t="n">
+      <x:c r="A28" s="242" t="n">
         <x:v>46427</x:v>
       </x:c>
-      <x:c r="B28" s="194" t="n">
+      <x:c r="B28" s="242" t="n">
         <x:f>A28-7</x:f>
         <x:v>46420</x:v>
       </x:c>
-      <x:c r="C28" s="194" t="n">
+      <x:c r="C28" s="242" t="n">
         <x:f>A28-1</x:f>
         <x:v>46426</x:v>
       </x:c>
-      <x:c r="D28" s="148"/>
-      <x:c r="E28" s="148"/>
-      <x:c r="F28" s="148"/>
-      <x:c r="G28" s="149"/>
-      <x:c r="H28" s="148"/>
-      <x:c r="I28" s="150" t="n">
+      <x:c r="D28" s="187"/>
+      <x:c r="E28" s="187"/>
+      <x:c r="F28" s="187"/>
+      <x:c r="G28" s="188"/>
+      <x:c r="H28" s="187"/>
+      <x:c r="I28" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B28,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J28" s="150" t="n">
+      <x:c r="J28" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B28,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K28" s="150" t="n">
+      <x:c r="K28" s="189" t="n">
         <x:f>I28+J28</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L28" s="150" t="str">
+      <x:c r="L28" s="189" t="str">
         <x:f>IF(H28="","",H28-K28)</x:f>
       </x:c>
-      <x:c r="M28" s="149"/>
+      <x:c r="M28" s="188"/>
     </x:row>
     <x:row r="29" ht="24" customHeight="1">
-      <x:c r="A29" s="194" t="n">
+      <x:c r="A29" s="242" t="n">
         <x:v>46434</x:v>
       </x:c>
-      <x:c r="B29" s="194" t="n">
+      <x:c r="B29" s="242" t="n">
         <x:f>A29-7</x:f>
         <x:v>46427</x:v>
       </x:c>
-      <x:c r="C29" s="194" t="n">
+      <x:c r="C29" s="242" t="n">
         <x:f>A29-1</x:f>
         <x:v>46433</x:v>
       </x:c>
-      <x:c r="D29" s="148"/>
-      <x:c r="E29" s="148"/>
-      <x:c r="F29" s="148"/>
-      <x:c r="G29" s="149"/>
-      <x:c r="H29" s="148"/>
-      <x:c r="I29" s="150" t="n">
+      <x:c r="D29" s="187"/>
+      <x:c r="E29" s="187"/>
+      <x:c r="F29" s="187"/>
+      <x:c r="G29" s="188"/>
+      <x:c r="H29" s="187"/>
+      <x:c r="I29" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B29,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J29" s="150" t="n">
+      <x:c r="J29" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B29,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K29" s="150" t="n">
+      <x:c r="K29" s="189" t="n">
         <x:f>I29+J29</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L29" s="150" t="str">
+      <x:c r="L29" s="189" t="str">
         <x:f>IF(H29="","",H29-K29)</x:f>
       </x:c>
-      <x:c r="M29" s="149"/>
+      <x:c r="M29" s="188"/>
     </x:row>
     <x:row r="30" ht="24" customHeight="1">
-      <x:c r="A30" s="194" t="n">
+      <x:c r="A30" s="242" t="n">
         <x:v>46441</x:v>
       </x:c>
-      <x:c r="B30" s="194" t="n">
+      <x:c r="B30" s="242" t="n">
         <x:f>A30-7</x:f>
         <x:v>46434</x:v>
       </x:c>
-      <x:c r="C30" s="194" t="n">
+      <x:c r="C30" s="242" t="n">
         <x:f>A30-1</x:f>
         <x:v>46440</x:v>
       </x:c>
-      <x:c r="D30" s="148"/>
-      <x:c r="E30" s="148"/>
-      <x:c r="F30" s="148"/>
-      <x:c r="G30" s="149"/>
-      <x:c r="H30" s="148"/>
-      <x:c r="I30" s="150" t="n">
+      <x:c r="D30" s="187"/>
+      <x:c r="E30" s="187"/>
+      <x:c r="F30" s="187"/>
+      <x:c r="G30" s="188"/>
+      <x:c r="H30" s="187"/>
+      <x:c r="I30" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B30,'Support - Ledger'!$E$5:$E$304,"Posted",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J30" s="150" t="n">
+      <x:c r="J30" s="189" t="n">
         <x:f>SUMIFS('Support - Ledger'!$D$5:$D$304,'Support - Ledger'!$H$5:$H$304,B30,'Support - Ledger'!$E$5:$E$304,"Pending",'Support - Ledger'!$G$5:$G$304,"Include",'Support - Ledger'!$M$5:$M$304,"Verified")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K30" s="150" t="n">
+      <x:c r="K30" s="189" t="n">
         <x:f>I30+J30</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L30" s="150" t="str">
+      <x:c r="L30" s="189" t="str">
         <x:f>IF(H30="","",H30-K30)</x:f>
       </x:c>
-      <x:c r="M30" s="149"/>
+      <x:c r="M30" s="188"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -7092,7 +7585,7 @@
     <x:mergeCell ref="A2:M2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="L5:L30">
-    <x:cfRule type="cellIs" dxfId="13" priority="1" operator="lessThan">
+    <x:cfRule type="cellIs" dxfId="17" priority="1" operator="lessThan">
       <x:formula>0</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
@@ -7221,7 +7714,7 @@
       <x:c r="G5" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H5" s="184" t="n">
+      <x:c r="H5" s="232" t="n">
         <x:f>IF(B5="","",B5-WEEKDAY(B5-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -7263,7 +7756,7 @@
       <x:c r="G6" s="41" t="str">
         <x:v>Exclude</x:v>
       </x:c>
-      <x:c r="H6" s="184" t="n">
+      <x:c r="H6" s="232" t="n">
         <x:f>IF(B6="","",B6-WEEKDAY(B6-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -7305,7 +7798,7 @@
       <x:c r="G7" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H7" s="184" t="n">
+      <x:c r="H7" s="232" t="n">
         <x:f>IF(B7="","",B7-WEEKDAY(B7-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -7347,7 +7840,7 @@
       <x:c r="G8" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H8" s="184" t="n">
+      <x:c r="H8" s="232" t="n">
         <x:f>IF(B8="","",B8-WEEKDAY(B8-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -7389,7 +7882,7 @@
       <x:c r="G9" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H9" s="184" t="n">
+      <x:c r="H9" s="232" t="n">
         <x:f>IF(B9="","",B9-WEEKDAY(B9-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -7431,7 +7924,7 @@
       <x:c r="G10" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H10" s="184" t="n">
+      <x:c r="H10" s="232" t="n">
         <x:f>IF(B10="","",B10-WEEKDAY(B10-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -7473,7 +7966,7 @@
       <x:c r="G11" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H11" s="184" t="n">
+      <x:c r="H11" s="232" t="n">
         <x:f>IF(B11="","",B11-WEEKDAY(B11-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -7515,7 +8008,7 @@
       <x:c r="G12" s="41" t="str">
         <x:v>Exclude</x:v>
       </x:c>
-      <x:c r="H12" s="184" t="n">
+      <x:c r="H12" s="232" t="n">
         <x:f>IF(B12="","",B12-WEEKDAY(B12-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -7557,7 +8050,7 @@
       <x:c r="G13" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H13" s="184" t="n">
+      <x:c r="H13" s="232" t="n">
         <x:f>IF(B13="","",B13-WEEKDAY(B13-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -7599,7 +8092,7 @@
       <x:c r="G14" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H14" s="184" t="n">
+      <x:c r="H14" s="232" t="n">
         <x:f>IF(B14="","",B14-WEEKDAY(B14-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -7641,7 +8134,7 @@
       <x:c r="G15" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H15" s="184" t="n">
+      <x:c r="H15" s="232" t="n">
         <x:f>IF(B15="","",B15-WEEKDAY(B15-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -7683,7 +8176,7 @@
       <x:c r="G16" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H16" s="184" t="n">
+      <x:c r="H16" s="232" t="n">
         <x:f>IF(B16="","",B16-WEEKDAY(B16-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -7725,7 +8218,7 @@
       <x:c r="G17" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H17" s="184" t="n">
+      <x:c r="H17" s="232" t="n">
         <x:f>IF(B17="","",B17-WEEKDAY(B17-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -7767,7 +8260,7 @@
       <x:c r="G18" s="41" t="str">
         <x:v>Exclude</x:v>
       </x:c>
-      <x:c r="H18" s="184" t="n">
+      <x:c r="H18" s="232" t="n">
         <x:f>IF(B18="","",B18-WEEKDAY(B18-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -7809,7 +8302,7 @@
       <x:c r="G19" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H19" s="184" t="n">
+      <x:c r="H19" s="232" t="n">
         <x:f>IF(B19="","",B19-WEEKDAY(B19-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -7851,7 +8344,7 @@
       <x:c r="G20" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H20" s="184" t="n">
+      <x:c r="H20" s="232" t="n">
         <x:f>IF(B20="","",B20-WEEKDAY(B20-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -7893,7 +8386,7 @@
       <x:c r="G21" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H21" s="184" t="n">
+      <x:c r="H21" s="232" t="n">
         <x:f>IF(B21="","",B21-WEEKDAY(B21-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -7935,7 +8428,7 @@
       <x:c r="G22" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H22" s="184" t="n">
+      <x:c r="H22" s="232" t="n">
         <x:f>IF(B22="","",B22-WEEKDAY(B22-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -7977,7 +8470,7 @@
       <x:c r="G23" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H23" s="184" t="n">
+      <x:c r="H23" s="232" t="n">
         <x:f>IF(B23="","",B23-WEEKDAY(B23-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -8019,7 +8512,7 @@
       <x:c r="G24" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H24" s="184" t="n">
+      <x:c r="H24" s="232" t="n">
         <x:f>IF(B24="","",B24-WEEKDAY(B24-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -8061,7 +8554,7 @@
       <x:c r="G25" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H25" s="184" t="n">
+      <x:c r="H25" s="232" t="n">
         <x:f>IF(B25="","",B25-WEEKDAY(B25-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -8103,7 +8596,7 @@
       <x:c r="G26" s="41" t="str">
         <x:v>Exclude</x:v>
       </x:c>
-      <x:c r="H26" s="184" t="n">
+      <x:c r="H26" s="232" t="n">
         <x:f>IF(B26="","",B26-WEEKDAY(B26-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -8145,7 +8638,7 @@
       <x:c r="G27" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H27" s="184" t="n">
+      <x:c r="H27" s="232" t="n">
         <x:f>IF(B27="","",B27-WEEKDAY(B27-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -8187,7 +8680,7 @@
       <x:c r="G28" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H28" s="184" t="n">
+      <x:c r="H28" s="232" t="n">
         <x:f>IF(B28="","",B28-WEEKDAY(B28-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -8229,7 +8722,7 @@
       <x:c r="G29" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H29" s="184" t="n">
+      <x:c r="H29" s="232" t="n">
         <x:f>IF(B29="","",B29-WEEKDAY(B29-2,1)+1)</x:f>
         <x:v>46266</x:v>
       </x:c>
@@ -8271,7 +8764,7 @@
       <x:c r="G30" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H30" s="184" t="n">
+      <x:c r="H30" s="232" t="n">
         <x:f>IF(B30="","",B30-WEEKDAY(B30-2,1)+1)</x:f>
         <x:v>46266</x:v>
       </x:c>
@@ -8313,7 +8806,7 @@
       <x:c r="G31" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H31" s="184" t="n">
+      <x:c r="H31" s="232" t="n">
         <x:f>IF(B31="","",B31-WEEKDAY(B31-2,1)+1)</x:f>
         <x:v>46266</x:v>
       </x:c>
@@ -8355,7 +8848,7 @@
       <x:c r="G32" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H32" s="184" t="n">
+      <x:c r="H32" s="232" t="n">
         <x:f>IF(B32="","",B32-WEEKDAY(B32-2,1)+1)</x:f>
         <x:v>46266</x:v>
       </x:c>
@@ -8397,7 +8890,7 @@
       <x:c r="G33" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H33" s="184" t="n">
+      <x:c r="H33" s="232" t="n">
         <x:f>IF(B33="","",B33-WEEKDAY(B33-2,1)+1)</x:f>
         <x:v>46266</x:v>
       </x:c>
@@ -8439,7 +8932,7 @@
       <x:c r="G34" s="41" t="str">
         <x:v>Exclude</x:v>
       </x:c>
-      <x:c r="H34" s="184" t="n">
+      <x:c r="H34" s="232" t="n">
         <x:f>IF(B34="","",B34-WEEKDAY(B34-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -8481,7 +8974,7 @@
       <x:c r="G35" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H35" s="184" t="n">
+      <x:c r="H35" s="232" t="n">
         <x:f>IF(B35="","",B35-WEEKDAY(B35-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -8523,7 +9016,7 @@
       <x:c r="G36" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H36" s="184" t="n">
+      <x:c r="H36" s="232" t="n">
         <x:f>IF(B36="","",B36-WEEKDAY(B36-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -8565,7 +9058,7 @@
       <x:c r="G37" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H37" s="184" t="n">
+      <x:c r="H37" s="232" t="n">
         <x:f>IF(B37="","",B37-WEEKDAY(B37-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -8607,7 +9100,7 @@
       <x:c r="G38" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H38" s="184" t="n">
+      <x:c r="H38" s="232" t="n">
         <x:f>IF(B38="","",B38-WEEKDAY(B38-2,1)+1)</x:f>
         <x:v>46266</x:v>
       </x:c>
@@ -8649,7 +9142,7 @@
       <x:c r="G39" s="41" t="str">
         <x:v>Exclude</x:v>
       </x:c>
-      <x:c r="H39" s="184" t="n">
+      <x:c r="H39" s="232" t="n">
         <x:f>IF(B39="","",B39-WEEKDAY(B39-2,1)+1)</x:f>
         <x:v>46266</x:v>
       </x:c>
@@ -8691,7 +9184,7 @@
       <x:c r="G40" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H40" s="184" t="n">
+      <x:c r="H40" s="232" t="n">
         <x:f>IF(B40="","",B40-WEEKDAY(B40-2,1)+1)</x:f>
         <x:v>46266</x:v>
       </x:c>
@@ -8733,7 +9226,7 @@
       <x:c r="G41" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H41" s="184" t="n">
+      <x:c r="H41" s="232" t="n">
         <x:f>IF(B41="","",B41-WEEKDAY(B41-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -8775,7 +9268,7 @@
       <x:c r="G42" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H42" s="184" t="n">
+      <x:c r="H42" s="232" t="n">
         <x:f>IF(B42="","",B42-WEEKDAY(B42-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -8817,7 +9310,7 @@
       <x:c r="G43" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H43" s="184" t="n">
+      <x:c r="H43" s="232" t="n">
         <x:f>IF(B43="","",B43-WEEKDAY(B43-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -8859,7 +9352,7 @@
       <x:c r="G44" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H44" s="184" t="n">
+      <x:c r="H44" s="232" t="n">
         <x:f>IF(B44="","",B44-WEEKDAY(B44-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -8901,7 +9394,7 @@
       <x:c r="G45" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H45" s="184" t="n">
+      <x:c r="H45" s="232" t="n">
         <x:f>IF(B45="","",B45-WEEKDAY(B45-2,1)+1)</x:f>
         <x:v>46259</x:v>
       </x:c>
@@ -8943,7 +9436,7 @@
       <x:c r="G46" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H46" s="184" t="n">
+      <x:c r="H46" s="232" t="n">
         <x:f>IF(B46="","",B46-WEEKDAY(B46-2,1)+1)</x:f>
         <x:v>46266</x:v>
       </x:c>
@@ -8985,7 +9478,7 @@
       <x:c r="G47" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H47" s="184" t="n">
+      <x:c r="H47" s="232" t="n">
         <x:f>IF(B47="","",B47-WEEKDAY(B47-2,1)+1)</x:f>
         <x:v>46266</x:v>
       </x:c>
@@ -9027,7 +9520,7 @@
       <x:c r="G48" s="41" t="str">
         <x:v>Exclude</x:v>
       </x:c>
-      <x:c r="H48" s="184" t="n">
+      <x:c r="H48" s="232" t="n">
         <x:f>IF(B48="","",B48-WEEKDAY(B48-2,1)+1)</x:f>
         <x:v>46266</x:v>
       </x:c>
@@ -9069,7 +9562,7 @@
       <x:c r="G49" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H49" s="184" t="n">
+      <x:c r="H49" s="232" t="n">
         <x:f>IF(B49="","",B49-WEEKDAY(B49-2,1)+1)</x:f>
         <x:v>46266</x:v>
       </x:c>
@@ -9111,7 +9604,7 @@
       <x:c r="G50" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H50" s="184" t="n">
+      <x:c r="H50" s="232" t="n">
         <x:f>IF(B50="","",B50-WEEKDAY(B50-2,1)+1)</x:f>
         <x:v>46266</x:v>
       </x:c>
@@ -9153,7 +9646,7 @@
       <x:c r="G51" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H51" s="184" t="n">
+      <x:c r="H51" s="232" t="n">
         <x:f>IF(B51="","",B51-WEEKDAY(B51-2,1)+1)</x:f>
         <x:v>46266</x:v>
       </x:c>
@@ -9195,7 +9688,7 @@
       <x:c r="G52" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H52" s="184" t="n">
+      <x:c r="H52" s="232" t="n">
         <x:f>IF(B52="","",B52-WEEKDAY(B52-2,1)+1)</x:f>
         <x:v>46266</x:v>
       </x:c>
@@ -9237,7 +9730,7 @@
       <x:c r="G53" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H53" s="184" t="n">
+      <x:c r="H53" s="232" t="n">
         <x:f>IF(B53="","",B53-WEEKDAY(B53-2,1)+1)</x:f>
         <x:v>46266</x:v>
       </x:c>
@@ -9279,7 +9772,7 @@
       <x:c r="G54" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H54" s="184" t="n">
+      <x:c r="H54" s="232" t="n">
         <x:f>IF(B54="","",B54-WEEKDAY(B54-2,1)+1)</x:f>
         <x:v>46266</x:v>
       </x:c>
@@ -9321,7 +9814,7 @@
       <x:c r="G55" s="41" t="str">
         <x:v>Exclude</x:v>
       </x:c>
-      <x:c r="H55" s="184" t="n">
+      <x:c r="H55" s="232" t="n">
         <x:f>IF(B55="","",B55-WEEKDAY(B55-2,1)+1)</x:f>
         <x:v>46266</x:v>
       </x:c>
@@ -9363,7 +9856,7 @@
       <x:c r="G56" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H56" s="184" t="n">
+      <x:c r="H56" s="232" t="n">
         <x:f>IF(B56="","",B56-WEEKDAY(B56-2,1)+1)</x:f>
         <x:v>46266</x:v>
       </x:c>
@@ -9405,7 +9898,7 @@
       <x:c r="G57" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H57" s="184" t="n">
+      <x:c r="H57" s="232" t="n">
         <x:f>IF(B57="","",B57-WEEKDAY(B57-2,1)+1)</x:f>
         <x:v>46266</x:v>
       </x:c>
@@ -9447,7 +9940,7 @@
       <x:c r="G58" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H58" s="184" t="n">
+      <x:c r="H58" s="232" t="n">
         <x:f>IF(B58="","",B58-WEEKDAY(B58-2,1)+1)</x:f>
         <x:v>46266</x:v>
       </x:c>
@@ -9489,7 +9982,7 @@
       <x:c r="G59" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H59" s="184" t="n">
+      <x:c r="H59" s="232" t="n">
         <x:f>IF(B59="","",B59-WEEKDAY(B59-2,1)+1)</x:f>
         <x:v>46266</x:v>
       </x:c>
@@ -9531,7 +10024,7 @@
       <x:c r="G60" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H60" s="184" t="n">
+      <x:c r="H60" s="232" t="n">
         <x:f>IF(B60="","",B60-WEEKDAY(B60-2,1)+1)</x:f>
         <x:v>46266</x:v>
       </x:c>
@@ -9573,7 +10066,7 @@
       <x:c r="G61" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H61" s="184" t="n">
+      <x:c r="H61" s="232" t="n">
         <x:f>IF(B61="","",B61-WEEKDAY(B61-2,1)+1)</x:f>
         <x:v>46266</x:v>
       </x:c>
@@ -9615,7 +10108,7 @@
       <x:c r="G62" s="41" t="str">
         <x:v>Exclude</x:v>
       </x:c>
-      <x:c r="H62" s="184" t="n">
+      <x:c r="H62" s="232" t="n">
         <x:f>IF(B62="","",B62-WEEKDAY(B62-2,1)+1)</x:f>
         <x:v>46266</x:v>
       </x:c>
@@ -9657,7 +10150,7 @@
       <x:c r="G63" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H63" s="184" t="n">
+      <x:c r="H63" s="232" t="n">
         <x:f>IF(B63="","",B63-WEEKDAY(B63-2,1)+1)</x:f>
         <x:v>46266</x:v>
       </x:c>
@@ -9699,7 +10192,7 @@
       <x:c r="G64" s="41" t="str">
         <x:v>Exclude</x:v>
       </x:c>
-      <x:c r="H64" s="184" t="n">
+      <x:c r="H64" s="232" t="n">
         <x:f>IF(B64="","",B64-WEEKDAY(B64-2,1)+1)</x:f>
         <x:v>46273</x:v>
       </x:c>
@@ -9741,7 +10234,7 @@
       <x:c r="G65" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H65" s="184" t="n">
+      <x:c r="H65" s="232" t="n">
         <x:f>IF(B65="","",B65-WEEKDAY(B65-2,1)+1)</x:f>
         <x:v>46273</x:v>
       </x:c>
@@ -9783,7 +10276,7 @@
       <x:c r="G66" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H66" s="184" t="n">
+      <x:c r="H66" s="232" t="n">
         <x:f>IF(B66="","",B66-WEEKDAY(B66-2,1)+1)</x:f>
         <x:v>46273</x:v>
       </x:c>
@@ -9825,7 +10318,7 @@
       <x:c r="G67" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H67" s="184" t="n">
+      <x:c r="H67" s="232" t="n">
         <x:f>IF(B67="","",B67-WEEKDAY(B67-2,1)+1)</x:f>
         <x:v>46273</x:v>
       </x:c>
@@ -9867,7 +10360,7 @@
       <x:c r="G68" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H68" s="184" t="n">
+      <x:c r="H68" s="232" t="n">
         <x:f>IF(B68="","",B68-WEEKDAY(B68-2,1)+1)</x:f>
         <x:v>46266</x:v>
       </x:c>
@@ -9909,7 +10402,7 @@
       <x:c r="G69" s="41" t="str">
         <x:v>Include</x:v>
       </x:c>
-      <x:c r="H69" s="184" t="n">
+      <x:c r="H69" s="232" t="n">
         <x:f>IF(B69="","",B69-WEEKDAY(B69-2,1)+1)</x:f>
         <x:v>46273</x:v>
       </x:c>
@@ -9937,7 +10430,7 @@
       <x:c r="E70" s="41"/>
       <x:c r="F70" s="41"/>
       <x:c r="G70" s="41"/>
-      <x:c r="H70" s="184" t="str">
+      <x:c r="H70" s="232" t="str">
         <x:f>IF(B70="","",B70-WEEKDAY(B70-2,1)+1)</x:f>
       </x:c>
       <x:c r="I70" s="41"/>
@@ -9954,7 +10447,7 @@
       <x:c r="E71" s="41"/>
       <x:c r="F71" s="41"/>
       <x:c r="G71" s="41"/>
-      <x:c r="H71" s="184" t="str">
+      <x:c r="H71" s="232" t="str">
         <x:f>IF(B71="","",B71-WEEKDAY(B71-2,1)+1)</x:f>
       </x:c>
       <x:c r="I71" s="41"/>
@@ -9971,7 +10464,7 @@
       <x:c r="E72" s="41"/>
       <x:c r="F72" s="41"/>
       <x:c r="G72" s="41"/>
-      <x:c r="H72" s="184" t="str">
+      <x:c r="H72" s="232" t="str">
         <x:f>IF(B72="","",B72-WEEKDAY(B72-2,1)+1)</x:f>
       </x:c>
       <x:c r="I72" s="41"/>
@@ -9988,7 +10481,7 @@
       <x:c r="E73" s="41"/>
       <x:c r="F73" s="41"/>
       <x:c r="G73" s="41"/>
-      <x:c r="H73" s="184" t="str">
+      <x:c r="H73" s="232" t="str">
         <x:f>IF(B73="","",B73-WEEKDAY(B73-2,1)+1)</x:f>
       </x:c>
       <x:c r="I73" s="41"/>
@@ -10005,7 +10498,7 @@
       <x:c r="E74" s="41"/>
       <x:c r="F74" s="41"/>
       <x:c r="G74" s="41"/>
-      <x:c r="H74" s="184" t="str">
+      <x:c r="H74" s="232" t="str">
         <x:f>IF(B74="","",B74-WEEKDAY(B74-2,1)+1)</x:f>
       </x:c>
       <x:c r="I74" s="41"/>
@@ -10022,7 +10515,7 @@
       <x:c r="E75" s="41"/>
       <x:c r="F75" s="41"/>
       <x:c r="G75" s="41"/>
-      <x:c r="H75" s="184" t="str">
+      <x:c r="H75" s="232" t="str">
         <x:f>IF(B75="","",B75-WEEKDAY(B75-2,1)+1)</x:f>
       </x:c>
       <x:c r="I75" s="41"/>
@@ -10039,7 +10532,7 @@
       <x:c r="E76" s="41"/>
       <x:c r="F76" s="41"/>
       <x:c r="G76" s="41"/>
-      <x:c r="H76" s="184" t="str">
+      <x:c r="H76" s="232" t="str">
         <x:f>IF(B76="","",B76-WEEKDAY(B76-2,1)+1)</x:f>
       </x:c>
       <x:c r="I76" s="41"/>
@@ -10056,7 +10549,7 @@
       <x:c r="E77" s="41"/>
       <x:c r="F77" s="41"/>
       <x:c r="G77" s="41"/>
-      <x:c r="H77" s="184" t="str">
+      <x:c r="H77" s="232" t="str">
         <x:f>IF(B77="","",B77-WEEKDAY(B77-2,1)+1)</x:f>
       </x:c>
       <x:c r="I77" s="41"/>
@@ -10073,7 +10566,7 @@
       <x:c r="E78" s="41"/>
       <x:c r="F78" s="41"/>
       <x:c r="G78" s="41"/>
-      <x:c r="H78" s="184" t="str">
+      <x:c r="H78" s="232" t="str">
         <x:f>IF(B78="","",B78-WEEKDAY(B78-2,1)+1)</x:f>
       </x:c>
       <x:c r="I78" s="41"/>
@@ -10090,7 +10583,7 @@
       <x:c r="E79" s="41"/>
       <x:c r="F79" s="41"/>
       <x:c r="G79" s="41"/>
-      <x:c r="H79" s="184" t="str">
+      <x:c r="H79" s="232" t="str">
         <x:f>IF(B79="","",B79-WEEKDAY(B79-2,1)+1)</x:f>
       </x:c>
       <x:c r="I79" s="41"/>
@@ -10107,7 +10600,7 @@
       <x:c r="E80" s="41"/>
       <x:c r="F80" s="41"/>
       <x:c r="G80" s="41"/>
-      <x:c r="H80" s="184" t="str">
+      <x:c r="H80" s="232" t="str">
         <x:f>IF(B80="","",B80-WEEKDAY(B80-2,1)+1)</x:f>
       </x:c>
       <x:c r="I80" s="41"/>
@@ -10124,7 +10617,7 @@
       <x:c r="E81" s="41"/>
       <x:c r="F81" s="41"/>
       <x:c r="G81" s="41"/>
-      <x:c r="H81" s="184" t="str">
+      <x:c r="H81" s="232" t="str">
         <x:f>IF(B81="","",B81-WEEKDAY(B81-2,1)+1)</x:f>
       </x:c>
       <x:c r="I81" s="41"/>
@@ -10141,7 +10634,7 @@
       <x:c r="E82" s="41"/>
       <x:c r="F82" s="41"/>
       <x:c r="G82" s="41"/>
-      <x:c r="H82" s="184" t="str">
+      <x:c r="H82" s="232" t="str">
         <x:f>IF(B82="","",B82-WEEKDAY(B82-2,1)+1)</x:f>
       </x:c>
       <x:c r="I82" s="41"/>
@@ -10158,7 +10651,7 @@
       <x:c r="E83" s="41"/>
       <x:c r="F83" s="41"/>
       <x:c r="G83" s="41"/>
-      <x:c r="H83" s="184" t="str">
+      <x:c r="H83" s="232" t="str">
         <x:f>IF(B83="","",B83-WEEKDAY(B83-2,1)+1)</x:f>
       </x:c>
       <x:c r="I83" s="41"/>
@@ -10175,7 +10668,7 @@
       <x:c r="E84" s="41"/>
       <x:c r="F84" s="41"/>
       <x:c r="G84" s="41"/>
-      <x:c r="H84" s="184" t="str">
+      <x:c r="H84" s="232" t="str">
         <x:f>IF(B84="","",B84-WEEKDAY(B84-2,1)+1)</x:f>
       </x:c>
       <x:c r="I84" s="41"/>
@@ -10192,7 +10685,7 @@
       <x:c r="E85" s="41"/>
       <x:c r="F85" s="41"/>
       <x:c r="G85" s="41"/>
-      <x:c r="H85" s="184" t="str">
+      <x:c r="H85" s="232" t="str">
         <x:f>IF(B85="","",B85-WEEKDAY(B85-2,1)+1)</x:f>
       </x:c>
       <x:c r="I85" s="41"/>
@@ -10209,7 +10702,7 @@
       <x:c r="E86" s="41"/>
       <x:c r="F86" s="41"/>
       <x:c r="G86" s="41"/>
-      <x:c r="H86" s="184" t="str">
+      <x:c r="H86" s="232" t="str">
         <x:f>IF(B86="","",B86-WEEKDAY(B86-2,1)+1)</x:f>
       </x:c>
       <x:c r="I86" s="41"/>
@@ -10226,7 +10719,7 @@
       <x:c r="E87" s="41"/>
       <x:c r="F87" s="41"/>
       <x:c r="G87" s="41"/>
-      <x:c r="H87" s="184" t="str">
+      <x:c r="H87" s="232" t="str">
         <x:f>IF(B87="","",B87-WEEKDAY(B87-2,1)+1)</x:f>
       </x:c>
       <x:c r="I87" s="41"/>
@@ -10243,7 +10736,7 @@
       <x:c r="E88" s="41"/>
       <x:c r="F88" s="41"/>
       <x:c r="G88" s="41"/>
-      <x:c r="H88" s="184" t="str">
+      <x:c r="H88" s="232" t="str">
         <x:f>IF(B88="","",B88-WEEKDAY(B88-2,1)+1)</x:f>
       </x:c>
       <x:c r="I88" s="41"/>
@@ -10260,7 +10753,7 @@
       <x:c r="E89" s="41"/>
       <x:c r="F89" s="41"/>
       <x:c r="G89" s="41"/>
-      <x:c r="H89" s="184" t="str">
+      <x:c r="H89" s="232" t="str">
         <x:f>IF(B89="","",B89-WEEKDAY(B89-2,1)+1)</x:f>
       </x:c>
       <x:c r="I89" s="41"/>
@@ -10277,7 +10770,7 @@
       <x:c r="E90" s="41"/>
       <x:c r="F90" s="41"/>
       <x:c r="G90" s="41"/>
-      <x:c r="H90" s="184" t="str">
+      <x:c r="H90" s="232" t="str">
         <x:f>IF(B90="","",B90-WEEKDAY(B90-2,1)+1)</x:f>
       </x:c>
       <x:c r="I90" s="41"/>
@@ -10294,7 +10787,7 @@
       <x:c r="E91" s="41"/>
       <x:c r="F91" s="41"/>
       <x:c r="G91" s="41"/>
-      <x:c r="H91" s="184" t="str">
+      <x:c r="H91" s="232" t="str">
         <x:f>IF(B91="","",B91-WEEKDAY(B91-2,1)+1)</x:f>
       </x:c>
       <x:c r="I91" s="41"/>
@@ -10311,7 +10804,7 @@
       <x:c r="E92" s="41"/>
       <x:c r="F92" s="41"/>
       <x:c r="G92" s="41"/>
-      <x:c r="H92" s="184" t="str">
+      <x:c r="H92" s="232" t="str">
         <x:f>IF(B92="","",B92-WEEKDAY(B92-2,1)+1)</x:f>
       </x:c>
       <x:c r="I92" s="41"/>
@@ -10328,7 +10821,7 @@
       <x:c r="E93" s="41"/>
       <x:c r="F93" s="41"/>
       <x:c r="G93" s="41"/>
-      <x:c r="H93" s="184" t="str">
+      <x:c r="H93" s="232" t="str">
         <x:f>IF(B93="","",B93-WEEKDAY(B93-2,1)+1)</x:f>
       </x:c>
       <x:c r="I93" s="41"/>
@@ -10345,7 +10838,7 @@
       <x:c r="E94" s="41"/>
       <x:c r="F94" s="41"/>
       <x:c r="G94" s="41"/>
-      <x:c r="H94" s="184" t="str">
+      <x:c r="H94" s="232" t="str">
         <x:f>IF(B94="","",B94-WEEKDAY(B94-2,1)+1)</x:f>
       </x:c>
       <x:c r="I94" s="41"/>
@@ -10362,7 +10855,7 @@
       <x:c r="E95" s="41"/>
       <x:c r="F95" s="41"/>
       <x:c r="G95" s="41"/>
-      <x:c r="H95" s="184" t="str">
+      <x:c r="H95" s="232" t="str">
         <x:f>IF(B95="","",B95-WEEKDAY(B95-2,1)+1)</x:f>
       </x:c>
       <x:c r="I95" s="41"/>
@@ -10379,7 +10872,7 @@
       <x:c r="E96" s="41"/>
       <x:c r="F96" s="41"/>
       <x:c r="G96" s="41"/>
-      <x:c r="H96" s="184" t="str">
+      <x:c r="H96" s="232" t="str">
         <x:f>IF(B96="","",B96-WEEKDAY(B96-2,1)+1)</x:f>
       </x:c>
       <x:c r="I96" s="41"/>
@@ -10396,7 +10889,7 @@
       <x:c r="E97" s="41"/>
       <x:c r="F97" s="41"/>
       <x:c r="G97" s="41"/>
-      <x:c r="H97" s="184" t="str">
+      <x:c r="H97" s="232" t="str">
         <x:f>IF(B97="","",B97-WEEKDAY(B97-2,1)+1)</x:f>
       </x:c>
       <x:c r="I97" s="41"/>
@@ -10413,7 +10906,7 @@
       <x:c r="E98" s="41"/>
       <x:c r="F98" s="41"/>
       <x:c r="G98" s="41"/>
-      <x:c r="H98" s="184" t="str">
+      <x:c r="H98" s="232" t="str">
         <x:f>IF(B98="","",B98-WEEKDAY(B98-2,1)+1)</x:f>
       </x:c>
       <x:c r="I98" s="41"/>
@@ -10430,7 +10923,7 @@
       <x:c r="E99" s="41"/>
       <x:c r="F99" s="41"/>
       <x:c r="G99" s="41"/>
-      <x:c r="H99" s="184" t="str">
+      <x:c r="H99" s="232" t="str">
         <x:f>IF(B99="","",B99-WEEKDAY(B99-2,1)+1)</x:f>
       </x:c>
       <x:c r="I99" s="41"/>
@@ -10447,7 +10940,7 @@
       <x:c r="E100" s="41"/>
       <x:c r="F100" s="41"/>
       <x:c r="G100" s="41"/>
-      <x:c r="H100" s="184" t="str">
+      <x:c r="H100" s="232" t="str">
         <x:f>IF(B100="","",B100-WEEKDAY(B100-2,1)+1)</x:f>
       </x:c>
       <x:c r="I100" s="41"/>
@@ -10464,7 +10957,7 @@
       <x:c r="E101" s="41"/>
       <x:c r="F101" s="41"/>
       <x:c r="G101" s="41"/>
-      <x:c r="H101" s="184" t="str">
+      <x:c r="H101" s="232" t="str">
         <x:f>IF(B101="","",B101-WEEKDAY(B101-2,1)+1)</x:f>
       </x:c>
       <x:c r="I101" s="41"/>
@@ -10481,7 +10974,7 @@
       <x:c r="E102" s="41"/>
       <x:c r="F102" s="41"/>
       <x:c r="G102" s="41"/>
-      <x:c r="H102" s="184" t="str">
+      <x:c r="H102" s="232" t="str">
         <x:f>IF(B102="","",B102-WEEKDAY(B102-2,1)+1)</x:f>
       </x:c>
       <x:c r="I102" s="41"/>
@@ -10498,7 +10991,7 @@
       <x:c r="E103" s="41"/>
       <x:c r="F103" s="41"/>
       <x:c r="G103" s="41"/>
-      <x:c r="H103" s="184" t="str">
+      <x:c r="H103" s="232" t="str">
         <x:f>IF(B103="","",B103-WEEKDAY(B103-2,1)+1)</x:f>
       </x:c>
       <x:c r="I103" s="41"/>
@@ -10515,7 +11008,7 @@
       <x:c r="E104" s="41"/>
       <x:c r="F104" s="41"/>
       <x:c r="G104" s="41"/>
-      <x:c r="H104" s="184" t="str">
+      <x:c r="H104" s="232" t="str">
         <x:f>IF(B104="","",B104-WEEKDAY(B104-2,1)+1)</x:f>
       </x:c>
       <x:c r="I104" s="41"/>
@@ -10532,7 +11025,7 @@
       <x:c r="E105" s="41"/>
       <x:c r="F105" s="41"/>
       <x:c r="G105" s="41"/>
-      <x:c r="H105" s="184" t="str">
+      <x:c r="H105" s="232" t="str">
         <x:f>IF(B105="","",B105-WEEKDAY(B105-2,1)+1)</x:f>
       </x:c>
       <x:c r="I105" s="41"/>
@@ -10549,7 +11042,7 @@
       <x:c r="E106" s="41"/>
       <x:c r="F106" s="41"/>
       <x:c r="G106" s="41"/>
-      <x:c r="H106" s="184" t="str">
+      <x:c r="H106" s="232" t="str">
         <x:f>IF(B106="","",B106-WEEKDAY(B106-2,1)+1)</x:f>
       </x:c>
       <x:c r="I106" s="41"/>
@@ -10566,7 +11059,7 @@
       <x:c r="E107" s="41"/>
       <x:c r="F107" s="41"/>
       <x:c r="G107" s="41"/>
-      <x:c r="H107" s="184" t="str">
+      <x:c r="H107" s="232" t="str">
         <x:f>IF(B107="","",B107-WEEKDAY(B107-2,1)+1)</x:f>
       </x:c>
       <x:c r="I107" s="41"/>
@@ -10583,7 +11076,7 @@
       <x:c r="E108" s="41"/>
       <x:c r="F108" s="41"/>
       <x:c r="G108" s="41"/>
-      <x:c r="H108" s="184" t="str">
+      <x:c r="H108" s="232" t="str">
         <x:f>IF(B108="","",B108-WEEKDAY(B108-2,1)+1)</x:f>
       </x:c>
       <x:c r="I108" s="41"/>
@@ -10600,7 +11093,7 @@
       <x:c r="E109" s="41"/>
       <x:c r="F109" s="41"/>
       <x:c r="G109" s="41"/>
-      <x:c r="H109" s="184" t="str">
+      <x:c r="H109" s="232" t="str">
         <x:f>IF(B109="","",B109-WEEKDAY(B109-2,1)+1)</x:f>
       </x:c>
       <x:c r="I109" s="41"/>
@@ -10617,7 +11110,7 @@
       <x:c r="E110" s="41"/>
       <x:c r="F110" s="41"/>
       <x:c r="G110" s="41"/>
-      <x:c r="H110" s="184" t="str">
+      <x:c r="H110" s="232" t="str">
         <x:f>IF(B110="","",B110-WEEKDAY(B110-2,1)+1)</x:f>
       </x:c>
       <x:c r="I110" s="41"/>
@@ -10634,7 +11127,7 @@
       <x:c r="E111" s="41"/>
       <x:c r="F111" s="41"/>
       <x:c r="G111" s="41"/>
-      <x:c r="H111" s="184" t="str">
+      <x:c r="H111" s="232" t="str">
         <x:f>IF(B111="","",B111-WEEKDAY(B111-2,1)+1)</x:f>
       </x:c>
       <x:c r="I111" s="41"/>
@@ -10651,7 +11144,7 @@
       <x:c r="E112" s="41"/>
       <x:c r="F112" s="41"/>
       <x:c r="G112" s="41"/>
-      <x:c r="H112" s="184" t="str">
+      <x:c r="H112" s="232" t="str">
         <x:f>IF(B112="","",B112-WEEKDAY(B112-2,1)+1)</x:f>
       </x:c>
       <x:c r="I112" s="41"/>
@@ -10668,7 +11161,7 @@
       <x:c r="E113" s="41"/>
       <x:c r="F113" s="41"/>
       <x:c r="G113" s="41"/>
-      <x:c r="H113" s="184" t="str">
+      <x:c r="H113" s="232" t="str">
         <x:f>IF(B113="","",B113-WEEKDAY(B113-2,1)+1)</x:f>
       </x:c>
       <x:c r="I113" s="41"/>
@@ -10685,7 +11178,7 @@
       <x:c r="E114" s="41"/>
       <x:c r="F114" s="41"/>
       <x:c r="G114" s="41"/>
-      <x:c r="H114" s="184" t="str">
+      <x:c r="H114" s="232" t="str">
         <x:f>IF(B114="","",B114-WEEKDAY(B114-2,1)+1)</x:f>
       </x:c>
       <x:c r="I114" s="41"/>
@@ -10702,7 +11195,7 @@
       <x:c r="E115" s="41"/>
       <x:c r="F115" s="41"/>
       <x:c r="G115" s="41"/>
-      <x:c r="H115" s="184" t="str">
+      <x:c r="H115" s="232" t="str">
         <x:f>IF(B115="","",B115-WEEKDAY(B115-2,1)+1)</x:f>
       </x:c>
       <x:c r="I115" s="41"/>
@@ -10719,7 +11212,7 @@
       <x:c r="E116" s="41"/>
       <x:c r="F116" s="41"/>
       <x:c r="G116" s="41"/>
-      <x:c r="H116" s="184" t="str">
+      <x:c r="H116" s="232" t="str">
         <x:f>IF(B116="","",B116-WEEKDAY(B116-2,1)+1)</x:f>
       </x:c>
       <x:c r="I116" s="41"/>
@@ -10736,7 +11229,7 @@
       <x:c r="E117" s="41"/>
       <x:c r="F117" s="41"/>
       <x:c r="G117" s="41"/>
-      <x:c r="H117" s="184" t="str">
+      <x:c r="H117" s="232" t="str">
         <x:f>IF(B117="","",B117-WEEKDAY(B117-2,1)+1)</x:f>
       </x:c>
       <x:c r="I117" s="41"/>
@@ -10753,7 +11246,7 @@
       <x:c r="E118" s="41"/>
       <x:c r="F118" s="41"/>
       <x:c r="G118" s="41"/>
-      <x:c r="H118" s="184" t="str">
+      <x:c r="H118" s="232" t="str">
         <x:f>IF(B118="","",B118-WEEKDAY(B118-2,1)+1)</x:f>
       </x:c>
       <x:c r="I118" s="41"/>
@@ -10770,7 +11263,7 @@
       <x:c r="E119" s="41"/>
       <x:c r="F119" s="41"/>
       <x:c r="G119" s="41"/>
-      <x:c r="H119" s="184" t="str">
+      <x:c r="H119" s="232" t="str">
         <x:f>IF(B119="","",B119-WEEKDAY(B119-2,1)+1)</x:f>
       </x:c>
       <x:c r="I119" s="41"/>
@@ -10787,7 +11280,7 @@
       <x:c r="E120" s="41"/>
       <x:c r="F120" s="41"/>
       <x:c r="G120" s="41"/>
-      <x:c r="H120" s="184" t="str">
+      <x:c r="H120" s="232" t="str">
         <x:f>IF(B120="","",B120-WEEKDAY(B120-2,1)+1)</x:f>
       </x:c>
       <x:c r="I120" s="41"/>
@@ -10804,7 +11297,7 @@
       <x:c r="E121" s="41"/>
       <x:c r="F121" s="41"/>
       <x:c r="G121" s="41"/>
-      <x:c r="H121" s="184" t="str">
+      <x:c r="H121" s="232" t="str">
         <x:f>IF(B121="","",B121-WEEKDAY(B121-2,1)+1)</x:f>
       </x:c>
       <x:c r="I121" s="41"/>
@@ -10821,7 +11314,7 @@
       <x:c r="E122" s="41"/>
       <x:c r="F122" s="41"/>
       <x:c r="G122" s="41"/>
-      <x:c r="H122" s="184" t="str">
+      <x:c r="H122" s="232" t="str">
         <x:f>IF(B122="","",B122-WEEKDAY(B122-2,1)+1)</x:f>
       </x:c>
       <x:c r="I122" s="41"/>
@@ -10838,7 +11331,7 @@
       <x:c r="E123" s="41"/>
       <x:c r="F123" s="41"/>
       <x:c r="G123" s="41"/>
-      <x:c r="H123" s="184" t="str">
+      <x:c r="H123" s="232" t="str">
         <x:f>IF(B123="","",B123-WEEKDAY(B123-2,1)+1)</x:f>
       </x:c>
       <x:c r="I123" s="41"/>
@@ -10855,7 +11348,7 @@
       <x:c r="E124" s="41"/>
       <x:c r="F124" s="41"/>
       <x:c r="G124" s="41"/>
-      <x:c r="H124" s="184" t="str">
+      <x:c r="H124" s="232" t="str">
         <x:f>IF(B124="","",B124-WEEKDAY(B124-2,1)+1)</x:f>
       </x:c>
       <x:c r="I124" s="41"/>
@@ -10872,7 +11365,7 @@
       <x:c r="E125" s="41"/>
       <x:c r="F125" s="41"/>
       <x:c r="G125" s="41"/>
-      <x:c r="H125" s="184" t="str">
+      <x:c r="H125" s="232" t="str">
         <x:f>IF(B125="","",B125-WEEKDAY(B125-2,1)+1)</x:f>
       </x:c>
       <x:c r="I125" s="41"/>
@@ -10889,7 +11382,7 @@
       <x:c r="E126" s="41"/>
       <x:c r="F126" s="41"/>
       <x:c r="G126" s="41"/>
-      <x:c r="H126" s="184" t="str">
+      <x:c r="H126" s="232" t="str">
         <x:f>IF(B126="","",B126-WEEKDAY(B126-2,1)+1)</x:f>
       </x:c>
       <x:c r="I126" s="41"/>
@@ -10906,7 +11399,7 @@
       <x:c r="E127" s="41"/>
       <x:c r="F127" s="41"/>
       <x:c r="G127" s="41"/>
-      <x:c r="H127" s="184" t="str">
+      <x:c r="H127" s="232" t="str">
         <x:f>IF(B127="","",B127-WEEKDAY(B127-2,1)+1)</x:f>
       </x:c>
       <x:c r="I127" s="41"/>
@@ -10923,7 +11416,7 @@
       <x:c r="E128" s="41"/>
       <x:c r="F128" s="41"/>
       <x:c r="G128" s="41"/>
-      <x:c r="H128" s="184" t="str">
+      <x:c r="H128" s="232" t="str">
         <x:f>IF(B128="","",B128-WEEKDAY(B128-2,1)+1)</x:f>
       </x:c>
       <x:c r="I128" s="41"/>
@@ -10940,7 +11433,7 @@
       <x:c r="E129" s="41"/>
       <x:c r="F129" s="41"/>
       <x:c r="G129" s="41"/>
-      <x:c r="H129" s="184" t="str">
+      <x:c r="H129" s="232" t="str">
         <x:f>IF(B129="","",B129-WEEKDAY(B129-2,1)+1)</x:f>
       </x:c>
       <x:c r="I129" s="41"/>
@@ -10957,7 +11450,7 @@
       <x:c r="E130" s="41"/>
       <x:c r="F130" s="41"/>
       <x:c r="G130" s="41"/>
-      <x:c r="H130" s="184" t="str">
+      <x:c r="H130" s="232" t="str">
         <x:f>IF(B130="","",B130-WEEKDAY(B130-2,1)+1)</x:f>
       </x:c>
       <x:c r="I130" s="41"/>
@@ -10974,7 +11467,7 @@
       <x:c r="E131" s="41"/>
       <x:c r="F131" s="41"/>
       <x:c r="G131" s="41"/>
-      <x:c r="H131" s="184" t="str">
+      <x:c r="H131" s="232" t="str">
         <x:f>IF(B131="","",B131-WEEKDAY(B131-2,1)+1)</x:f>
       </x:c>
       <x:c r="I131" s="41"/>
@@ -10991,7 +11484,7 @@
       <x:c r="E132" s="41"/>
       <x:c r="F132" s="41"/>
       <x:c r="G132" s="41"/>
-      <x:c r="H132" s="184" t="str">
+      <x:c r="H132" s="232" t="str">
         <x:f>IF(B132="","",B132-WEEKDAY(B132-2,1)+1)</x:f>
       </x:c>
       <x:c r="I132" s="41"/>
@@ -11008,7 +11501,7 @@
       <x:c r="E133" s="41"/>
       <x:c r="F133" s="41"/>
       <x:c r="G133" s="41"/>
-      <x:c r="H133" s="184" t="str">
+      <x:c r="H133" s="232" t="str">
         <x:f>IF(B133="","",B133-WEEKDAY(B133-2,1)+1)</x:f>
       </x:c>
       <x:c r="I133" s="41"/>
@@ -11025,7 +11518,7 @@
       <x:c r="E134" s="41"/>
       <x:c r="F134" s="41"/>
       <x:c r="G134" s="41"/>
-      <x:c r="H134" s="184" t="str">
+      <x:c r="H134" s="232" t="str">
         <x:f>IF(B134="","",B134-WEEKDAY(B134-2,1)+1)</x:f>
       </x:c>
       <x:c r="I134" s="41"/>
@@ -11042,7 +11535,7 @@
       <x:c r="E135" s="41"/>
       <x:c r="F135" s="41"/>
       <x:c r="G135" s="41"/>
-      <x:c r="H135" s="184" t="str">
+      <x:c r="H135" s="232" t="str">
         <x:f>IF(B135="","",B135-WEEKDAY(B135-2,1)+1)</x:f>
       </x:c>
       <x:c r="I135" s="41"/>
@@ -11059,7 +11552,7 @@
       <x:c r="E136" s="41"/>
       <x:c r="F136" s="41"/>
       <x:c r="G136" s="41"/>
-      <x:c r="H136" s="184" t="str">
+      <x:c r="H136" s="232" t="str">
         <x:f>IF(B136="","",B136-WEEKDAY(B136-2,1)+1)</x:f>
       </x:c>
       <x:c r="I136" s="41"/>
@@ -11076,7 +11569,7 @@
       <x:c r="E137" s="41"/>
       <x:c r="F137" s="41"/>
       <x:c r="G137" s="41"/>
-      <x:c r="H137" s="184" t="str">
+      <x:c r="H137" s="232" t="str">
         <x:f>IF(B137="","",B137-WEEKDAY(B137-2,1)+1)</x:f>
       </x:c>
       <x:c r="I137" s="41"/>
@@ -11093,7 +11586,7 @@
       <x:c r="E138" s="41"/>
       <x:c r="F138" s="41"/>
       <x:c r="G138" s="41"/>
-      <x:c r="H138" s="184" t="str">
+      <x:c r="H138" s="232" t="str">
         <x:f>IF(B138="","",B138-WEEKDAY(B138-2,1)+1)</x:f>
       </x:c>
       <x:c r="I138" s="41"/>
@@ -11110,7 +11603,7 @@
       <x:c r="E139" s="41"/>
       <x:c r="F139" s="41"/>
       <x:c r="G139" s="41"/>
-      <x:c r="H139" s="184" t="str">
+      <x:c r="H139" s="232" t="str">
         <x:f>IF(B139="","",B139-WEEKDAY(B139-2,1)+1)</x:f>
       </x:c>
       <x:c r="I139" s="41"/>
@@ -11127,7 +11620,7 @@
       <x:c r="E140" s="41"/>
       <x:c r="F140" s="41"/>
       <x:c r="G140" s="41"/>
-      <x:c r="H140" s="184" t="str">
+      <x:c r="H140" s="232" t="str">
         <x:f>IF(B140="","",B140-WEEKDAY(B140-2,1)+1)</x:f>
       </x:c>
       <x:c r="I140" s="41"/>
@@ -11144,7 +11637,7 @@
       <x:c r="E141" s="41"/>
       <x:c r="F141" s="41"/>
       <x:c r="G141" s="41"/>
-      <x:c r="H141" s="184" t="str">
+      <x:c r="H141" s="232" t="str">
         <x:f>IF(B141="","",B141-WEEKDAY(B141-2,1)+1)</x:f>
       </x:c>
       <x:c r="I141" s="41"/>
@@ -11161,7 +11654,7 @@
       <x:c r="E142" s="41"/>
       <x:c r="F142" s="41"/>
       <x:c r="G142" s="41"/>
-      <x:c r="H142" s="184" t="str">
+      <x:c r="H142" s="232" t="str">
         <x:f>IF(B142="","",B142-WEEKDAY(B142-2,1)+1)</x:f>
       </x:c>
       <x:c r="I142" s="41"/>
@@ -11178,7 +11671,7 @@
       <x:c r="E143" s="41"/>
       <x:c r="F143" s="41"/>
       <x:c r="G143" s="41"/>
-      <x:c r="H143" s="184" t="str">
+      <x:c r="H143" s="232" t="str">
         <x:f>IF(B143="","",B143-WEEKDAY(B143-2,1)+1)</x:f>
       </x:c>
       <x:c r="I143" s="41"/>
@@ -11195,7 +11688,7 @@
       <x:c r="E144" s="41"/>
       <x:c r="F144" s="41"/>
       <x:c r="G144" s="41"/>
-      <x:c r="H144" s="184" t="str">
+      <x:c r="H144" s="232" t="str">
         <x:f>IF(B144="","",B144-WEEKDAY(B144-2,1)+1)</x:f>
       </x:c>
       <x:c r="I144" s="41"/>
@@ -11212,7 +11705,7 @@
       <x:c r="E145" s="41"/>
       <x:c r="F145" s="41"/>
       <x:c r="G145" s="41"/>
-      <x:c r="H145" s="184" t="str">
+      <x:c r="H145" s="232" t="str">
         <x:f>IF(B145="","",B145-WEEKDAY(B145-2,1)+1)</x:f>
       </x:c>
       <x:c r="I145" s="41"/>
@@ -11229,7 +11722,7 @@
       <x:c r="E146" s="41"/>
       <x:c r="F146" s="41"/>
       <x:c r="G146" s="41"/>
-      <x:c r="H146" s="184" t="str">
+      <x:c r="H146" s="232" t="str">
         <x:f>IF(B146="","",B146-WEEKDAY(B146-2,1)+1)</x:f>
       </x:c>
       <x:c r="I146" s="41"/>
@@ -11246,7 +11739,7 @@
       <x:c r="E147" s="41"/>
       <x:c r="F147" s="41"/>
       <x:c r="G147" s="41"/>
-      <x:c r="H147" s="184" t="str">
+      <x:c r="H147" s="232" t="str">
         <x:f>IF(B147="","",B147-WEEKDAY(B147-2,1)+1)</x:f>
       </x:c>
       <x:c r="I147" s="41"/>
@@ -11263,7 +11756,7 @@
       <x:c r="E148" s="41"/>
       <x:c r="F148" s="41"/>
       <x:c r="G148" s="41"/>
-      <x:c r="H148" s="184" t="str">
+      <x:c r="H148" s="232" t="str">
         <x:f>IF(B148="","",B148-WEEKDAY(B148-2,1)+1)</x:f>
       </x:c>
       <x:c r="I148" s="41"/>
@@ -11280,7 +11773,7 @@
       <x:c r="E149" s="41"/>
       <x:c r="F149" s="41"/>
       <x:c r="G149" s="41"/>
-      <x:c r="H149" s="184" t="str">
+      <x:c r="H149" s="232" t="str">
         <x:f>IF(B149="","",B149-WEEKDAY(B149-2,1)+1)</x:f>
       </x:c>
       <x:c r="I149" s="41"/>
@@ -11297,7 +11790,7 @@
       <x:c r="E150" s="41"/>
       <x:c r="F150" s="41"/>
       <x:c r="G150" s="41"/>
-      <x:c r="H150" s="184" t="str">
+      <x:c r="H150" s="232" t="str">
         <x:f>IF(B150="","",B150-WEEKDAY(B150-2,1)+1)</x:f>
       </x:c>
       <x:c r="I150" s="41"/>
@@ -11314,7 +11807,7 @@
       <x:c r="E151" s="41"/>
       <x:c r="F151" s="41"/>
       <x:c r="G151" s="41"/>
-      <x:c r="H151" s="184" t="str">
+      <x:c r="H151" s="232" t="str">
         <x:f>IF(B151="","",B151-WEEKDAY(B151-2,1)+1)</x:f>
       </x:c>
       <x:c r="I151" s="41"/>
@@ -11331,7 +11824,7 @@
       <x:c r="E152" s="41"/>
       <x:c r="F152" s="41"/>
       <x:c r="G152" s="41"/>
-      <x:c r="H152" s="184" t="str">
+      <x:c r="H152" s="232" t="str">
         <x:f>IF(B152="","",B152-WEEKDAY(B152-2,1)+1)</x:f>
       </x:c>
       <x:c r="I152" s="41"/>
@@ -11348,7 +11841,7 @@
       <x:c r="E153" s="41"/>
       <x:c r="F153" s="41"/>
       <x:c r="G153" s="41"/>
-      <x:c r="H153" s="184" t="str">
+      <x:c r="H153" s="232" t="str">
         <x:f>IF(B153="","",B153-WEEKDAY(B153-2,1)+1)</x:f>
       </x:c>
       <x:c r="I153" s="41"/>
@@ -11365,7 +11858,7 @@
       <x:c r="E154" s="41"/>
       <x:c r="F154" s="41"/>
       <x:c r="G154" s="41"/>
-      <x:c r="H154" s="184" t="str">
+      <x:c r="H154" s="232" t="str">
         <x:f>IF(B154="","",B154-WEEKDAY(B154-2,1)+1)</x:f>
       </x:c>
       <x:c r="I154" s="41"/>
@@ -11382,7 +11875,7 @@
       <x:c r="E155" s="41"/>
       <x:c r="F155" s="41"/>
       <x:c r="G155" s="41"/>
-      <x:c r="H155" s="184" t="str">
+      <x:c r="H155" s="232" t="str">
         <x:f>IF(B155="","",B155-WEEKDAY(B155-2,1)+1)</x:f>
       </x:c>
       <x:c r="I155" s="41"/>
@@ -11399,7 +11892,7 @@
       <x:c r="E156" s="41"/>
       <x:c r="F156" s="41"/>
       <x:c r="G156" s="41"/>
-      <x:c r="H156" s="184" t="str">
+      <x:c r="H156" s="232" t="str">
         <x:f>IF(B156="","",B156-WEEKDAY(B156-2,1)+1)</x:f>
       </x:c>
       <x:c r="I156" s="41"/>
@@ -11416,7 +11909,7 @@
       <x:c r="E157" s="41"/>
       <x:c r="F157" s="41"/>
       <x:c r="G157" s="41"/>
-      <x:c r="H157" s="184" t="str">
+      <x:c r="H157" s="232" t="str">
         <x:f>IF(B157="","",B157-WEEKDAY(B157-2,1)+1)</x:f>
       </x:c>
       <x:c r="I157" s="41"/>
@@ -11433,7 +11926,7 @@
       <x:c r="E158" s="41"/>
       <x:c r="F158" s="41"/>
       <x:c r="G158" s="41"/>
-      <x:c r="H158" s="184" t="str">
+      <x:c r="H158" s="232" t="str">
         <x:f>IF(B158="","",B158-WEEKDAY(B158-2,1)+1)</x:f>
       </x:c>
       <x:c r="I158" s="41"/>
@@ -11450,7 +11943,7 @@
       <x:c r="E159" s="41"/>
       <x:c r="F159" s="41"/>
       <x:c r="G159" s="41"/>
-      <x:c r="H159" s="184" t="str">
+      <x:c r="H159" s="232" t="str">
         <x:f>IF(B159="","",B159-WEEKDAY(B159-2,1)+1)</x:f>
       </x:c>
       <x:c r="I159" s="41"/>
@@ -11467,7 +11960,7 @@
       <x:c r="E160" s="41"/>
       <x:c r="F160" s="41"/>
       <x:c r="G160" s="41"/>
-      <x:c r="H160" s="184" t="str">
+      <x:c r="H160" s="232" t="str">
         <x:f>IF(B160="","",B160-WEEKDAY(B160-2,1)+1)</x:f>
       </x:c>
       <x:c r="I160" s="41"/>
@@ -11484,7 +11977,7 @@
       <x:c r="E161" s="41"/>
       <x:c r="F161" s="41"/>
       <x:c r="G161" s="41"/>
-      <x:c r="H161" s="184" t="str">
+      <x:c r="H161" s="232" t="str">
         <x:f>IF(B161="","",B161-WEEKDAY(B161-2,1)+1)</x:f>
       </x:c>
       <x:c r="I161" s="41"/>
@@ -11501,7 +11994,7 @@
       <x:c r="E162" s="41"/>
       <x:c r="F162" s="41"/>
       <x:c r="G162" s="41"/>
-      <x:c r="H162" s="184" t="str">
+      <x:c r="H162" s="232" t="str">
         <x:f>IF(B162="","",B162-WEEKDAY(B162-2,1)+1)</x:f>
       </x:c>
       <x:c r="I162" s="41"/>
@@ -11518,7 +12011,7 @@
       <x:c r="E163" s="41"/>
       <x:c r="F163" s="41"/>
       <x:c r="G163" s="41"/>
-      <x:c r="H163" s="184" t="str">
+      <x:c r="H163" s="232" t="str">
         <x:f>IF(B163="","",B163-WEEKDAY(B163-2,1)+1)</x:f>
       </x:c>
       <x:c r="I163" s="41"/>
@@ -11535,7 +12028,7 @@
       <x:c r="E164" s="41"/>
       <x:c r="F164" s="41"/>
       <x:c r="G164" s="41"/>
-      <x:c r="H164" s="184" t="str">
+      <x:c r="H164" s="232" t="str">
         <x:f>IF(B164="","",B164-WEEKDAY(B164-2,1)+1)</x:f>
       </x:c>
       <x:c r="I164" s="41"/>
@@ -11552,7 +12045,7 @@
       <x:c r="E165" s="41"/>
       <x:c r="F165" s="41"/>
       <x:c r="G165" s="41"/>
-      <x:c r="H165" s="184" t="str">
+      <x:c r="H165" s="232" t="str">
         <x:f>IF(B165="","",B165-WEEKDAY(B165-2,1)+1)</x:f>
       </x:c>
       <x:c r="I165" s="41"/>
@@ -11569,7 +12062,7 @@
       <x:c r="E166" s="41"/>
       <x:c r="F166" s="41"/>
       <x:c r="G166" s="41"/>
-      <x:c r="H166" s="184" t="str">
+      <x:c r="H166" s="232" t="str">
         <x:f>IF(B166="","",B166-WEEKDAY(B166-2,1)+1)</x:f>
       </x:c>
       <x:c r="I166" s="41"/>
@@ -11586,7 +12079,7 @@
       <x:c r="E167" s="41"/>
       <x:c r="F167" s="41"/>
       <x:c r="G167" s="41"/>
-      <x:c r="H167" s="184" t="str">
+      <x:c r="H167" s="232" t="str">
         <x:f>IF(B167="","",B167-WEEKDAY(B167-2,1)+1)</x:f>
       </x:c>
       <x:c r="I167" s="41"/>
@@ -11603,7 +12096,7 @@
       <x:c r="E168" s="41"/>
       <x:c r="F168" s="41"/>
       <x:c r="G168" s="41"/>
-      <x:c r="H168" s="184" t="str">
+      <x:c r="H168" s="232" t="str">
         <x:f>IF(B168="","",B168-WEEKDAY(B168-2,1)+1)</x:f>
       </x:c>
       <x:c r="I168" s="41"/>
@@ -11620,7 +12113,7 @@
       <x:c r="E169" s="41"/>
       <x:c r="F169" s="41"/>
       <x:c r="G169" s="41"/>
-      <x:c r="H169" s="184" t="str">
+      <x:c r="H169" s="232" t="str">
         <x:f>IF(B169="","",B169-WEEKDAY(B169-2,1)+1)</x:f>
       </x:c>
       <x:c r="I169" s="41"/>
@@ -11637,7 +12130,7 @@
       <x:c r="E170" s="41"/>
       <x:c r="F170" s="41"/>
       <x:c r="G170" s="41"/>
-      <x:c r="H170" s="184" t="str">
+      <x:c r="H170" s="232" t="str">
         <x:f>IF(B170="","",B170-WEEKDAY(B170-2,1)+1)</x:f>
       </x:c>
       <x:c r="I170" s="41"/>
@@ -11654,7 +12147,7 @@
       <x:c r="E171" s="41"/>
       <x:c r="F171" s="41"/>
       <x:c r="G171" s="41"/>
-      <x:c r="H171" s="184" t="str">
+      <x:c r="H171" s="232" t="str">
         <x:f>IF(B171="","",B171-WEEKDAY(B171-2,1)+1)</x:f>
       </x:c>
       <x:c r="I171" s="41"/>
@@ -11671,7 +12164,7 @@
       <x:c r="E172" s="41"/>
       <x:c r="F172" s="41"/>
       <x:c r="G172" s="41"/>
-      <x:c r="H172" s="184" t="str">
+      <x:c r="H172" s="232" t="str">
         <x:f>IF(B172="","",B172-WEEKDAY(B172-2,1)+1)</x:f>
       </x:c>
       <x:c r="I172" s="41"/>
@@ -11688,7 +12181,7 @@
       <x:c r="E173" s="41"/>
       <x:c r="F173" s="41"/>
       <x:c r="G173" s="41"/>
-      <x:c r="H173" s="184" t="str">
+      <x:c r="H173" s="232" t="str">
         <x:f>IF(B173="","",B173-WEEKDAY(B173-2,1)+1)</x:f>
       </x:c>
       <x:c r="I173" s="41"/>
@@ -11705,7 +12198,7 @@
       <x:c r="E174" s="41"/>
       <x:c r="F174" s="41"/>
       <x:c r="G174" s="41"/>
-      <x:c r="H174" s="184" t="str">
+      <x:c r="H174" s="232" t="str">
         <x:f>IF(B174="","",B174-WEEKDAY(B174-2,1)+1)</x:f>
       </x:c>
       <x:c r="I174" s="41"/>
@@ -11722,7 +12215,7 @@
       <x:c r="E175" s="41"/>
       <x:c r="F175" s="41"/>
       <x:c r="G175" s="41"/>
-      <x:c r="H175" s="184" t="str">
+      <x:c r="H175" s="232" t="str">
         <x:f>IF(B175="","",B175-WEEKDAY(B175-2,1)+1)</x:f>
       </x:c>
       <x:c r="I175" s="41"/>
@@ -11739,7 +12232,7 @@
       <x:c r="E176" s="41"/>
       <x:c r="F176" s="41"/>
       <x:c r="G176" s="41"/>
-      <x:c r="H176" s="184" t="str">
+      <x:c r="H176" s="232" t="str">
         <x:f>IF(B176="","",B176-WEEKDAY(B176-2,1)+1)</x:f>
       </x:c>
       <x:c r="I176" s="41"/>
@@ -11756,7 +12249,7 @@
       <x:c r="E177" s="41"/>
       <x:c r="F177" s="41"/>
       <x:c r="G177" s="41"/>
-      <x:c r="H177" s="184" t="str">
+      <x:c r="H177" s="232" t="str">
         <x:f>IF(B177="","",B177-WEEKDAY(B177-2,1)+1)</x:f>
       </x:c>
       <x:c r="I177" s="41"/>
@@ -11773,7 +12266,7 @@
       <x:c r="E178" s="41"/>
       <x:c r="F178" s="41"/>
       <x:c r="G178" s="41"/>
-      <x:c r="H178" s="184" t="str">
+      <x:c r="H178" s="232" t="str">
         <x:f>IF(B178="","",B178-WEEKDAY(B178-2,1)+1)</x:f>
       </x:c>
       <x:c r="I178" s="41"/>
@@ -11790,7 +12283,7 @@
       <x:c r="E179" s="41"/>
       <x:c r="F179" s="41"/>
       <x:c r="G179" s="41"/>
-      <x:c r="H179" s="184" t="str">
+      <x:c r="H179" s="232" t="str">
         <x:f>IF(B179="","",B179-WEEKDAY(B179-2,1)+1)</x:f>
       </x:c>
       <x:c r="I179" s="41"/>
@@ -11807,7 +12300,7 @@
       <x:c r="E180" s="41"/>
       <x:c r="F180" s="41"/>
       <x:c r="G180" s="41"/>
-      <x:c r="H180" s="184" t="str">
+      <x:c r="H180" s="232" t="str">
         <x:f>IF(B180="","",B180-WEEKDAY(B180-2,1)+1)</x:f>
       </x:c>
       <x:c r="I180" s="41"/>
@@ -11824,7 +12317,7 @@
       <x:c r="E181" s="41"/>
       <x:c r="F181" s="41"/>
       <x:c r="G181" s="41"/>
-      <x:c r="H181" s="184" t="str">
+      <x:c r="H181" s="232" t="str">
         <x:f>IF(B181="","",B181-WEEKDAY(B181-2,1)+1)</x:f>
       </x:c>
       <x:c r="I181" s="41"/>
@@ -11841,7 +12334,7 @@
       <x:c r="E182" s="41"/>
       <x:c r="F182" s="41"/>
       <x:c r="G182" s="41"/>
-      <x:c r="H182" s="184" t="str">
+      <x:c r="H182" s="232" t="str">
         <x:f>IF(B182="","",B182-WEEKDAY(B182-2,1)+1)</x:f>
       </x:c>
       <x:c r="I182" s="41"/>
@@ -11858,7 +12351,7 @@
       <x:c r="E183" s="41"/>
       <x:c r="F183" s="41"/>
       <x:c r="G183" s="41"/>
-      <x:c r="H183" s="184" t="str">
+      <x:c r="H183" s="232" t="str">
         <x:f>IF(B183="","",B183-WEEKDAY(B183-2,1)+1)</x:f>
       </x:c>
       <x:c r="I183" s="41"/>
@@ -11875,7 +12368,7 @@
       <x:c r="E184" s="41"/>
       <x:c r="F184" s="41"/>
       <x:c r="G184" s="41"/>
-      <x:c r="H184" s="184" t="str">
+      <x:c r="H184" s="232" t="str">
         <x:f>IF(B184="","",B184-WEEKDAY(B184-2,1)+1)</x:f>
       </x:c>
       <x:c r="I184" s="41"/>
@@ -11892,7 +12385,7 @@
       <x:c r="E185" s="41"/>
       <x:c r="F185" s="41"/>
       <x:c r="G185" s="41"/>
-      <x:c r="H185" s="184" t="str">
+      <x:c r="H185" s="232" t="str">
         <x:f>IF(B185="","",B185-WEEKDAY(B185-2,1)+1)</x:f>
       </x:c>
       <x:c r="I185" s="41"/>
@@ -11909,7 +12402,7 @@
       <x:c r="E186" s="41"/>
       <x:c r="F186" s="41"/>
       <x:c r="G186" s="41"/>
-      <x:c r="H186" s="184" t="str">
+      <x:c r="H186" s="232" t="str">
         <x:f>IF(B186="","",B186-WEEKDAY(B186-2,1)+1)</x:f>
       </x:c>
       <x:c r="I186" s="41"/>
@@ -11926,7 +12419,7 @@
       <x:c r="E187" s="41"/>
       <x:c r="F187" s="41"/>
       <x:c r="G187" s="41"/>
-      <x:c r="H187" s="184" t="str">
+      <x:c r="H187" s="232" t="str">
         <x:f>IF(B187="","",B187-WEEKDAY(B187-2,1)+1)</x:f>
       </x:c>
       <x:c r="I187" s="41"/>
@@ -11943,7 +12436,7 @@
       <x:c r="E188" s="41"/>
       <x:c r="F188" s="41"/>
       <x:c r="G188" s="41"/>
-      <x:c r="H188" s="184" t="str">
+      <x:c r="H188" s="232" t="str">
         <x:f>IF(B188="","",B188-WEEKDAY(B188-2,1)+1)</x:f>
       </x:c>
       <x:c r="I188" s="41"/>
@@ -11960,7 +12453,7 @@
       <x:c r="E189" s="41"/>
       <x:c r="F189" s="41"/>
       <x:c r="G189" s="41"/>
-      <x:c r="H189" s="184" t="str">
+      <x:c r="H189" s="232" t="str">
         <x:f>IF(B189="","",B189-WEEKDAY(B189-2,1)+1)</x:f>
       </x:c>
       <x:c r="I189" s="41"/>
@@ -11977,7 +12470,7 @@
       <x:c r="E190" s="41"/>
       <x:c r="F190" s="41"/>
       <x:c r="G190" s="41"/>
-      <x:c r="H190" s="184" t="str">
+      <x:c r="H190" s="232" t="str">
         <x:f>IF(B190="","",B190-WEEKDAY(B190-2,1)+1)</x:f>
       </x:c>
       <x:c r="I190" s="41"/>
@@ -11994,7 +12487,7 @@
       <x:c r="E191" s="41"/>
       <x:c r="F191" s="41"/>
       <x:c r="G191" s="41"/>
-      <x:c r="H191" s="184" t="str">
+      <x:c r="H191" s="232" t="str">
         <x:f>IF(B191="","",B191-WEEKDAY(B191-2,1)+1)</x:f>
       </x:c>
       <x:c r="I191" s="41"/>
@@ -12011,7 +12504,7 @@
       <x:c r="E192" s="41"/>
       <x:c r="F192" s="41"/>
       <x:c r="G192" s="41"/>
-      <x:c r="H192" s="184" t="str">
+      <x:c r="H192" s="232" t="str">
         <x:f>IF(B192="","",B192-WEEKDAY(B192-2,1)+1)</x:f>
       </x:c>
       <x:c r="I192" s="41"/>
@@ -12028,7 +12521,7 @@
       <x:c r="E193" s="41"/>
       <x:c r="F193" s="41"/>
       <x:c r="G193" s="41"/>
-      <x:c r="H193" s="184" t="str">
+      <x:c r="H193" s="232" t="str">
         <x:f>IF(B193="","",B193-WEEKDAY(B193-2,1)+1)</x:f>
       </x:c>
       <x:c r="I193" s="41"/>
@@ -12045,7 +12538,7 @@
       <x:c r="E194" s="41"/>
       <x:c r="F194" s="41"/>
       <x:c r="G194" s="41"/>
-      <x:c r="H194" s="184" t="str">
+      <x:c r="H194" s="232" t="str">
         <x:f>IF(B194="","",B194-WEEKDAY(B194-2,1)+1)</x:f>
       </x:c>
       <x:c r="I194" s="41"/>
@@ -12062,7 +12555,7 @@
       <x:c r="E195" s="41"/>
       <x:c r="F195" s="41"/>
       <x:c r="G195" s="41"/>
-      <x:c r="H195" s="184" t="str">
+      <x:c r="H195" s="232" t="str">
         <x:f>IF(B195="","",B195-WEEKDAY(B195-2,1)+1)</x:f>
       </x:c>
       <x:c r="I195" s="41"/>
@@ -12079,7 +12572,7 @@
       <x:c r="E196" s="41"/>
       <x:c r="F196" s="41"/>
       <x:c r="G196" s="41"/>
-      <x:c r="H196" s="184" t="str">
+      <x:c r="H196" s="232" t="str">
         <x:f>IF(B196="","",B196-WEEKDAY(B196-2,1)+1)</x:f>
       </x:c>
       <x:c r="I196" s="41"/>
@@ -12096,7 +12589,7 @@
       <x:c r="E197" s="41"/>
       <x:c r="F197" s="41"/>
       <x:c r="G197" s="41"/>
-      <x:c r="H197" s="184" t="str">
+      <x:c r="H197" s="232" t="str">
         <x:f>IF(B197="","",B197-WEEKDAY(B197-2,1)+1)</x:f>
       </x:c>
       <x:c r="I197" s="41"/>
@@ -12113,7 +12606,7 @@
       <x:c r="E198" s="41"/>
       <x:c r="F198" s="41"/>
       <x:c r="G198" s="41"/>
-      <x:c r="H198" s="184" t="str">
+      <x:c r="H198" s="232" t="str">
         <x:f>IF(B198="","",B198-WEEKDAY(B198-2,1)+1)</x:f>
       </x:c>
       <x:c r="I198" s="41"/>
@@ -12130,7 +12623,7 @@
       <x:c r="E199" s="41"/>
       <x:c r="F199" s="41"/>
       <x:c r="G199" s="41"/>
-      <x:c r="H199" s="184" t="str">
+      <x:c r="H199" s="232" t="str">
         <x:f>IF(B199="","",B199-WEEKDAY(B199-2,1)+1)</x:f>
       </x:c>
       <x:c r="I199" s="41"/>
@@ -12147,7 +12640,7 @@
       <x:c r="E200" s="41"/>
       <x:c r="F200" s="41"/>
       <x:c r="G200" s="41"/>
-      <x:c r="H200" s="184" t="str">
+      <x:c r="H200" s="232" t="str">
         <x:f>IF(B200="","",B200-WEEKDAY(B200-2,1)+1)</x:f>
       </x:c>
       <x:c r="I200" s="41"/>
@@ -12164,7 +12657,7 @@
       <x:c r="E201" s="41"/>
       <x:c r="F201" s="41"/>
       <x:c r="G201" s="41"/>
-      <x:c r="H201" s="184" t="str">
+      <x:c r="H201" s="232" t="str">
         <x:f>IF(B201="","",B201-WEEKDAY(B201-2,1)+1)</x:f>
       </x:c>
       <x:c r="I201" s="41"/>
@@ -12181,7 +12674,7 @@
       <x:c r="E202" s="41"/>
       <x:c r="F202" s="41"/>
       <x:c r="G202" s="41"/>
-      <x:c r="H202" s="184" t="str">
+      <x:c r="H202" s="232" t="str">
         <x:f>IF(B202="","",B202-WEEKDAY(B202-2,1)+1)</x:f>
       </x:c>
       <x:c r="I202" s="41"/>
@@ -12198,7 +12691,7 @@
       <x:c r="E203" s="41"/>
       <x:c r="F203" s="41"/>
       <x:c r="G203" s="41"/>
-      <x:c r="H203" s="184" t="str">
+      <x:c r="H203" s="232" t="str">
         <x:f>IF(B203="","",B203-WEEKDAY(B203-2,1)+1)</x:f>
       </x:c>
       <x:c r="I203" s="41"/>
@@ -12215,7 +12708,7 @@
       <x:c r="E204" s="41"/>
       <x:c r="F204" s="41"/>
       <x:c r="G204" s="41"/>
-      <x:c r="H204" s="184" t="str">
+      <x:c r="H204" s="232" t="str">
         <x:f>IF(B204="","",B204-WEEKDAY(B204-2,1)+1)</x:f>
       </x:c>
       <x:c r="I204" s="41"/>
@@ -12232,7 +12725,7 @@
       <x:c r="E205" s="41"/>
       <x:c r="F205" s="41"/>
       <x:c r="G205" s="41"/>
-      <x:c r="H205" s="184" t="str">
+      <x:c r="H205" s="232" t="str">
         <x:f>IF(B205="","",B205-WEEKDAY(B205-2,1)+1)</x:f>
       </x:c>
       <x:c r="I205" s="41"/>
@@ -12249,7 +12742,7 @@
       <x:c r="E206" s="41"/>
       <x:c r="F206" s="41"/>
       <x:c r="G206" s="41"/>
-      <x:c r="H206" s="184" t="str">
+      <x:c r="H206" s="232" t="str">
         <x:f>IF(B206="","",B206-WEEKDAY(B206-2,1)+1)</x:f>
       </x:c>
       <x:c r="I206" s="41"/>
@@ -12266,7 +12759,7 @@
       <x:c r="E207" s="41"/>
       <x:c r="F207" s="41"/>
       <x:c r="G207" s="41"/>
-      <x:c r="H207" s="184" t="str">
+      <x:c r="H207" s="232" t="str">
         <x:f>IF(B207="","",B207-WEEKDAY(B207-2,1)+1)</x:f>
       </x:c>
       <x:c r="I207" s="41"/>
@@ -12283,7 +12776,7 @@
       <x:c r="E208" s="41"/>
       <x:c r="F208" s="41"/>
       <x:c r="G208" s="41"/>
-      <x:c r="H208" s="184" t="str">
+      <x:c r="H208" s="232" t="str">
         <x:f>IF(B208="","",B208-WEEKDAY(B208-2,1)+1)</x:f>
       </x:c>
       <x:c r="I208" s="41"/>
@@ -12300,7 +12793,7 @@
       <x:c r="E209" s="41"/>
       <x:c r="F209" s="41"/>
       <x:c r="G209" s="41"/>
-      <x:c r="H209" s="184" t="str">
+      <x:c r="H209" s="232" t="str">
         <x:f>IF(B209="","",B209-WEEKDAY(B209-2,1)+1)</x:f>
       </x:c>
       <x:c r="I209" s="41"/>
@@ -12317,7 +12810,7 @@
       <x:c r="E210" s="41"/>
       <x:c r="F210" s="41"/>
       <x:c r="G210" s="41"/>
-      <x:c r="H210" s="184" t="str">
+      <x:c r="H210" s="232" t="str">
         <x:f>IF(B210="","",B210-WEEKDAY(B210-2,1)+1)</x:f>
       </x:c>
       <x:c r="I210" s="41"/>
@@ -12334,7 +12827,7 @@
       <x:c r="E211" s="41"/>
       <x:c r="F211" s="41"/>
       <x:c r="G211" s="41"/>
-      <x:c r="H211" s="184" t="str">
+      <x:c r="H211" s="232" t="str">
         <x:f>IF(B211="","",B211-WEEKDAY(B211-2,1)+1)</x:f>
       </x:c>
       <x:c r="I211" s="41"/>
@@ -12351,7 +12844,7 @@
       <x:c r="E212" s="41"/>
       <x:c r="F212" s="41"/>
       <x:c r="G212" s="41"/>
-      <x:c r="H212" s="184" t="str">
+      <x:c r="H212" s="232" t="str">
         <x:f>IF(B212="","",B212-WEEKDAY(B212-2,1)+1)</x:f>
       </x:c>
       <x:c r="I212" s="41"/>
@@ -12368,7 +12861,7 @@
       <x:c r="E213" s="41"/>
       <x:c r="F213" s="41"/>
       <x:c r="G213" s="41"/>
-      <x:c r="H213" s="184" t="str">
+      <x:c r="H213" s="232" t="str">
         <x:f>IF(B213="","",B213-WEEKDAY(B213-2,1)+1)</x:f>
       </x:c>
       <x:c r="I213" s="41"/>
@@ -12385,7 +12878,7 @@
       <x:c r="E214" s="41"/>
       <x:c r="F214" s="41"/>
       <x:c r="G214" s="41"/>
-      <x:c r="H214" s="184" t="str">
+      <x:c r="H214" s="232" t="str">
         <x:f>IF(B214="","",B214-WEEKDAY(B214-2,1)+1)</x:f>
       </x:c>
       <x:c r="I214" s="41"/>
@@ -12402,7 +12895,7 @@
       <x:c r="E215" s="41"/>
       <x:c r="F215" s="41"/>
       <x:c r="G215" s="41"/>
-      <x:c r="H215" s="184" t="str">
+      <x:c r="H215" s="232" t="str">
         <x:f>IF(B215="","",B215-WEEKDAY(B215-2,1)+1)</x:f>
       </x:c>
       <x:c r="I215" s="41"/>
@@ -12419,7 +12912,7 @@
       <x:c r="E216" s="41"/>
       <x:c r="F216" s="41"/>
       <x:c r="G216" s="41"/>
-      <x:c r="H216" s="184" t="str">
+      <x:c r="H216" s="232" t="str">
         <x:f>IF(B216="","",B216-WEEKDAY(B216-2,1)+1)</x:f>
       </x:c>
       <x:c r="I216" s="41"/>
@@ -12436,7 +12929,7 @@
       <x:c r="E217" s="41"/>
       <x:c r="F217" s="41"/>
       <x:c r="G217" s="41"/>
-      <x:c r="H217" s="184" t="str">
+      <x:c r="H217" s="232" t="str">
         <x:f>IF(B217="","",B217-WEEKDAY(B217-2,1)+1)</x:f>
       </x:c>
       <x:c r="I217" s="41"/>
@@ -12453,7 +12946,7 @@
       <x:c r="E218" s="41"/>
       <x:c r="F218" s="41"/>
       <x:c r="G218" s="41"/>
-      <x:c r="H218" s="184" t="str">
+      <x:c r="H218" s="232" t="str">
         <x:f>IF(B218="","",B218-WEEKDAY(B218-2,1)+1)</x:f>
       </x:c>
       <x:c r="I218" s="41"/>
@@ -12470,7 +12963,7 @@
       <x:c r="E219" s="41"/>
       <x:c r="F219" s="41"/>
       <x:c r="G219" s="41"/>
-      <x:c r="H219" s="184" t="str">
+      <x:c r="H219" s="232" t="str">
         <x:f>IF(B219="","",B219-WEEKDAY(B219-2,1)+1)</x:f>
       </x:c>
       <x:c r="I219" s="41"/>
@@ -12487,7 +12980,7 @@
       <x:c r="E220" s="41"/>
       <x:c r="F220" s="41"/>
       <x:c r="G220" s="41"/>
-      <x:c r="H220" s="184" t="str">
+      <x:c r="H220" s="232" t="str">
         <x:f>IF(B220="","",B220-WEEKDAY(B220-2,1)+1)</x:f>
       </x:c>
       <x:c r="I220" s="41"/>
@@ -12504,7 +12997,7 @@
       <x:c r="E221" s="41"/>
       <x:c r="F221" s="41"/>
       <x:c r="G221" s="41"/>
-      <x:c r="H221" s="184" t="str">
+      <x:c r="H221" s="232" t="str">
         <x:f>IF(B221="","",B221-WEEKDAY(B221-2,1)+1)</x:f>
       </x:c>
       <x:c r="I221" s="41"/>
@@ -12521,7 +13014,7 @@
       <x:c r="E222" s="41"/>
       <x:c r="F222" s="41"/>
       <x:c r="G222" s="41"/>
-      <x:c r="H222" s="184" t="str">
+      <x:c r="H222" s="232" t="str">
         <x:f>IF(B222="","",B222-WEEKDAY(B222-2,1)+1)</x:f>
       </x:c>
       <x:c r="I222" s="41"/>
@@ -12538,7 +13031,7 @@
       <x:c r="E223" s="41"/>
       <x:c r="F223" s="41"/>
       <x:c r="G223" s="41"/>
-      <x:c r="H223" s="184" t="str">
+      <x:c r="H223" s="232" t="str">
         <x:f>IF(B223="","",B223-WEEKDAY(B223-2,1)+1)</x:f>
       </x:c>
       <x:c r="I223" s="41"/>
@@ -12555,7 +13048,7 @@
       <x:c r="E224" s="41"/>
       <x:c r="F224" s="41"/>
       <x:c r="G224" s="41"/>
-      <x:c r="H224" s="184" t="str">
+      <x:c r="H224" s="232" t="str">
         <x:f>IF(B224="","",B224-WEEKDAY(B224-2,1)+1)</x:f>
       </x:c>
       <x:c r="I224" s="41"/>
@@ -12572,7 +13065,7 @@
       <x:c r="E225" s="41"/>
       <x:c r="F225" s="41"/>
       <x:c r="G225" s="41"/>
-      <x:c r="H225" s="184" t="str">
+      <x:c r="H225" s="232" t="str">
         <x:f>IF(B225="","",B225-WEEKDAY(B225-2,1)+1)</x:f>
       </x:c>
       <x:c r="I225" s="41"/>
@@ -12589,7 +13082,7 @@
       <x:c r="E226" s="41"/>
       <x:c r="F226" s="41"/>
       <x:c r="G226" s="41"/>
-      <x:c r="H226" s="184" t="str">
+      <x:c r="H226" s="232" t="str">
         <x:f>IF(B226="","",B226-WEEKDAY(B226-2,1)+1)</x:f>
       </x:c>
       <x:c r="I226" s="41"/>
@@ -12606,7 +13099,7 @@
       <x:c r="E227" s="41"/>
       <x:c r="F227" s="41"/>
       <x:c r="G227" s="41"/>
-      <x:c r="H227" s="184" t="str">
+      <x:c r="H227" s="232" t="str">
         <x:f>IF(B227="","",B227-WEEKDAY(B227-2,1)+1)</x:f>
       </x:c>
       <x:c r="I227" s="41"/>
@@ -12623,7 +13116,7 @@
       <x:c r="E228" s="41"/>
       <x:c r="F228" s="41"/>
       <x:c r="G228" s="41"/>
-      <x:c r="H228" s="184" t="str">
+      <x:c r="H228" s="232" t="str">
         <x:f>IF(B228="","",B228-WEEKDAY(B228-2,1)+1)</x:f>
       </x:c>
       <x:c r="I228" s="41"/>
@@ -12640,7 +13133,7 @@
       <x:c r="E229" s="41"/>
       <x:c r="F229" s="41"/>
       <x:c r="G229" s="41"/>
-      <x:c r="H229" s="184" t="str">
+      <x:c r="H229" s="232" t="str">
         <x:f>IF(B229="","",B229-WEEKDAY(B229-2,1)+1)</x:f>
       </x:c>
       <x:c r="I229" s="41"/>
@@ -12657,7 +13150,7 @@
       <x:c r="E230" s="41"/>
       <x:c r="F230" s="41"/>
       <x:c r="G230" s="41"/>
-      <x:c r="H230" s="184" t="str">
+      <x:c r="H230" s="232" t="str">
         <x:f>IF(B230="","",B230-WEEKDAY(B230-2,1)+1)</x:f>
       </x:c>
       <x:c r="I230" s="41"/>
@@ -12674,7 +13167,7 @@
       <x:c r="E231" s="41"/>
       <x:c r="F231" s="41"/>
       <x:c r="G231" s="41"/>
-      <x:c r="H231" s="184" t="str">
+      <x:c r="H231" s="232" t="str">
         <x:f>IF(B231="","",B231-WEEKDAY(B231-2,1)+1)</x:f>
       </x:c>
       <x:c r="I231" s="41"/>
@@ -12691,7 +13184,7 @@
       <x:c r="E232" s="41"/>
       <x:c r="F232" s="41"/>
       <x:c r="G232" s="41"/>
-      <x:c r="H232" s="184" t="str">
+      <x:c r="H232" s="232" t="str">
         <x:f>IF(B232="","",B232-WEEKDAY(B232-2,1)+1)</x:f>
       </x:c>
       <x:c r="I232" s="41"/>
@@ -12708,7 +13201,7 @@
       <x:c r="E233" s="41"/>
       <x:c r="F233" s="41"/>
       <x:c r="G233" s="41"/>
-      <x:c r="H233" s="184" t="str">
+      <x:c r="H233" s="232" t="str">
         <x:f>IF(B233="","",B233-WEEKDAY(B233-2,1)+1)</x:f>
       </x:c>
       <x:c r="I233" s="41"/>
@@ -12725,7 +13218,7 @@
       <x:c r="E234" s="41"/>
       <x:c r="F234" s="41"/>
       <x:c r="G234" s="41"/>
-      <x:c r="H234" s="184" t="str">
+      <x:c r="H234" s="232" t="str">
         <x:f>IF(B234="","",B234-WEEKDAY(B234-2,1)+1)</x:f>
       </x:c>
       <x:c r="I234" s="41"/>
@@ -12742,7 +13235,7 @@
       <x:c r="E235" s="41"/>
       <x:c r="F235" s="41"/>
       <x:c r="G235" s="41"/>
-      <x:c r="H235" s="184" t="str">
+      <x:c r="H235" s="232" t="str">
         <x:f>IF(B235="","",B235-WEEKDAY(B235-2,1)+1)</x:f>
       </x:c>
       <x:c r="I235" s="41"/>
@@ -12759,7 +13252,7 @@
       <x:c r="E236" s="41"/>
       <x:c r="F236" s="41"/>
       <x:c r="G236" s="41"/>
-      <x:c r="H236" s="184" t="str">
+      <x:c r="H236" s="232" t="str">
         <x:f>IF(B236="","",B236-WEEKDAY(B236-2,1)+1)</x:f>
       </x:c>
       <x:c r="I236" s="41"/>
@@ -12776,7 +13269,7 @@
       <x:c r="E237" s="41"/>
       <x:c r="F237" s="41"/>
       <x:c r="G237" s="41"/>
-      <x:c r="H237" s="184" t="str">
+      <x:c r="H237" s="232" t="str">
         <x:f>IF(B237="","",B237-WEEKDAY(B237-2,1)+1)</x:f>
       </x:c>
       <x:c r="I237" s="41"/>
@@ -12793,7 +13286,7 @@
       <x:c r="E238" s="41"/>
       <x:c r="F238" s="41"/>
       <x:c r="G238" s="41"/>
-      <x:c r="H238" s="184" t="str">
+      <x:c r="H238" s="232" t="str">
         <x:f>IF(B238="","",B238-WEEKDAY(B238-2,1)+1)</x:f>
       </x:c>
       <x:c r="I238" s="41"/>
@@ -12810,7 +13303,7 @@
       <x:c r="E239" s="41"/>
       <x:c r="F239" s="41"/>
       <x:c r="G239" s="41"/>
-      <x:c r="H239" s="184" t="str">
+      <x:c r="H239" s="232" t="str">
         <x:f>IF(B239="","",B239-WEEKDAY(B239-2,1)+1)</x:f>
       </x:c>
       <x:c r="I239" s="41"/>
@@ -12827,7 +13320,7 @@
       <x:c r="E240" s="41"/>
       <x:c r="F240" s="41"/>
       <x:c r="G240" s="41"/>
-      <x:c r="H240" s="184" t="str">
+      <x:c r="H240" s="232" t="str">
         <x:f>IF(B240="","",B240-WEEKDAY(B240-2,1)+1)</x:f>
       </x:c>
       <x:c r="I240" s="41"/>
@@ -12844,7 +13337,7 @@
       <x:c r="E241" s="41"/>
       <x:c r="F241" s="41"/>
       <x:c r="G241" s="41"/>
-      <x:c r="H241" s="184" t="str">
+      <x:c r="H241" s="232" t="str">
         <x:f>IF(B241="","",B241-WEEKDAY(B241-2,1)+1)</x:f>
       </x:c>
       <x:c r="I241" s="41"/>
@@ -12861,7 +13354,7 @@
       <x:c r="E242" s="41"/>
       <x:c r="F242" s="41"/>
       <x:c r="G242" s="41"/>
-      <x:c r="H242" s="184" t="str">
+      <x:c r="H242" s="232" t="str">
         <x:f>IF(B242="","",B242-WEEKDAY(B242-2,1)+1)</x:f>
       </x:c>
       <x:c r="I242" s="41"/>
@@ -12878,7 +13371,7 @@
       <x:c r="E243" s="41"/>
       <x:c r="F243" s="41"/>
       <x:c r="G243" s="41"/>
-      <x:c r="H243" s="184" t="str">
+      <x:c r="H243" s="232" t="str">
         <x:f>IF(B243="","",B243-WEEKDAY(B243-2,1)+1)</x:f>
       </x:c>
       <x:c r="I243" s="41"/>
@@ -12895,7 +13388,7 @@
       <x:c r="E244" s="41"/>
       <x:c r="F244" s="41"/>
       <x:c r="G244" s="41"/>
-      <x:c r="H244" s="184" t="str">
+      <x:c r="H244" s="232" t="str">
         <x:f>IF(B244="","",B244-WEEKDAY(B244-2,1)+1)</x:f>
       </x:c>
       <x:c r="I244" s="41"/>
@@ -12912,7 +13405,7 @@
       <x:c r="E245" s="41"/>
       <x:c r="F245" s="41"/>
       <x:c r="G245" s="41"/>
-      <x:c r="H245" s="184" t="str">
+      <x:c r="H245" s="232" t="str">
         <x:f>IF(B245="","",B245-WEEKDAY(B245-2,1)+1)</x:f>
       </x:c>
       <x:c r="I245" s="41"/>
@@ -12929,7 +13422,7 @@
       <x:c r="E246" s="41"/>
       <x:c r="F246" s="41"/>
       <x:c r="G246" s="41"/>
-      <x:c r="H246" s="184" t="str">
+      <x:c r="H246" s="232" t="str">
         <x:f>IF(B246="","",B246-WEEKDAY(B246-2,1)+1)</x:f>
       </x:c>
       <x:c r="I246" s="41"/>
@@ -12946,7 +13439,7 @@
       <x:c r="E247" s="41"/>
       <x:c r="F247" s="41"/>
       <x:c r="G247" s="41"/>
-      <x:c r="H247" s="184" t="str">
+      <x:c r="H247" s="232" t="str">
         <x:f>IF(B247="","",B247-WEEKDAY(B247-2,1)+1)</x:f>
       </x:c>
       <x:c r="I247" s="41"/>
@@ -12963,7 +13456,7 @@
       <x:c r="E248" s="41"/>
       <x:c r="F248" s="41"/>
       <x:c r="G248" s="41"/>
-      <x:c r="H248" s="184" t="str">
+      <x:c r="H248" s="232" t="str">
         <x:f>IF(B248="","",B248-WEEKDAY(B248-2,1)+1)</x:f>
       </x:c>
       <x:c r="I248" s="41"/>
@@ -12980,7 +13473,7 @@
       <x:c r="E249" s="41"/>
       <x:c r="F249" s="41"/>
       <x:c r="G249" s="41"/>
-      <x:c r="H249" s="184" t="str">
+      <x:c r="H249" s="232" t="str">
         <x:f>IF(B249="","",B249-WEEKDAY(B249-2,1)+1)</x:f>
       </x:c>
       <x:c r="I249" s="41"/>
@@ -12997,7 +13490,7 @@
       <x:c r="E250" s="41"/>
       <x:c r="F250" s="41"/>
       <x:c r="G250" s="41"/>
-      <x:c r="H250" s="184" t="str">
+      <x:c r="H250" s="232" t="str">
         <x:f>IF(B250="","",B250-WEEKDAY(B250-2,1)+1)</x:f>
       </x:c>
       <x:c r="I250" s="41"/>
@@ -13014,7 +13507,7 @@
       <x:c r="E251" s="41"/>
       <x:c r="F251" s="41"/>
       <x:c r="G251" s="41"/>
-      <x:c r="H251" s="184" t="str">
+      <x:c r="H251" s="232" t="str">
         <x:f>IF(B251="","",B251-WEEKDAY(B251-2,1)+1)</x:f>
       </x:c>
       <x:c r="I251" s="41"/>
@@ -13031,7 +13524,7 @@
       <x:c r="E252" s="41"/>
       <x:c r="F252" s="41"/>
       <x:c r="G252" s="41"/>
-      <x:c r="H252" s="184" t="str">
+      <x:c r="H252" s="232" t="str">
         <x:f>IF(B252="","",B252-WEEKDAY(B252-2,1)+1)</x:f>
       </x:c>
       <x:c r="I252" s="41"/>
@@ -13048,7 +13541,7 @@
       <x:c r="E253" s="41"/>
       <x:c r="F253" s="41"/>
       <x:c r="G253" s="41"/>
-      <x:c r="H253" s="184" t="str">
+      <x:c r="H253" s="232" t="str">
         <x:f>IF(B253="","",B253-WEEKDAY(B253-2,1)+1)</x:f>
       </x:c>
       <x:c r="I253" s="41"/>
@@ -13065,7 +13558,7 @@
       <x:c r="E254" s="41"/>
       <x:c r="F254" s="41"/>
       <x:c r="G254" s="41"/>
-      <x:c r="H254" s="184" t="str">
+      <x:c r="H254" s="232" t="str">
         <x:f>IF(B254="","",B254-WEEKDAY(B254-2,1)+1)</x:f>
       </x:c>
       <x:c r="I254" s="41"/>
@@ -13082,7 +13575,7 @@
       <x:c r="E255" s="41"/>
       <x:c r="F255" s="41"/>
       <x:c r="G255" s="41"/>
-      <x:c r="H255" s="184" t="str">
+      <x:c r="H255" s="232" t="str">
         <x:f>IF(B255="","",B255-WEEKDAY(B255-2,1)+1)</x:f>
       </x:c>
       <x:c r="I255" s="41"/>
@@ -13099,7 +13592,7 @@
       <x:c r="E256" s="41"/>
       <x:c r="F256" s="41"/>
       <x:c r="G256" s="41"/>
-      <x:c r="H256" s="184" t="str">
+      <x:c r="H256" s="232" t="str">
         <x:f>IF(B256="","",B256-WEEKDAY(B256-2,1)+1)</x:f>
       </x:c>
       <x:c r="I256" s="41"/>
@@ -13116,7 +13609,7 @@
       <x:c r="E257" s="41"/>
       <x:c r="F257" s="41"/>
       <x:c r="G257" s="41"/>
-      <x:c r="H257" s="184" t="str">
+      <x:c r="H257" s="232" t="str">
         <x:f>IF(B257="","",B257-WEEKDAY(B257-2,1)+1)</x:f>
       </x:c>
       <x:c r="I257" s="41"/>
@@ -13133,7 +13626,7 @@
       <x:c r="E258" s="41"/>
       <x:c r="F258" s="41"/>
       <x:c r="G258" s="41"/>
-      <x:c r="H258" s="184" t="str">
+      <x:c r="H258" s="232" t="str">
         <x:f>IF(B258="","",B258-WEEKDAY(B258-2,1)+1)</x:f>
       </x:c>
       <x:c r="I258" s="41"/>
@@ -13150,7 +13643,7 @@
       <x:c r="E259" s="41"/>
       <x:c r="F259" s="41"/>
       <x:c r="G259" s="41"/>
-      <x:c r="H259" s="184" t="str">
+      <x:c r="H259" s="232" t="str">
         <x:f>IF(B259="","",B259-WEEKDAY(B259-2,1)+1)</x:f>
       </x:c>
       <x:c r="I259" s="41"/>
@@ -13167,7 +13660,7 @@
       <x:c r="E260" s="41"/>
       <x:c r="F260" s="41"/>
       <x:c r="G260" s="41"/>
-      <x:c r="H260" s="184" t="str">
+      <x:c r="H260" s="232" t="str">
         <x:f>IF(B260="","",B260-WEEKDAY(B260-2,1)+1)</x:f>
       </x:c>
       <x:c r="I260" s="41"/>
@@ -13184,7 +13677,7 @@
       <x:c r="E261" s="41"/>
       <x:c r="F261" s="41"/>
       <x:c r="G261" s="41"/>
-      <x:c r="H261" s="184" t="str">
+      <x:c r="H261" s="232" t="str">
         <x:f>IF(B261="","",B261-WEEKDAY(B261-2,1)+1)</x:f>
       </x:c>
       <x:c r="I261" s="41"/>
@@ -13201,7 +13694,7 @@
       <x:c r="E262" s="41"/>
       <x:c r="F262" s="41"/>
       <x:c r="G262" s="41"/>
-      <x:c r="H262" s="184" t="str">
+      <x:c r="H262" s="232" t="str">
         <x:f>IF(B262="","",B262-WEEKDAY(B262-2,1)+1)</x:f>
       </x:c>
       <x:c r="I262" s="41"/>
@@ -13218,7 +13711,7 @@
       <x:c r="E263" s="41"/>
       <x:c r="F263" s="41"/>
       <x:c r="G263" s="41"/>
-      <x:c r="H263" s="184" t="str">
+      <x:c r="H263" s="232" t="str">
         <x:f>IF(B263="","",B263-WEEKDAY(B263-2,1)+1)</x:f>
       </x:c>
       <x:c r="I263" s="41"/>
@@ -13235,7 +13728,7 @@
       <x:c r="E264" s="41"/>
       <x:c r="F264" s="41"/>
       <x:c r="G264" s="41"/>
-      <x:c r="H264" s="184" t="str">
+      <x:c r="H264" s="232" t="str">
         <x:f>IF(B264="","",B264-WEEKDAY(B264-2,1)+1)</x:f>
       </x:c>
       <x:c r="I264" s="41"/>
@@ -13252,7 +13745,7 @@
       <x:c r="E265" s="41"/>
       <x:c r="F265" s="41"/>
       <x:c r="G265" s="41"/>
-      <x:c r="H265" s="184" t="str">
+      <x:c r="H265" s="232" t="str">
         <x:f>IF(B265="","",B265-WEEKDAY(B265-2,1)+1)</x:f>
       </x:c>
       <x:c r="I265" s="41"/>
@@ -13269,7 +13762,7 @@
       <x:c r="E266" s="41"/>
       <x:c r="F266" s="41"/>
       <x:c r="G266" s="41"/>
-      <x:c r="H266" s="184" t="str">
+      <x:c r="H266" s="232" t="str">
         <x:f>IF(B266="","",B266-WEEKDAY(B266-2,1)+1)</x:f>
       </x:c>
       <x:c r="I266" s="41"/>
@@ -13286,7 +13779,7 @@
       <x:c r="E267" s="41"/>
       <x:c r="F267" s="41"/>
       <x:c r="G267" s="41"/>
-      <x:c r="H267" s="184" t="str">
+      <x:c r="H267" s="232" t="str">
         <x:f>IF(B267="","",B267-WEEKDAY(B267-2,1)+1)</x:f>
       </x:c>
       <x:c r="I267" s="41"/>
@@ -13303,7 +13796,7 @@
       <x:c r="E268" s="41"/>
       <x:c r="F268" s="41"/>
       <x:c r="G268" s="41"/>
-      <x:c r="H268" s="184" t="str">
+      <x:c r="H268" s="232" t="str">
         <x:f>IF(B268="","",B268-WEEKDAY(B268-2,1)+1)</x:f>
       </x:c>
       <x:c r="I268" s="41"/>
@@ -13320,7 +13813,7 @@
       <x:c r="E269" s="41"/>
       <x:c r="F269" s="41"/>
       <x:c r="G269" s="41"/>
-      <x:c r="H269" s="184" t="str">
+      <x:c r="H269" s="232" t="str">
         <x:f>IF(B269="","",B269-WEEKDAY(B269-2,1)+1)</x:f>
       </x:c>
       <x:c r="I269" s="41"/>
@@ -13337,7 +13830,7 @@
       <x:c r="E270" s="41"/>
       <x:c r="F270" s="41"/>
       <x:c r="G270" s="41"/>
-      <x:c r="H270" s="184" t="str">
+      <x:c r="H270" s="232" t="str">
         <x:f>IF(B270="","",B270-WEEKDAY(B270-2,1)+1)</x:f>
       </x:c>
       <x:c r="I270" s="41"/>
@@ -13354,7 +13847,7 @@
       <x:c r="E271" s="41"/>
       <x:c r="F271" s="41"/>
       <x:c r="G271" s="41"/>
-      <x:c r="H271" s="184" t="str">
+      <x:c r="H271" s="232" t="str">
         <x:f>IF(B271="","",B271-WEEKDAY(B271-2,1)+1)</x:f>
       </x:c>
       <x:c r="I271" s="41"/>
@@ -13371,7 +13864,7 @@
       <x:c r="E272" s="41"/>
       <x:c r="F272" s="41"/>
       <x:c r="G272" s="41"/>
-      <x:c r="H272" s="184" t="str">
+      <x:c r="H272" s="232" t="str">
         <x:f>IF(B272="","",B272-WEEKDAY(B272-2,1)+1)</x:f>
       </x:c>
       <x:c r="I272" s="41"/>
@@ -13388,7 +13881,7 @@
       <x:c r="E273" s="41"/>
       <x:c r="F273" s="41"/>
       <x:c r="G273" s="41"/>
-      <x:c r="H273" s="184" t="str">
+      <x:c r="H273" s="232" t="str">
         <x:f>IF(B273="","",B273-WEEKDAY(B273-2,1)+1)</x:f>
       </x:c>
       <x:c r="I273" s="41"/>
@@ -13405,7 +13898,7 @@
       <x:c r="E274" s="41"/>
       <x:c r="F274" s="41"/>
       <x:c r="G274" s="41"/>
-      <x:c r="H274" s="184" t="str">
+      <x:c r="H274" s="232" t="str">
         <x:f>IF(B274="","",B274-WEEKDAY(B274-2,1)+1)</x:f>
       </x:c>
       <x:c r="I274" s="41"/>
@@ -13422,7 +13915,7 @@
       <x:c r="E275" s="41"/>
       <x:c r="F275" s="41"/>
       <x:c r="G275" s="41"/>
-      <x:c r="H275" s="184" t="str">
+      <x:c r="H275" s="232" t="str">
         <x:f>IF(B275="","",B275-WEEKDAY(B275-2,1)+1)</x:f>
       </x:c>
       <x:c r="I275" s="41"/>
@@ -13439,7 +13932,7 @@
       <x:c r="E276" s="41"/>
       <x:c r="F276" s="41"/>
       <x:c r="G276" s="41"/>
-      <x:c r="H276" s="184" t="str">
+      <x:c r="H276" s="232" t="str">
         <x:f>IF(B276="","",B276-WEEKDAY(B276-2,1)+1)</x:f>
       </x:c>
       <x:c r="I276" s="41"/>
@@ -13456,7 +13949,7 @@
       <x:c r="E277" s="41"/>
       <x:c r="F277" s="41"/>
       <x:c r="G277" s="41"/>
-      <x:c r="H277" s="184" t="str">
+      <x:c r="H277" s="232" t="str">
         <x:f>IF(B277="","",B277-WEEKDAY(B277-2,1)+1)</x:f>
       </x:c>
       <x:c r="I277" s="41"/>
@@ -13473,7 +13966,7 @@
       <x:c r="E278" s="41"/>
       <x:c r="F278" s="41"/>
       <x:c r="G278" s="41"/>
-      <x:c r="H278" s="184" t="str">
+      <x:c r="H278" s="232" t="str">
         <x:f>IF(B278="","",B278-WEEKDAY(B278-2,1)+1)</x:f>
       </x:c>
       <x:c r="I278" s="41"/>
@@ -13490,7 +13983,7 @@
       <x:c r="E279" s="41"/>
       <x:c r="F279" s="41"/>
       <x:c r="G279" s="41"/>
-      <x:c r="H279" s="184" t="str">
+      <x:c r="H279" s="232" t="str">
         <x:f>IF(B279="","",B279-WEEKDAY(B279-2,1)+1)</x:f>
       </x:c>
       <x:c r="I279" s="41"/>
@@ -13507,7 +14000,7 @@
       <x:c r="E280" s="41"/>
       <x:c r="F280" s="41"/>
       <x:c r="G280" s="41"/>
-      <x:c r="H280" s="184" t="str">
+      <x:c r="H280" s="232" t="str">
         <x:f>IF(B280="","",B280-WEEKDAY(B280-2,1)+1)</x:f>
       </x:c>
       <x:c r="I280" s="41"/>
@@ -13524,7 +14017,7 @@
       <x:c r="E281" s="41"/>
       <x:c r="F281" s="41"/>
       <x:c r="G281" s="41"/>
-      <x:c r="H281" s="184" t="str">
+      <x:c r="H281" s="232" t="str">
         <x:f>IF(B281="","",B281-WEEKDAY(B281-2,1)+1)</x:f>
       </x:c>
       <x:c r="I281" s="41"/>
@@ -13541,7 +14034,7 @@
       <x:c r="E282" s="41"/>
       <x:c r="F282" s="41"/>
       <x:c r="G282" s="41"/>
-      <x:c r="H282" s="184" t="str">
+      <x:c r="H282" s="232" t="str">
         <x:f>IF(B282="","",B282-WEEKDAY(B282-2,1)+1)</x:f>
       </x:c>
       <x:c r="I282" s="41"/>
@@ -13558,7 +14051,7 @@
       <x:c r="E283" s="41"/>
       <x:c r="F283" s="41"/>
       <x:c r="G283" s="41"/>
-      <x:c r="H283" s="184" t="str">
+      <x:c r="H283" s="232" t="str">
         <x:f>IF(B283="","",B283-WEEKDAY(B283-2,1)+1)</x:f>
       </x:c>
       <x:c r="I283" s="41"/>
@@ -13575,7 +14068,7 @@
       <x:c r="E284" s="41"/>
       <x:c r="F284" s="41"/>
       <x:c r="G284" s="41"/>
-      <x:c r="H284" s="184" t="str">
+      <x:c r="H284" s="232" t="str">
         <x:f>IF(B284="","",B284-WEEKDAY(B284-2,1)+1)</x:f>
       </x:c>
       <x:c r="I284" s="41"/>
@@ -13592,7 +14085,7 @@
       <x:c r="E285" s="41"/>
       <x:c r="F285" s="41"/>
       <x:c r="G285" s="41"/>
-      <x:c r="H285" s="184" t="str">
+      <x:c r="H285" s="232" t="str">
         <x:f>IF(B285="","",B285-WEEKDAY(B285-2,1)+1)</x:f>
       </x:c>
       <x:c r="I285" s="41"/>
@@ -13609,7 +14102,7 @@
       <x:c r="E286" s="41"/>
       <x:c r="F286" s="41"/>
       <x:c r="G286" s="41"/>
-      <x:c r="H286" s="184" t="str">
+      <x:c r="H286" s="232" t="str">
         <x:f>IF(B286="","",B286-WEEKDAY(B286-2,1)+1)</x:f>
       </x:c>
       <x:c r="I286" s="41"/>
@@ -13626,7 +14119,7 @@
       <x:c r="E287" s="41"/>
       <x:c r="F287" s="41"/>
       <x:c r="G287" s="41"/>
-      <x:c r="H287" s="184" t="str">
+      <x:c r="H287" s="232" t="str">
         <x:f>IF(B287="","",B287-WEEKDAY(B287-2,1)+1)</x:f>
       </x:c>
       <x:c r="I287" s="41"/>
@@ -13643,7 +14136,7 @@
       <x:c r="E288" s="41"/>
       <x:c r="F288" s="41"/>
       <x:c r="G288" s="41"/>
-      <x:c r="H288" s="184" t="str">
+      <x:c r="H288" s="232" t="str">
         <x:f>IF(B288="","",B288-WEEKDAY(B288-2,1)+1)</x:f>
       </x:c>
       <x:c r="I288" s="41"/>
@@ -13660,7 +14153,7 @@
       <x:c r="E289" s="41"/>
       <x:c r="F289" s="41"/>
       <x:c r="G289" s="41"/>
-      <x:c r="H289" s="184" t="str">
+      <x:c r="H289" s="232" t="str">
         <x:f>IF(B289="","",B289-WEEKDAY(B289-2,1)+1)</x:f>
       </x:c>
       <x:c r="I289" s="41"/>
@@ -13677,7 +14170,7 @@
       <x:c r="E290" s="41"/>
       <x:c r="F290" s="41"/>
       <x:c r="G290" s="41"/>
-      <x:c r="H290" s="184" t="str">
+      <x:c r="H290" s="232" t="str">
         <x:f>IF(B290="","",B290-WEEKDAY(B290-2,1)+1)</x:f>
       </x:c>
       <x:c r="I290" s="41"/>
@@ -13694,7 +14187,7 @@
       <x:c r="E291" s="41"/>
       <x:c r="F291" s="41"/>
       <x:c r="G291" s="41"/>
-      <x:c r="H291" s="184" t="str">
+      <x:c r="H291" s="232" t="str">
         <x:f>IF(B291="","",B291-WEEKDAY(B291-2,1)+1)</x:f>
       </x:c>
       <x:c r="I291" s="41"/>
@@ -13711,7 +14204,7 @@
       <x:c r="E292" s="41"/>
       <x:c r="F292" s="41"/>
       <x:c r="G292" s="41"/>
-      <x:c r="H292" s="184" t="str">
+      <x:c r="H292" s="232" t="str">
         <x:f>IF(B292="","",B292-WEEKDAY(B292-2,1)+1)</x:f>
       </x:c>
       <x:c r="I292" s="41"/>
@@ -13728,7 +14221,7 @@
       <x:c r="E293" s="41"/>
       <x:c r="F293" s="41"/>
       <x:c r="G293" s="41"/>
-      <x:c r="H293" s="184" t="str">
+      <x:c r="H293" s="232" t="str">
         <x:f>IF(B293="","",B293-WEEKDAY(B293-2,1)+1)</x:f>
       </x:c>
       <x:c r="I293" s="41"/>
@@ -13745,7 +14238,7 @@
       <x:c r="E294" s="41"/>
       <x:c r="F294" s="41"/>
       <x:c r="G294" s="41"/>
-      <x:c r="H294" s="184" t="str">
+      <x:c r="H294" s="232" t="str">
         <x:f>IF(B294="","",B294-WEEKDAY(B294-2,1)+1)</x:f>
       </x:c>
       <x:c r="I294" s="41"/>
@@ -13762,7 +14255,7 @@
       <x:c r="E295" s="41"/>
       <x:c r="F295" s="41"/>
       <x:c r="G295" s="41"/>
-      <x:c r="H295" s="184" t="str">
+      <x:c r="H295" s="232" t="str">
         <x:f>IF(B295="","",B295-WEEKDAY(B295-2,1)+1)</x:f>
       </x:c>
       <x:c r="I295" s="41"/>
@@ -13779,7 +14272,7 @@
       <x:c r="E296" s="41"/>
       <x:c r="F296" s="41"/>
       <x:c r="G296" s="41"/>
-      <x:c r="H296" s="184" t="str">
+      <x:c r="H296" s="232" t="str">
         <x:f>IF(B296="","",B296-WEEKDAY(B296-2,1)+1)</x:f>
       </x:c>
       <x:c r="I296" s="41"/>
@@ -13796,7 +14289,7 @@
       <x:c r="E297" s="41"/>
       <x:c r="F297" s="41"/>
       <x:c r="G297" s="41"/>
-      <x:c r="H297" s="184" t="str">
+      <x:c r="H297" s="232" t="str">
         <x:f>IF(B297="","",B297-WEEKDAY(B297-2,1)+1)</x:f>
       </x:c>
       <x:c r="I297" s="41"/>
@@ -13813,7 +14306,7 @@
       <x:c r="E298" s="41"/>
       <x:c r="F298" s="41"/>
       <x:c r="G298" s="41"/>
-      <x:c r="H298" s="184" t="str">
+      <x:c r="H298" s="232" t="str">
         <x:f>IF(B298="","",B298-WEEKDAY(B298-2,1)+1)</x:f>
       </x:c>
       <x:c r="I298" s="41"/>
@@ -13830,7 +14323,7 @@
       <x:c r="E299" s="41"/>
       <x:c r="F299" s="41"/>
       <x:c r="G299" s="41"/>
-      <x:c r="H299" s="184" t="str">
+      <x:c r="H299" s="232" t="str">
         <x:f>IF(B299="","",B299-WEEKDAY(B299-2,1)+1)</x:f>
       </x:c>
       <x:c r="I299" s="41"/>
@@ -13847,7 +14340,7 @@
       <x:c r="E300" s="41"/>
       <x:c r="F300" s="41"/>
       <x:c r="G300" s="41"/>
-      <x:c r="H300" s="184" t="str">
+      <x:c r="H300" s="232" t="str">
         <x:f>IF(B300="","",B300-WEEKDAY(B300-2,1)+1)</x:f>
       </x:c>
       <x:c r="I300" s="41"/>
@@ -13864,7 +14357,7 @@
       <x:c r="E301" s="41"/>
       <x:c r="F301" s="41"/>
       <x:c r="G301" s="41"/>
-      <x:c r="H301" s="184" t="str">
+      <x:c r="H301" s="232" t="str">
         <x:f>IF(B301="","",B301-WEEKDAY(B301-2,1)+1)</x:f>
       </x:c>
       <x:c r="I301" s="41"/>
@@ -13881,7 +14374,7 @@
       <x:c r="E302" s="41"/>
       <x:c r="F302" s="41"/>
       <x:c r="G302" s="41"/>
-      <x:c r="H302" s="184" t="str">
+      <x:c r="H302" s="232" t="str">
         <x:f>IF(B302="","",B302-WEEKDAY(B302-2,1)+1)</x:f>
       </x:c>
       <x:c r="I302" s="41"/>
@@ -13898,7 +14391,7 @@
       <x:c r="E303" s="41"/>
       <x:c r="F303" s="41"/>
       <x:c r="G303" s="41"/>
-      <x:c r="H303" s="184" t="str">
+      <x:c r="H303" s="232" t="str">
         <x:f>IF(B303="","",B303-WEEKDAY(B303-2,1)+1)</x:f>
       </x:c>
       <x:c r="I303" s="41"/>
@@ -13915,7 +14408,7 @@
       <x:c r="E304" s="41"/>
       <x:c r="F304" s="41"/>
       <x:c r="G304" s="41"/>
-      <x:c r="H304" s="184" t="str">
+      <x:c r="H304" s="232" t="str">
         <x:f>IF(B304="","",B304-WEEKDAY(B304-2,1)+1)</x:f>
       </x:c>
       <x:c r="I304" s="41"/>
@@ -13930,19 +14423,19 @@
     <x:mergeCell ref="A2:M2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="A5:M304">
-    <x:cfRule type="expression" dxfId="6" priority="1">
+    <x:cfRule type="expression" dxfId="10" priority="1">
       <x:formula>AND($C5&lt;&gt;"",$G5="Exclude")</x:formula>
     </x:cfRule>
-    <x:cfRule type="expression" dxfId="7" priority="2">
+    <x:cfRule type="expression" dxfId="11" priority="2">
       <x:formula>AND($C5&lt;&gt;"",$G5="Transfer / verify")</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="G5:G304">
-    <x:cfRule type="containsText" dxfId="8" priority="3" operator="containsText" text="Include"/>
+    <x:cfRule type="containsText" dxfId="12" priority="3" operator="containsText" text="Include"/>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="M5:M304">
-    <x:cfRule type="containsText" dxfId="9" priority="4" operator="containsText" text="Verified"/>
-    <x:cfRule type="containsText" dxfId="10" priority="5" operator="containsText" text="Needs verification"/>
+    <x:cfRule type="containsText" dxfId="13" priority="4" operator="containsText" text="Verified"/>
+    <x:cfRule type="containsText" dxfId="14" priority="5" operator="containsText" text="Needs verification"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -14117,7 +14610,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="F12" s="36" t="str">
-        <x:v>Fund on the four Tuesdays after rent is paid; $300 x 4 creates a modest cushion at the current rent</x:v>
+        <x:v>Maximum weekly rent target. Fund only from verified Wells capacity after required actions; record the actual amount in Savings &amp; Debt.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -14662,654 +15155,654 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="129" t="str">
+      <x:c r="A1" s="171" t="str">
         <x:v>Funding &amp; Due-Date Detail</x:v>
       </x:c>
-      <x:c r="B1" s="129"/>
-      <x:c r="C1" s="129"/>
-      <x:c r="D1" s="129"/>
-      <x:c r="E1" s="129"/>
-      <x:c r="F1" s="129"/>
-      <x:c r="G1" s="129"/>
-      <x:c r="H1" s="129"/>
+      <x:c r="B1" s="171"/>
+      <x:c r="C1" s="171"/>
+      <x:c r="D1" s="171"/>
+      <x:c r="E1" s="171"/>
+      <x:c r="F1" s="171"/>
+      <x:c r="G1" s="171"/>
+      <x:c r="H1" s="171"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="130" t="str">
+      <x:c r="A2" s="172" t="str">
         <x:v>This is the bridge between the weekly budget and Tuesday payments. A reserve transfer is not new spending. Keep future-dated reserves in Wealthfront; move money to Wells only ahead of a Wells autopay or card payoff.</x:v>
       </x:c>
-      <x:c r="B2" s="130"/>
-      <x:c r="C2" s="130"/>
-      <x:c r="D2" s="130"/>
-      <x:c r="E2" s="130"/>
-      <x:c r="F2" s="130"/>
-      <x:c r="G2" s="130"/>
-      <x:c r="H2" s="130"/>
+      <x:c r="B2" s="172"/>
+      <x:c r="C2" s="172"/>
+      <x:c r="D2" s="172"/>
+      <x:c r="E2" s="172"/>
+      <x:c r="F2" s="172"/>
+      <x:c r="G2" s="172"/>
+      <x:c r="H2" s="172"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="131"/>
-      <x:c r="B3" s="131"/>
-      <x:c r="C3" s="131"/>
-      <x:c r="D3" s="131"/>
-      <x:c r="E3" s="131"/>
-      <x:c r="F3" s="131"/>
-      <x:c r="G3" s="131"/>
-      <x:c r="H3" s="131"/>
+      <x:c r="A3" s="173"/>
+      <x:c r="B3" s="173"/>
+      <x:c r="C3" s="173"/>
+      <x:c r="D3" s="173"/>
+      <x:c r="E3" s="173"/>
+      <x:c r="F3" s="173"/>
+      <x:c r="G3" s="173"/>
+      <x:c r="H3" s="173"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="145" t="str">
+      <x:c r="A4" s="184" t="str">
         <x:v>Category</x:v>
       </x:c>
-      <x:c r="B4" s="146" t="str">
+      <x:c r="B4" s="185" t="str">
         <x:v>Bill / reserve</x:v>
       </x:c>
-      <x:c r="C4" s="146" t="str">
+      <x:c r="C4" s="185" t="str">
         <x:v>Weekly funding</x:v>
       </x:c>
-      <x:c r="D4" s="146" t="str">
+      <x:c r="D4" s="185" t="str">
         <x:v>Next due / action</x:v>
       </x:c>
-      <x:c r="E4" s="146" t="str">
+      <x:c r="E4" s="185" t="str">
         <x:v>Where cash lives</x:v>
       </x:c>
-      <x:c r="F4" s="146" t="str">
+      <x:c r="F4" s="185" t="str">
         <x:v>Payment route</x:v>
       </x:c>
-      <x:c r="G4" s="146" t="str">
+      <x:c r="G4" s="185" t="str">
         <x:v>This Tuesday</x:v>
       </x:c>
-      <x:c r="H4" s="147" t="str">
+      <x:c r="H4" s="186" t="str">
         <x:v>Note</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="32" customHeight="1">
-      <x:c r="A5" s="131" t="str">
+      <x:c r="A5" s="173" t="str">
         <x:v>Housing</x:v>
       </x:c>
-      <x:c r="B5" s="131" t="str">
+      <x:c r="B5" s="173" t="str">
         <x:v>Rent — next month</x:v>
       </x:c>
-      <x:c r="C5" s="200" t="n">
-        <x:f>'Support - Budget Inputs'!E12</x:f>
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="D5" s="193" t="n">
+      <x:c r="C5" s="248" t="n">
+        <x:f>'2. Tuesday Review'!D13</x:f>
+        <x:v>178.49169230769235</x:v>
+      </x:c>
+      <x:c r="D5" s="241" t="n">
         <x:v>46296</x:v>
       </x:c>
-      <x:c r="E5" s="131" t="str">
+      <x:c r="E5" s="173" t="str">
         <x:v>Wealthfront rent bucket</x:v>
       </x:c>
-      <x:c r="F5" s="131" t="str">
+      <x:c r="F5" s="173" t="str">
         <x:v>Wealthfront to rent payment</x:v>
       </x:c>
-      <x:c r="G5" s="131" t="str">
-        <x:v>Rent-payment Tuesday: $0; then $300 x 4</x:v>
-      </x:c>
-      <x:c r="H5" s="131" t="str">
-        <x:v>Sep. 1 rent payment is $1,169.46 from prior contributions. No new contribution today; fund Sep. 8, 15, 22, and 29 for the October payment</x:v>
+      <x:c r="G5" s="173" t="str">
+        <x:v>Fund only Wells capacity, up to $300</x:v>
+      </x:c>
+      <x:c r="H5" s="173" t="str">
+        <x:v>Track the actual Tuesday contribution in Savings &amp; Debt. Do not assume a catch-up contribution is feasible.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="32" customHeight="1">
-      <x:c r="A6" s="131" t="str">
+      <x:c r="A6" s="173" t="str">
         <x:v>Auto loan</x:v>
       </x:c>
-      <x:c r="B6" s="131" t="str">
+      <x:c r="B6" s="173" t="str">
         <x:v>Genesis G70 / CUTX</x:v>
       </x:c>
-      <x:c r="C6" s="200" t="n">
+      <x:c r="C6" s="248" t="n">
         <x:f>'Support - Budget Inputs'!E13</x:f>
         <x:v>172.26230769230767</x:v>
       </x:c>
-      <x:c r="D6" s="193" t="n">
+      <x:c r="D6" s="241" t="n">
         <x:v>46292</x:v>
       </x:c>
-      <x:c r="E6" s="131" t="str">
+      <x:c r="E6" s="173" t="str">
         <x:v>Wealthfront car reserve</x:v>
       </x:c>
-      <x:c r="F6" s="131" t="str">
+      <x:c r="F6" s="173" t="str">
         <x:v>Wealthfront to CUTX on the 27th</x:v>
       </x:c>
-      <x:c r="G6" s="131" t="str">
+      <x:c r="G6" s="173" t="str">
         <x:v>Set aside the displayed weekly amount</x:v>
       </x:c>
-      <x:c r="H6" s="131" t="str">
+      <x:c r="H6" s="173" t="str">
         <x:v>Pay the exact $746.47 monthly amount. Do not reduce a direct weekly payment to $172.26 unless the reserve already bridges four-Tuesday months</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="32" customHeight="1">
-      <x:c r="A7" s="131" t="str">
+      <x:c r="A7" s="173" t="str">
         <x:v>PayPal promo</x:v>
       </x:c>
-      <x:c r="B7" s="131" t="str">
+      <x:c r="B7" s="173" t="str">
         <x:v>October deferred-interest payoff</x:v>
       </x:c>
-      <x:c r="C7" s="200" t="n">
+      <x:c r="C7" s="248" t="n">
         <x:f>'Support - Budget Inputs'!E20</x:f>
         <x:v>148.616</x:v>
       </x:c>
-      <x:c r="D7" s="193" t="n">
+      <x:c r="D7" s="241" t="n">
         <x:v>46305</x:v>
       </x:c>
-      <x:c r="E7" s="131" t="str">
+      <x:c r="E7" s="173" t="str">
         <x:v>Wells until paid</x:v>
       </x:c>
-      <x:c r="F7" s="131" t="str">
+      <x:c r="F7" s="173" t="str">
         <x:v>Wells to PayPal Credit</x:v>
       </x:c>
-      <x:c r="G7" s="131" t="str">
+      <x:c r="G7" s="173" t="str">
         <x:v>Pay scheduled promo amount</x:v>
       </x:c>
-      <x:c r="H7" s="131" t="str">
+      <x:c r="H7" s="173" t="str">
         <x:v>Funded separately from purchases so deferred interest is avoided</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="32" customHeight="1">
-      <x:c r="A8" s="131" t="str">
+      <x:c r="A8" s="173" t="str">
         <x:v>Phone</x:v>
       </x:c>
-      <x:c r="B8" s="131" t="str">
+      <x:c r="B8" s="173" t="str">
         <x:v>AT&amp;T wireless</x:v>
       </x:c>
-      <x:c r="C8" s="200" t="n">
+      <x:c r="C8" s="248" t="n">
         <x:f>'Support - Budget Inputs'!E15</x:f>
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="193" t="n">
+      <x:c r="D8" s="241" t="n">
         <x:v>46281</x:v>
       </x:c>
-      <x:c r="E8" s="131" t="str">
+      <x:c r="E8" s="173" t="str">
         <x:v>Wealthfront AT&amp;T reserve</x:v>
       </x:c>
-      <x:c r="F8" s="131" t="str">
+      <x:c r="F8" s="173" t="str">
         <x:v>Wealthfront to Wells; Wells AutoPay</x:v>
       </x:c>
-      <x:c r="G8" s="131" t="str">
+      <x:c r="G8" s="173" t="str">
         <x:v>Reserve this cycle's $88.59</x:v>
       </x:c>
-      <x:c r="H8" s="131" t="str">
+      <x:c r="H8" s="173" t="str">
         <x:v>Normal baseline remains $65/month; this cycle includes roaming</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="32" customHeight="1">
-      <x:c r="A9" s="131" t="str">
+      <x:c r="A9" s="173" t="str">
         <x:v>Student loan</x:v>
       </x:c>
-      <x:c r="B9" s="131" t="str">
+      <x:c r="B9" s="173" t="str">
         <x:v>RBC Canada student loan</x:v>
       </x:c>
-      <x:c r="C9" s="200" t="n">
+      <x:c r="C9" s="248" t="n">
         <x:f>'Support - Budget Inputs'!E21</x:f>
         <x:v>13.476923076923075</x:v>
       </x:c>
-      <x:c r="D9" s="193" t="n">
+      <x:c r="D9" s="241" t="n">
         <x:v>46295</x:v>
       </x:c>
-      <x:c r="E9" s="131" t="str">
+      <x:c r="E9" s="173" t="str">
         <x:v>Wealthfront Canada-bills reserve</x:v>
       </x:c>
-      <x:c r="F9" s="131" t="str">
+      <x:c r="F9" s="173" t="str">
         <x:v>Wealthfront to Wise to RBC</x:v>
       </x:c>
-      <x:c r="G9" s="131" t="str">
+      <x:c r="G9" s="173" t="str">
         <x:v>Continue weekly reserve</x:v>
       </x:c>
-      <x:c r="H9" s="131" t="str">
+      <x:c r="H9" s="173" t="str">
         <x:v>Debit occurs on the last day of each month; use Wise lead time</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="32" customHeight="1">
-      <x:c r="A10" s="131" t="str">
+      <x:c r="A10" s="173" t="str">
         <x:v>Insurance</x:v>
       </x:c>
-      <x:c r="B10" s="131" t="str">
+      <x:c r="B10" s="173" t="str">
         <x:v>Life insurance</x:v>
       </x:c>
-      <x:c r="C10" s="200" t="n">
+      <x:c r="C10" s="248" t="n">
         <x:f>'Support - Budget Inputs'!E22</x:f>
         <x:v>17.23866923076923</x:v>
       </x:c>
-      <x:c r="D10" s="193" t="n">
+      <x:c r="D10" s="241" t="n">
         <x:v>46292</x:v>
       </x:c>
-      <x:c r="E10" s="131" t="str">
+      <x:c r="E10" s="173" t="str">
         <x:v>Wealthfront Canada-bills reserve</x:v>
       </x:c>
-      <x:c r="F10" s="131" t="str">
+      <x:c r="F10" s="173" t="str">
         <x:v>Wealthfront to Wise to RBC</x:v>
       </x:c>
-      <x:c r="G10" s="131" t="str">
+      <x:c r="G10" s="173" t="str">
         <x:v>Continue weekly reserve</x:v>
       </x:c>
-      <x:c r="H10" s="131" t="str">
+      <x:c r="H10" s="173" t="str">
         <x:v>Debit occurs on the 27th; use Wise lead time</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="32" customHeight="1">
-      <x:c r="A11" s="131" t="str">
+      <x:c r="A11" s="173" t="str">
         <x:v>Pet</x:v>
       </x:c>
-      <x:c r="B11" s="131" t="str">
+      <x:c r="B11" s="173" t="str">
         <x:v>BudgetPetCare + grooming</x:v>
       </x:c>
-      <x:c r="C11" s="200" t="n">
+      <x:c r="C11" s="248" t="n">
         <x:f>'Support - Budget Inputs'!E26</x:f>
         <x:v>47.48076923076923</x:v>
       </x:c>
-      <x:c r="D11" s="193" t="n">
+      <x:c r="D11" s="241" t="n">
         <x:v>46311</x:v>
       </x:c>
-      <x:c r="E11" s="131" t="str">
+      <x:c r="E11" s="173" t="str">
         <x:v>Wealthfront pet reserve</x:v>
       </x:c>
-      <x:c r="F11" s="131" t="str">
+      <x:c r="F11" s="173" t="str">
         <x:v>Card / scheduled order</x:v>
       </x:c>
-      <x:c r="G11" s="131" t="str">
+      <x:c r="G11" s="173" t="str">
         <x:v>No separate transfer unless order is imminent</x:v>
       </x:c>
-      <x:c r="H11" s="131" t="str">
+      <x:c r="H11" s="173" t="str">
         <x:v>BudgetPetCare expected Oct. 16; grooming cadence is every five weeks</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="32" customHeight="1">
-      <x:c r="A12" s="131" t="str">
+      <x:c r="A12" s="173" t="str">
         <x:v>Card-funded spending</x:v>
       </x:c>
-      <x:c r="B12" s="131" t="str">
+      <x:c r="B12" s="173" t="str">
         <x:v>Weekly Scorecard categories</x:v>
       </x:c>
-      <x:c r="C12" s="200" t="n">
+      <x:c r="C12" s="248" t="n">
         <x:f>'3. This Week'!B23</x:f>
         <x:v>476.6607692307693</x:v>
       </x:c>
-      <x:c r="D12" s="131" t="str">
+      <x:c r="D12" s="173" t="str">
         <x:v>Every Tuesday — next card payoff</x:v>
       </x:c>
-      <x:c r="E12" s="131" t="str">
+      <x:c r="E12" s="173" t="str">
         <x:v>Wells available cash until card payoff</x:v>
       </x:c>
-      <x:c r="F12" s="131" t="str">
+      <x:c r="F12" s="173" t="str">
         <x:v>Chase / Citi / Prime then weekly payoff</x:v>
       </x:c>
-      <x:c r="G12" s="131" t="str">
+      <x:c r="G12" s="173" t="str">
         <x:v>Spend only within Scorecard targets</x:v>
       </x:c>
-      <x:c r="H12" s="131" t="str">
+      <x:c r="H12" s="173" t="str">
         <x:v>Do not create a duplicate reserve for items charged to a card and paid next Tuesday</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="32" customHeight="1">
-      <x:c r="A13" s="131" t="str">
+      <x:c r="A13" s="173" t="str">
         <x:v>Education</x:v>
       </x:c>
-      <x:c r="B13" s="131" t="str">
+      <x:c r="B13" s="173" t="str">
         <x:v>Del Mar tuition savings</x:v>
       </x:c>
-      <x:c r="C13" s="200" t="n">
+      <x:c r="C13" s="248" t="n">
         <x:f>'5. Savings &amp; Debt'!B15</x:f>
         <x:v>193.36</x:v>
       </x:c>
-      <x:c r="D13" s="131" t="str">
+      <x:c r="D13" s="173" t="str">
         <x:v>Every Tuesday</x:v>
       </x:c>
-      <x:c r="E13" s="131" t="str">
+      <x:c r="E13" s="173" t="str">
         <x:v>PayPal savings</x:v>
       </x:c>
-      <x:c r="F13" s="131" t="str">
+      <x:c r="F13" s="173" t="str">
         <x:v>Automatic PayPal savings transfer</x:v>
       </x:c>
-      <x:c r="G13" s="131" t="str">
+      <x:c r="G13" s="173" t="str">
         <x:v>No manual action</x:v>
       </x:c>
-      <x:c r="H13" s="131" t="str">
+      <x:c r="H13" s="173" t="str">
         <x:v>New automated weekly tuition bucket; cumulative amount is on Savings &amp; Debt</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="32" customHeight="1">
-      <x:c r="A14" s="131" t="str">
+      <x:c r="A14" s="173" t="str">
         <x:v>Future expenses</x:v>
       </x:c>
-      <x:c r="B14" s="131" t="str">
+      <x:c r="B14" s="173" t="str">
         <x:v>PayPal future-expenses fund</x:v>
       </x:c>
-      <x:c r="C14" s="200" t="n">
+      <x:c r="C14" s="248" t="n">
         <x:f>'5. Savings &amp; Debt'!B16</x:f>
         <x:v>50</x:v>
       </x:c>
-      <x:c r="D14" s="131" t="str">
+      <x:c r="D14" s="173" t="str">
         <x:v>Every Tuesday</x:v>
       </x:c>
-      <x:c r="E14" s="131" t="str">
+      <x:c r="E14" s="173" t="str">
         <x:v>PayPal savings</x:v>
       </x:c>
-      <x:c r="F14" s="131" t="str">
+      <x:c r="F14" s="173" t="str">
         <x:v>Automatic PayPal savings transfer</x:v>
       </x:c>
-      <x:c r="G14" s="131" t="str">
+      <x:c r="G14" s="173" t="str">
         <x:v>No manual action</x:v>
       </x:c>
-      <x:c r="H14" s="131" t="str">
+      <x:c r="H14" s="173" t="str">
         <x:v>New automated weekly future-expenses bucket; cumulative amount is on Savings &amp; Debt</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="131"/>
-      <x:c r="B15" s="131"/>
-      <x:c r="C15" s="131"/>
-      <x:c r="D15" s="131"/>
-      <x:c r="E15" s="131"/>
-      <x:c r="F15" s="131"/>
-      <x:c r="G15" s="131"/>
-      <x:c r="H15" s="131"/>
+      <x:c r="A15" s="173"/>
+      <x:c r="B15" s="173"/>
+      <x:c r="C15" s="173"/>
+      <x:c r="D15" s="173"/>
+      <x:c r="E15" s="173"/>
+      <x:c r="F15" s="173"/>
+      <x:c r="G15" s="173"/>
+      <x:c r="H15" s="173"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="132" t="str">
+      <x:c r="A16" s="174" t="str">
         <x:v>Archived payment log — Sep 2</x:v>
       </x:c>
-      <x:c r="B16" s="132"/>
-      <x:c r="C16" s="132"/>
-      <x:c r="D16" s="132"/>
-      <x:c r="E16" s="132"/>
-      <x:c r="F16" s="132"/>
-      <x:c r="G16" s="132"/>
-      <x:c r="H16" s="132"/>
+      <x:c r="B16" s="174"/>
+      <x:c r="C16" s="174"/>
+      <x:c r="D16" s="174"/>
+      <x:c r="E16" s="174"/>
+      <x:c r="F16" s="174"/>
+      <x:c r="G16" s="174"/>
+      <x:c r="H16" s="174"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="131"/>
-      <x:c r="B17" s="131"/>
-      <x:c r="C17" s="131"/>
-      <x:c r="D17" s="131"/>
-      <x:c r="E17" s="131"/>
-      <x:c r="F17" s="131"/>
-      <x:c r="G17" s="131"/>
-      <x:c r="H17" s="131"/>
+      <x:c r="A17" s="173"/>
+      <x:c r="B17" s="173"/>
+      <x:c r="C17" s="173"/>
+      <x:c r="D17" s="173"/>
+      <x:c r="E17" s="173"/>
+      <x:c r="F17" s="173"/>
+      <x:c r="G17" s="173"/>
+      <x:c r="H17" s="173"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="145" t="str">
+      <x:c r="A18" s="184" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="B18" s="146" t="str">
+      <x:c r="B18" s="185" t="str">
         <x:v>Payment or transfer</x:v>
       </x:c>
-      <x:c r="C18" s="146" t="str">
+      <x:c r="C18" s="185" t="str">
         <x:v>Basis</x:v>
       </x:c>
-      <x:c r="D18" s="146" t="str">
+      <x:c r="D18" s="185" t="str">
         <x:v>Planned</x:v>
       </x:c>
-      <x:c r="E18" s="146" t="str">
+      <x:c r="E18" s="185" t="str">
         <x:v>Completed</x:v>
       </x:c>
-      <x:c r="F18" s="146" t="str">
+      <x:c r="F18" s="185" t="str">
         <x:v>Status</x:v>
       </x:c>
-      <x:c r="G18" s="147" t="str">
+      <x:c r="G18" s="186" t="str">
         <x:v>Confirmation</x:v>
       </x:c>
-      <x:c r="H18" s="131"/>
+      <x:c r="H18" s="173"/>
     </x:row>
     <x:row r="19" ht="24" customHeight="1">
-      <x:c r="A19" s="131" t="str">
+      <x:c r="A19" s="173" t="str">
         <x:v>Card payment</x:v>
       </x:c>
-      <x:c r="B19" s="131" t="str">
+      <x:c r="B19" s="173" t="str">
         <x:v>Chase Sapphire</x:v>
       </x:c>
-      <x:c r="C19" s="131" t="str">
+      <x:c r="C19" s="173" t="str">
         <x:v>Balance at Sep. 2 review</x:v>
       </x:c>
-      <x:c r="D19" s="150" t="n">
+      <x:c r="D19" s="189" t="n">
         <x:v>72.61</x:v>
       </x:c>
-      <x:c r="E19" s="150" t="n">
+      <x:c r="E19" s="189" t="n">
         <x:v>72.61</x:v>
       </x:c>
-      <x:c r="F19" s="131" t="str">
+      <x:c r="F19" s="173" t="str">
         <x:v>✓ Done</x:v>
       </x:c>
-      <x:c r="G19" s="131" t="str">
+      <x:c r="G19" s="173" t="str">
         <x:v>Paid Sep. 2</x:v>
       </x:c>
-      <x:c r="H19" s="131"/>
+      <x:c r="H19" s="173"/>
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
-      <x:c r="A20" s="131" t="str">
+      <x:c r="A20" s="173" t="str">
         <x:v>Card payment</x:v>
       </x:c>
-      <x:c r="B20" s="131" t="str">
+      <x:c r="B20" s="173" t="str">
         <x:v>Citi card</x:v>
       </x:c>
-      <x:c r="C20" s="131" t="str">
+      <x:c r="C20" s="173" t="str">
         <x:v>Balance at Sep. 2 review</x:v>
       </x:c>
-      <x:c r="D20" s="150" t="n">
+      <x:c r="D20" s="189" t="n">
         <x:v>79.46</x:v>
       </x:c>
-      <x:c r="E20" s="150" t="n">
+      <x:c r="E20" s="189" t="n">
         <x:v>79.46</x:v>
       </x:c>
-      <x:c r="F20" s="131" t="str">
+      <x:c r="F20" s="173" t="str">
         <x:v>✓ Done</x:v>
       </x:c>
-      <x:c r="G20" s="131" t="str">
+      <x:c r="G20" s="173" t="str">
         <x:v>Paid Sep. 2</x:v>
       </x:c>
-      <x:c r="H20" s="131"/>
+      <x:c r="H20" s="173"/>
     </x:row>
     <x:row r="21" ht="24" customHeight="1">
-      <x:c r="A21" s="131" t="str">
+      <x:c r="A21" s="173" t="str">
         <x:v>Card payment</x:v>
       </x:c>
-      <x:c r="B21" s="131" t="str">
+      <x:c r="B21" s="173" t="str">
         <x:v>Prime Visa</x:v>
       </x:c>
-      <x:c r="C21" s="131" t="str">
+      <x:c r="C21" s="173" t="str">
         <x:v>No balance due</x:v>
       </x:c>
-      <x:c r="D21" s="150" t="n">
+      <x:c r="D21" s="189" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E21" s="150" t="n">
+      <x:c r="E21" s="189" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F21" s="131" t="str">
+      <x:c r="F21" s="173" t="str">
         <x:v>✓ Done</x:v>
       </x:c>
-      <x:c r="G21" s="131" t="str">
+      <x:c r="G21" s="173" t="str">
         <x:v>Not due</x:v>
       </x:c>
-      <x:c r="H21" s="131"/>
+      <x:c r="H21" s="173"/>
     </x:row>
     <x:row r="22" ht="24" customHeight="1">
-      <x:c r="A22" s="131" t="str">
+      <x:c r="A22" s="173" t="str">
         <x:v>Debt payment</x:v>
       </x:c>
-      <x:c r="B22" s="131" t="str">
+      <x:c r="B22" s="173" t="str">
         <x:v>PayPal promotional payoff</x:v>
       </x:c>
-      <x:c r="C22" s="131" t="str">
+      <x:c r="C22" s="173" t="str">
         <x:v>Weekly promo payoff</x:v>
       </x:c>
-      <x:c r="D22" s="150" t="n">
+      <x:c r="D22" s="189" t="n">
         <x:v>148.65</x:v>
       </x:c>
-      <x:c r="E22" s="150" t="n">
+      <x:c r="E22" s="189" t="n">
         <x:v>148.65</x:v>
       </x:c>
-      <x:c r="F22" s="131" t="str">
+      <x:c r="F22" s="173" t="str">
         <x:v>✓ Done</x:v>
       </x:c>
-      <x:c r="G22" s="131" t="str">
+      <x:c r="G22" s="173" t="str">
         <x:v>Paid Sep. 2</x:v>
       </x:c>
-      <x:c r="H22" s="131"/>
+      <x:c r="H22" s="173"/>
     </x:row>
     <x:row r="23" ht="24" customHeight="1">
-      <x:c r="A23" s="131" t="str">
+      <x:c r="A23" s="173" t="str">
         <x:v>Transfer</x:v>
       </x:c>
-      <x:c r="B23" s="131" t="str">
+      <x:c r="B23" s="173" t="str">
         <x:v>Rent fund — next month</x:v>
       </x:c>
-      <x:c r="C23" s="131" t="str">
+      <x:c r="C23" s="173" t="str">
         <x:v>Rent-payment Tuesday</x:v>
       </x:c>
-      <x:c r="D23" s="150" t="n">
+      <x:c r="D23" s="189" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E23" s="150" t="n">
+      <x:c r="E23" s="189" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F23" s="131" t="str">
+      <x:c r="F23" s="173" t="str">
         <x:v>✓ Done</x:v>
       </x:c>
-      <x:c r="G23" s="131" t="str">
+      <x:c r="G23" s="173" t="str">
         <x:v>No deposit on rent-payment Tuesday</x:v>
       </x:c>
-      <x:c r="H23" s="131"/>
+      <x:c r="H23" s="173"/>
     </x:row>
     <x:row r="24" ht="24" customHeight="1">
-      <x:c r="A24" s="131" t="str">
+      <x:c r="A24" s="173" t="str">
         <x:v>Rent payment</x:v>
       </x:c>
-      <x:c r="B24" s="131" t="str">
+      <x:c r="B24" s="173" t="str">
         <x:v>September rent — current month</x:v>
       </x:c>
-      <x:c r="C24" s="131" t="str">
+      <x:c r="C24" s="173" t="str">
         <x:v>Due Sep. 1</x:v>
       </x:c>
-      <x:c r="D24" s="150" t="n">
+      <x:c r="D24" s="189" t="n">
         <x:v>1169.46</x:v>
       </x:c>
-      <x:c r="E24" s="150" t="n">
+      <x:c r="E24" s="189" t="n">
         <x:v>1169.46</x:v>
       </x:c>
-      <x:c r="F24" s="131" t="str">
+      <x:c r="F24" s="173" t="str">
         <x:v>✓ Done</x:v>
       </x:c>
-      <x:c r="G24" s="131" t="str">
+      <x:c r="G24" s="173" t="str">
         <x:v>Paid from Wells after Wealthfront transfer</x:v>
       </x:c>
-      <x:c r="H24" s="131"/>
+      <x:c r="H24" s="173"/>
     </x:row>
     <x:row r="25" ht="24" customHeight="1">
-      <x:c r="A25" s="131" t="str">
+      <x:c r="A25" s="173" t="str">
         <x:v>Automatic</x:v>
       </x:c>
-      <x:c r="B25" s="131" t="str">
+      <x:c r="B25" s="173" t="str">
         <x:v>Fidelity 401(k)</x:v>
       </x:c>
-      <x:c r="C25" s="131" t="str">
+      <x:c r="C25" s="173" t="str">
         <x:v>Weekly automatic transfer</x:v>
       </x:c>
-      <x:c r="D25" s="150" t="n">
+      <x:c r="D25" s="189" t="n">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="E25" s="150" t="n">
+      <x:c r="E25" s="189" t="n">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="F25" s="131" t="str">
+      <x:c r="F25" s="173" t="str">
         <x:v>✓ Done</x:v>
       </x:c>
-      <x:c r="G25" s="131" t="str">
+      <x:c r="G25" s="173" t="str">
         <x:v>Confirmed at later review</x:v>
       </x:c>
-      <x:c r="H25" s="131"/>
+      <x:c r="H25" s="173"/>
     </x:row>
     <x:row r="26" ht="24" customHeight="1">
-      <x:c r="A26" s="131" t="str">
+      <x:c r="A26" s="173" t="str">
         <x:v>Automatic</x:v>
       </x:c>
-      <x:c r="B26" s="131" t="str">
+      <x:c r="B26" s="173" t="str">
         <x:v>PayPal cruise savings</x:v>
       </x:c>
-      <x:c r="C26" s="131" t="str">
+      <x:c r="C26" s="173" t="str">
         <x:v>Weekly automatic transfer</x:v>
       </x:c>
-      <x:c r="D26" s="150" t="n">
+      <x:c r="D26" s="189" t="n">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="E26" s="150" t="n">
+      <x:c r="E26" s="189" t="n">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="F26" s="131" t="str">
+      <x:c r="F26" s="173" t="str">
         <x:v>✓ Done</x:v>
       </x:c>
-      <x:c r="G26" s="131" t="str">
+      <x:c r="G26" s="173" t="str">
         <x:v>Confirmed at later review</x:v>
       </x:c>
-      <x:c r="H26" s="131"/>
+      <x:c r="H26" s="173"/>
     </x:row>
     <x:row r="27" ht="24" customHeight="1">
-      <x:c r="A27" s="131" t="str">
+      <x:c r="A27" s="173" t="str">
         <x:v>Automatic</x:v>
       </x:c>
-      <x:c r="B27" s="131" t="str">
+      <x:c r="B27" s="173" t="str">
         <x:v>PayPal tuition savings</x:v>
       </x:c>
-      <x:c r="C27" s="131" t="str">
+      <x:c r="C27" s="173" t="str">
         <x:v>Weekly automatic transfer</x:v>
       </x:c>
-      <x:c r="D27" s="150" t="n">
+      <x:c r="D27" s="189" t="n">
         <x:v>193.36</x:v>
       </x:c>
-      <x:c r="E27" s="150" t="n">
+      <x:c r="E27" s="189" t="n">
         <x:v>193.36</x:v>
       </x:c>
-      <x:c r="F27" s="131" t="str">
+      <x:c r="F27" s="173" t="str">
         <x:v>✓ Done</x:v>
       </x:c>
-      <x:c r="G27" s="131" t="str">
+      <x:c r="G27" s="173" t="str">
         <x:v>Confirmed at later review</x:v>
       </x:c>
-      <x:c r="H27" s="131"/>
+      <x:c r="H27" s="173"/>
     </x:row>
     <x:row r="28" ht="24" customHeight="1">
-      <x:c r="A28" s="131" t="str">
+      <x:c r="A28" s="173" t="str">
         <x:v>Automatic</x:v>
       </x:c>
-      <x:c r="B28" s="131" t="str">
+      <x:c r="B28" s="173" t="str">
         <x:v>PayPal future-expenses savings</x:v>
       </x:c>
-      <x:c r="C28" s="131" t="str">
+      <x:c r="C28" s="173" t="str">
         <x:v>Weekly automatic transfer</x:v>
       </x:c>
-      <x:c r="D28" s="150" t="n">
+      <x:c r="D28" s="189" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="E28" s="150" t="n">
+      <x:c r="E28" s="189" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="F28" s="131" t="str">
+      <x:c r="F28" s="173" t="str">
         <x:v>✓ Done</x:v>
       </x:c>
-      <x:c r="G28" s="131" t="str">
+      <x:c r="G28" s="173" t="str">
         <x:v>Confirmed at later review</x:v>
       </x:c>
-      <x:c r="H28" s="131"/>
+      <x:c r="H28" s="173"/>
     </x:row>
     <x:row r="29" ht="24" customHeight="1">
-      <x:c r="A29" s="131" t="str">
+      <x:c r="A29" s="173" t="str">
         <x:v>Transfer</x:v>
       </x:c>
-      <x:c r="B29" s="131" t="str">
+      <x:c r="B29" s="173" t="str">
         <x:v>Car fund / CUTX</x:v>
       </x:c>
-      <x:c r="C29" s="131" t="str">
+      <x:c r="C29" s="173" t="str">
         <x:v>Weekly reserve funding</x:v>
       </x:c>
-      <x:c r="D29" s="150" t="n">
+      <x:c r="D29" s="189" t="n">
         <x:v>172.26230769230767</x:v>
       </x:c>
-      <x:c r="E29" s="150" t="n">
+      <x:c r="E29" s="189" t="n">
         <x:v>172.26230769230767</x:v>
       </x:c>
-      <x:c r="F29" s="131" t="str">
+      <x:c r="F29" s="173" t="str">
         <x:v>✓ Done</x:v>
       </x:c>
-      <x:c r="G29" s="131" t="str">
+      <x:c r="G29" s="173" t="str">
         <x:v>Reserve funding completed</x:v>
       </x:c>
-      <x:c r="H29" s="131"/>
+      <x:c r="H29" s="173"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/outputs/01a04fdf-3751-72e2-88f1-daf19b8b9d1d/comprehensive_budget.xlsx
+++ b/outputs/01a04fdf-3751-72e2-88f1-daf19b8b9d1d/comprehensive_budget.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Start" sheetId="1" r:id="R8dce6b1616b44a7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Tuesday Review" sheetId="2" r:id="R20f8461391724fc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. This Week" sheetId="3" r:id="R63f3503aa61a4806"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Money Plan" sheetId="4" r:id="R39f6aa95fd3d4945"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Savings &amp; Debt" sheetId="5" r:id="Rb9845a1e90d0469c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. History" sheetId="6" r:id="R6e8d62f2685446fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Ledger" sheetId="7" r:id="R2cd3accae9fc4d5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Budget Inputs" sheetId="8" r:id="Rdf917bcb6cf2450f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Funding Detail" sheetId="9" r:id="R2b8d8271aa944d5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Debt Detail" sheetId="10" r:id="R4817fb1a492140e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Promo Detail" sheetId="11" r:id="Rd338409f71d74478"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Account Snapshots" sheetId="12" r:id="R41f15c41e3524239"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Pending Review" sheetId="13" r:id="Ra17a62bfcbe949b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Rules" sheetId="14" r:id="Re84c0c0b40724d21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Sources" sheetId="15" r:id="Ra37e92f0c0cf43c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Start" sheetId="1" r:id="R7d34f157624144c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Tuesday Review" sheetId="2" r:id="R67dd815b795643e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. This Week" sheetId="3" r:id="R113e1022a6f94610"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Money Plan" sheetId="4" r:id="Rf266c8b308bf481d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Savings &amp; Debt" sheetId="5" r:id="Rc9b85580c6d44334"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. History" sheetId="6" r:id="R71ed4a4e1be64cdd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Ledger" sheetId="7" r:id="Rfa48ec52d0be4b5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Budget Inputs" sheetId="8" r:id="R395cc778a23e4481"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Funding Detail" sheetId="9" r:id="Rba81e62b0f414c26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Debt Detail" sheetId="10" r:id="Rdef0ebc893be4770"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Promo Detail" sheetId="11" r:id="R63371b06745143e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Account Snapshots" sheetId="12" r:id="R0adc42b3e1364f29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Pending Review" sheetId="13" r:id="R0b0f34c7f8a64950"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Rules" sheetId="14" r:id="R80f91267578f4cda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Sources" sheetId="15" r:id="Ra34b38ca413045fe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2776,7 +2776,7 @@
         <x:v>Personal safe cash</x:v>
       </x:c>
       <x:c r="C7" s="42" t="n">
-        <x:v>60</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="D7" s="42" t="n">
         <x:v>0</x:v>
@@ -2785,10 +2785,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F7" s="42" t="n">
-        <x:v>60</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="G7" s="36" t="str">
-        <x:v>Wife’s income held as cash; excluded from Wells/Wealthfront funding</x:v>
+        <x:v>Wife’s Sep. 9 income held as cash; excluded from Wells/Wealthfront funding</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -4108,16 +4108,16 @@
         <x:v>Wells Fargo checking</x:v>
       </x:c>
       <x:c r="B4" s="36" t="str">
-        <x:v>Income and recurring payments</x:v>
+        <x:v>Sep. 9 balance + operating history</x:v>
       </x:c>
       <x:c r="C4" s="36" t="str">
-        <x:v>Jul 8-Aug 7, 2026</x:v>
+        <x:v>Sep 9, 2026</x:v>
       </x:c>
       <x:c r="D4" s="36" t="str">
-        <x:v>Weekly $1,343.37 payroll; $75/week automatic Fidelity 401(k) transfer; rent rebuilt at $300 on each of the four Tuesdays after a rent payment; prior $188 weekly Credit Union of Texas car-loan transfers</x:v>
+        <x:v>Available Wells $1,227.78 after pending Fidelity debit; pending payroll $1,343.38; wife’s $160 income is held in the personal safe</x:v>
       </x:c>
       <x:c r="E4" s="36" t="str">
-        <x:v>The prior $805 UMB category was an assumption and has been removed from savings. Rent paid Sep. 1 uses the existing Wealthfront rent bucket; no new rent deposit is made on that payment Tuesday. The next four Tuesday deposits are $300 each ($1,200 total) for the October payment. Fund the car at the annualized rate ($746.47 x 12 / 52) in a reserve, then pay the exact monthly amount on the 27th. An $85 Tuesday Wells Fargo-to-PayPal cruise transfer begins Sep. 1; $50/week is added for a Wealthfront future-expenses fund. AT&amp;T normal baseline is $65/month; Sep. 16 autopay is $88.59 due to a one-time roaming charge.</x:v>
+        <x:v>The earlier Jul–Aug account history establishes the $1,343.37 recurring-payroll baseline and $75 weekly Fidelity transfer. The Sep. 9 balance controls this live review. Rent funding is limited to verified Wells capacity after required actions, not a forced $300 deposit.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -5381,7 +5381,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="5" t="str">
-        <x:v>Use this on payday. Pay or move the listed amounts, then record only unexpected spending below. Statements are a monthly audit, not a required monthly rebuild.</x:v>
+        <x:v>Use this ongoing guide after the live Tuesday Review. It reflects the Sep. 9 import inputs; the current rent contribution is calculated in Tuesday Review and recorded in Savings &amp; Debt.</x:v>
       </x:c>
       <x:c r="B2" s="5"/>
       <x:c r="C2" s="5"/>
@@ -5746,7 +5746,7 @@
       </x:c>
       <x:c r="B25" s="42" t="n">
         <x:f>'Support - Budget Inputs'!D8</x:f>
-        <x:v>1403.37</x:v>
+        <x:v>1503.37</x:v>
       </x:c>
       <x:c r="C25" s="36"/>
       <x:c r="D25" s="36"/>
@@ -5759,7 +5759,7 @@
       </x:c>
       <x:c r="B26" s="217" t="n">
         <x:f>'Support - Budget Inputs'!D7</x:f>
-        <x:v>60</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C26" s="216"/>
       <x:c r="D26" s="216"/>
@@ -5785,7 +5785,7 @@
       </x:c>
       <x:c r="B28" s="49" t="n">
         <x:f>B25-B23</x:f>
-        <x:v>-128.24466923076943</x:v>
+        <x:v>-28.244669230769432</x:v>
       </x:c>
       <x:c r="C28" s="48"/>
       <x:c r="D28" s="50"/>
@@ -6015,7 +6015,7 @@
       </x:c>
       <x:c r="B6" s="169" t="n">
         <x:f>'Support - Account Snapshots'!F7</x:f>
-        <x:v>60</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C6" s="178" t="str">
         <x:v>Rent due estimate</x:v>
@@ -6033,7 +6033,7 @@
       </x:c>
       <x:c r="B7" s="180" t="n">
         <x:f>SUM(B5:B6)</x:f>
-        <x:v>11907.64</x:v>
+        <x:v>12007.64</x:v>
       </x:c>
       <x:c r="C7" s="178" t="str">
         <x:v>Tagged rent reserve</x:v>
@@ -6069,7 +6069,7 @@
       </x:c>
       <x:c r="B9" s="170" t="n">
         <x:f>B7-B8</x:f>
-        <x:v>-78.33070000000225</x:v>
+        <x:v>21.669299999997747</x:v>
       </x:c>
       <x:c r="C9" s="183" t="str">
         <x:v>Confirmed funding vs. monthly plan</x:v>
@@ -6587,7 +6587,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="247" t="str">
-        <x:v>History — Closed Weeks</x:v>
+        <x:v>History — Weekly Record</x:v>
       </x:c>
       <x:c r="B1" s="247"/>
       <x:c r="C1" s="247"/>
@@ -6675,7 +6675,7 @@
         <x:v>Notes</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="24" customHeight="1">
+    <x:row r="5" ht="42" customHeight="1">
       <x:c r="A5" s="242" t="n">
         <x:v>46266</x:v>
       </x:c>
@@ -6722,7 +6722,7 @@
         <x:v>Legacy baseline: no full line-level source archive existed before the Sep. 9 audit. Do not treat this row as source-certified.</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="24" customHeight="1">
+    <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="242" t="n">
         <x:v>46273</x:v>
       </x:c>
@@ -6734,11 +6734,17 @@
         <x:f>A6-1</x:f>
         <x:v>46272</x:v>
       </x:c>
-      <x:c r="D6" s="189"/>
-      <x:c r="E6" s="189"/>
-      <x:c r="F6" s="189"/>
+      <x:c r="D6" s="189" t="n">
+        <x:v>1227.78</x:v>
+      </x:c>
+      <x:c r="E6" s="189" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F6" s="189" t="n">
+        <x:v>1226.78</x:v>
+      </x:c>
       <x:c r="G6" s="188" t="str">
-        <x:v>Data verified — Sep 9</x:v>
+        <x:v>Plan created — Sep 9</x:v>
       </x:c>
       <x:c r="H6" s="189" t="n">
         <x:v>476.6607692307693</x:v>
@@ -6760,7 +6766,7 @@
         <x:v>26.17076923076928</x:v>
       </x:c>
       <x:c r="M6" s="188" t="str">
-        <x:v>Reviewed Wed Sep. 9 because of the holiday delay. Source-controlled import includes the Citi activity correction.</x:v>
+        <x:v>Reviewed Wed Sep. 9 because of the holiday delay. The source-controlled import is verified and the $1,226.78 cash plan is ready for execution; it is not marked completed yet.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
@@ -7591,7 +7597,7 @@
   </x:conditionalFormatting>
   <x:dataValidations count="1">
     <x:dataValidation type="list" sqref="G5:G30">
-      <x:formula1>"In progress,Data verified — Sep 9,Legacy — not source-audited,✓ Completed,Needs review"</x:formula1>
+      <x:formula1>"In progress,Plan created — Sep 9,Data verified — Sep 9,Legacy — not source-audited,✓ Completed,Needs review"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14526,17 +14532,17 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="36" t="str">
-        <x:v>Wife income (variable — personal safe)</x:v>
+        <x:v>Wife income (personal safe — Sep 9 actual)</x:v>
       </x:c>
       <x:c r="B7" s="36" t="str">
         <x:v>Weekly</x:v>
       </x:c>
       <x:c r="C7" s="41" t="n">
-        <x:v>60</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="D7" s="42" t="n">
         <x:f>IF(B7="Weekly",C7,C7*12/52)</x:f>
-        <x:v>60</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="E7" s="36"/>
       <x:c r="F7" s="36"/>
@@ -14549,7 +14555,7 @@
       <x:c r="C8" s="43"/>
       <x:c r="D8" s="44" t="n">
         <x:f>SUM(D6:D7)</x:f>
-        <x:v>1403.37</x:v>
+        <x:v>1503.37</x:v>
       </x:c>
       <x:c r="E8" s="36"/>
       <x:c r="F8" s="36"/>
@@ -15046,7 +15052,7 @@
       <x:c r="D34" s="49"/>
       <x:c r="E34" s="49" t="n">
         <x:f>D8-E32</x:f>
-        <x:v>-128.24466923076943</x:v>
+        <x:v>-28.244669230769432</x:v>
       </x:c>
       <x:c r="F34" s="50"/>
     </x:row>

--- a/outputs/01a04fdf-3751-72e2-88f1-daf19b8b9d1d/comprehensive_budget.xlsx
+++ b/outputs/01a04fdf-3751-72e2-88f1-daf19b8b9d1d/comprehensive_budget.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Start" sheetId="1" r:id="R7d34f157624144c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Tuesday Review" sheetId="2" r:id="R67dd815b795643e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. This Week" sheetId="3" r:id="R113e1022a6f94610"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Money Plan" sheetId="4" r:id="Rf266c8b308bf481d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Savings &amp; Debt" sheetId="5" r:id="Rc9b85580c6d44334"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. History" sheetId="6" r:id="R71ed4a4e1be64cdd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Ledger" sheetId="7" r:id="Rfa48ec52d0be4b5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Budget Inputs" sheetId="8" r:id="R395cc778a23e4481"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Funding Detail" sheetId="9" r:id="Rba81e62b0f414c26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Debt Detail" sheetId="10" r:id="Rdef0ebc893be4770"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Promo Detail" sheetId="11" r:id="R63371b06745143e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Account Snapshots" sheetId="12" r:id="R0adc42b3e1364f29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Pending Review" sheetId="13" r:id="R0b0f34c7f8a64950"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Rules" sheetId="14" r:id="R80f91267578f4cda"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Sources" sheetId="15" r:id="Ra34b38ca413045fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Start" sheetId="1" r:id="Rf398eaa1560b4adf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Tuesday Review" sheetId="2" r:id="R312c22abc6d6419d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. This Week" sheetId="3" r:id="R8bab0e0419bd49f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Money Plan" sheetId="4" r:id="Rfe035943d3584a4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Savings &amp; Debt" sheetId="5" r:id="R0c52b85a53f34508"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. History" sheetId="6" r:id="R6adddfb3df154af3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Ledger" sheetId="7" r:id="R3e4a55aab8b8449d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Budget Inputs" sheetId="8" r:id="R94b85015d2ea4cb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Funding Detail" sheetId="9" r:id="R6989b51a9e164106"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Debt Detail" sheetId="10" r:id="R95ff324414fc4c6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Promo Detail" sheetId="11" r:id="R4e5ae8a4bf7d4d9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Account Snapshots" sheetId="12" r:id="Rfddbde0f9c9d4251"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Pending Review" sheetId="13" r:id="R5effc21d8585403f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Rules" sheetId="14" r:id="Ra7a5f222eafa4b11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Sources" sheetId="15" r:id="R27e6824df9c24744"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2776,7 +2776,7 @@
         <x:v>Personal safe cash</x:v>
       </x:c>
       <x:c r="C7" s="42" t="n">
-        <x:v>160</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="D7" s="42" t="n">
         <x:v>0</x:v>
@@ -2785,10 +2785,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F7" s="42" t="n">
-        <x:v>160</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G7" s="36" t="str">
-        <x:v>Wife’s Sep. 9 income held as cash; excluded from Wells/Wealthfront funding</x:v>
+        <x:v>Wife’s Sep. 9 income held as cash; $160 added to the prior $60. Excluded from Wells/Wealthfront funding.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -4114,7 +4114,7 @@
         <x:v>Sep 9, 2026</x:v>
       </x:c>
       <x:c r="D4" s="36" t="str">
-        <x:v>Available Wells $1,227.78 after pending Fidelity debit; pending payroll $1,343.38; wife’s $160 income is held in the personal safe</x:v>
+        <x:v>Available Wells $1,227.78 after pending Fidelity debit; pending payroll $1,343.38; wife’s $220 total income is held in the personal safe</x:v>
       </x:c>
       <x:c r="E4" s="36" t="str">
         <x:v>The earlier Jul–Aug account history establishes the $1,343.37 recurring-payroll baseline and $75 weekly Fidelity transfer. The Sep. 9 balance controls this live review. Rent funding is limited to verified Wells capacity after required actions, not a forced $300 deposit.</x:v>
@@ -5746,7 +5746,7 @@
       </x:c>
       <x:c r="B25" s="42" t="n">
         <x:f>'Support - Budget Inputs'!D8</x:f>
-        <x:v>1503.37</x:v>
+        <x:v>1563.37</x:v>
       </x:c>
       <x:c r="C25" s="36"/>
       <x:c r="D25" s="36"/>
@@ -5759,7 +5759,7 @@
       </x:c>
       <x:c r="B26" s="217" t="n">
         <x:f>'Support - Budget Inputs'!D7</x:f>
-        <x:v>160</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C26" s="216"/>
       <x:c r="D26" s="216"/>
@@ -5785,7 +5785,7 @@
       </x:c>
       <x:c r="B28" s="49" t="n">
         <x:f>B25-B23</x:f>
-        <x:v>-28.244669230769432</x:v>
+        <x:v>31.755330769230568</x:v>
       </x:c>
       <x:c r="C28" s="48"/>
       <x:c r="D28" s="50"/>
@@ -6015,7 +6015,7 @@
       </x:c>
       <x:c r="B6" s="169" t="n">
         <x:f>'Support - Account Snapshots'!F7</x:f>
-        <x:v>160</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C6" s="178" t="str">
         <x:v>Rent due estimate</x:v>
@@ -6033,7 +6033,7 @@
       </x:c>
       <x:c r="B7" s="180" t="n">
         <x:f>SUM(B5:B6)</x:f>
-        <x:v>12007.64</x:v>
+        <x:v>12067.64</x:v>
       </x:c>
       <x:c r="C7" s="178" t="str">
         <x:v>Tagged rent reserve</x:v>
@@ -6069,7 +6069,7 @@
       </x:c>
       <x:c r="B9" s="170" t="n">
         <x:f>B7-B8</x:f>
-        <x:v>21.669299999997747</x:v>
+        <x:v>81.66929999999775</x:v>
       </x:c>
       <x:c r="C9" s="183" t="str">
         <x:v>Confirmed funding vs. monthly plan</x:v>
@@ -14532,17 +14532,17 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="36" t="str">
-        <x:v>Wife income (personal safe — Sep 9 actual)</x:v>
+        <x:v>Wife income (personal safe — Sep 9 total)</x:v>
       </x:c>
       <x:c r="B7" s="36" t="str">
         <x:v>Weekly</x:v>
       </x:c>
       <x:c r="C7" s="41" t="n">
-        <x:v>160</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="D7" s="42" t="n">
         <x:f>IF(B7="Weekly",C7,C7*12/52)</x:f>
-        <x:v>160</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="E7" s="36"/>
       <x:c r="F7" s="36"/>
@@ -14555,7 +14555,7 @@
       <x:c r="C8" s="43"/>
       <x:c r="D8" s="44" t="n">
         <x:f>SUM(D6:D7)</x:f>
-        <x:v>1503.37</x:v>
+        <x:v>1563.37</x:v>
       </x:c>
       <x:c r="E8" s="36"/>
       <x:c r="F8" s="36"/>
@@ -15052,7 +15052,7 @@
       <x:c r="D34" s="49"/>
       <x:c r="E34" s="49" t="n">
         <x:f>D8-E32</x:f>
-        <x:v>-28.244669230769432</x:v>
+        <x:v>31.755330769230568</x:v>
       </x:c>
       <x:c r="F34" s="50"/>
     </x:row>

--- a/outputs/01a04fdf-3751-72e2-88f1-daf19b8b9d1d/comprehensive_budget.xlsx
+++ b/outputs/01a04fdf-3751-72e2-88f1-daf19b8b9d1d/comprehensive_budget.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Start" sheetId="1" r:id="Rf398eaa1560b4adf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Tuesday Review" sheetId="2" r:id="R312c22abc6d6419d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. This Week" sheetId="3" r:id="R8bab0e0419bd49f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Money Plan" sheetId="4" r:id="Rfe035943d3584a4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Savings &amp; Debt" sheetId="5" r:id="R0c52b85a53f34508"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. History" sheetId="6" r:id="R6adddfb3df154af3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Ledger" sheetId="7" r:id="R3e4a55aab8b8449d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Budget Inputs" sheetId="8" r:id="R94b85015d2ea4cb0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Funding Detail" sheetId="9" r:id="R6989b51a9e164106"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Debt Detail" sheetId="10" r:id="R95ff324414fc4c6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Promo Detail" sheetId="11" r:id="R4e5ae8a4bf7d4d9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Account Snapshots" sheetId="12" r:id="Rfddbde0f9c9d4251"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Pending Review" sheetId="13" r:id="R5effc21d8585403f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Rules" sheetId="14" r:id="Ra7a5f222eafa4b11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Sources" sheetId="15" r:id="R27e6824df9c24744"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Start" sheetId="1" r:id="Rba18838499cf4a6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Tuesday Review" sheetId="2" r:id="Rd93fb7a100674c45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. This Week" sheetId="3" r:id="Rdd9f984027b4483f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Money Plan" sheetId="4" r:id="Rcbb60a861807497a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Savings &amp; Debt" sheetId="5" r:id="R846af412b47e4e74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. History" sheetId="6" r:id="R46890bf36ef0464e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Ledger" sheetId="7" r:id="R1b52cd76d74c4d4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Budget Inputs" sheetId="8" r:id="Rff817b8e88004d72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Funding Detail" sheetId="9" r:id="Rfab73a1dbf9f4da9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Debt Detail" sheetId="10" r:id="Rf45b14a99b8647f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Promo Detail" sheetId="11" r:id="R654ac55aed664095"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Account Snapshots" sheetId="12" r:id="R03b507273b2f4a0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Pending Review" sheetId="13" r:id="R2212354bf1974d39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Rules" sheetId="14" r:id="Rcc24325d07224147"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Sources" sheetId="15" r:id="R8604b36102634008"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/outputs/01a04fdf-3751-72e2-88f1-daf19b8b9d1d/comprehensive_budget.xlsx
+++ b/outputs/01a04fdf-3751-72e2-88f1-daf19b8b9d1d/comprehensive_budget.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Start" sheetId="1" r:id="Rba18838499cf4a6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Tuesday Review" sheetId="2" r:id="Rd93fb7a100674c45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. This Week" sheetId="3" r:id="Rdd9f984027b4483f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Money Plan" sheetId="4" r:id="Rcbb60a861807497a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Savings &amp; Debt" sheetId="5" r:id="R846af412b47e4e74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. History" sheetId="6" r:id="R46890bf36ef0464e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Ledger" sheetId="7" r:id="R1b52cd76d74c4d4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Budget Inputs" sheetId="8" r:id="Rff817b8e88004d72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Funding Detail" sheetId="9" r:id="Rfab73a1dbf9f4da9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Debt Detail" sheetId="10" r:id="Rf45b14a99b8647f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Promo Detail" sheetId="11" r:id="R654ac55aed664095"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Account Snapshots" sheetId="12" r:id="R03b507273b2f4a0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Pending Review" sheetId="13" r:id="R2212354bf1974d39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Rules" sheetId="14" r:id="Rcc24325d07224147"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Sources" sheetId="15" r:id="R8604b36102634008"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Start" sheetId="1" r:id="R6086c57efebf46f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Tuesday Review" sheetId="2" r:id="R008fe77a5cd842ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. This Week" sheetId="3" r:id="Rbb229010cea64a3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Money Plan" sheetId="4" r:id="Rd904b14ef5db496d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Savings &amp; Debt" sheetId="5" r:id="Rfd39959521da4793"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. History" sheetId="6" r:id="Rc04da9df1bbe4552"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Ledger" sheetId="7" r:id="R83f1f046232b481e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Budget Inputs" sheetId="8" r:id="Ra79412a9bbed43f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Funding Detail" sheetId="9" r:id="Rdf1335c2861a4555"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Debt Detail" sheetId="10" r:id="R6452a32044574189"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Promo Detail" sheetId="11" r:id="R30575320ea054184"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Account Snapshots" sheetId="12" r:id="R310f3391558144b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Pending Review" sheetId="13" r:id="R1dac5b1eb40d4422"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Rules" sheetId="14" r:id="R0835bd802e3a4617"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Sources" sheetId="15" r:id="R2165ea6366c74dc9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5653,7 +5653,7 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="36" t="str">
-        <x:v>Pet</x:v>
+        <x:v>Pet care + Nationwide insurance</x:v>
       </x:c>
       <x:c r="B19" s="42" t="n">
         <x:f>'Support - Budget Inputs'!E26</x:f>
@@ -5663,7 +5663,7 @@
         <x:v>Use as weekly envelope</x:v>
       </x:c>
       <x:c r="D19" s="36" t="str">
-        <x:v>Formula from weekly budget</x:v>
+        <x:v>Includes $48.27/month Nationwide pet insurance</x:v>
       </x:c>
       <x:c r="E19" s="36"/>
       <x:c r="F19" s="36"/>
@@ -5781,11 +5781,11 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="47" t="str">
-        <x:v>Household weekly buffer / shortfall</x:v>
+        <x:v>Weekly buffer / shortfall from banking income</x:v>
       </x:c>
       <x:c r="B28" s="49" t="n">
-        <x:f>B25-B23</x:f>
-        <x:v>31.755330769230568</x:v>
+        <x:f>B27-B23</x:f>
+        <x:v>-188.24466923076943</x:v>
       </x:c>
       <x:c r="C28" s="48"/>
       <x:c r="D28" s="50"/>
@@ -15387,7 +15387,7 @@
         <x:v>Pet</x:v>
       </x:c>
       <x:c r="B11" s="173" t="str">
-        <x:v>BudgetPetCare + grooming</x:v>
+        <x:v>Nationwide insurance + BudgetPetCare + grooming</x:v>
       </x:c>
       <x:c r="C11" s="248" t="n">
         <x:f>'Support - Budget Inputs'!E26</x:f>

--- a/outputs/01a04fdf-3751-72e2-88f1-daf19b8b9d1d/comprehensive_budget.xlsx
+++ b/outputs/01a04fdf-3751-72e2-88f1-daf19b8b9d1d/comprehensive_budget.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Start" sheetId="1" r:id="Rd6c0d134c11b4c7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Tuesday Review" sheetId="2" r:id="R89b34f3634104d05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. This Week" sheetId="3" r:id="R28119a27c9cb479f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Money Plan" sheetId="4" r:id="R04814f1484da4b05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Savings &amp; Debt" sheetId="5" r:id="R02ecf9df589a446c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. History" sheetId="6" r:id="Rcba7abf432ba43dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Ledger" sheetId="7" r:id="R2395564062f44e72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Budget Inputs" sheetId="8" r:id="R9a05857416684f14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Funding Detail" sheetId="9" r:id="R54317c2a17f3427d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Debt Detail" sheetId="10" r:id="R684dfd8a8a0445e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Promo Detail" sheetId="11" r:id="Ra4cbf5fe36ee4e29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Account Snapshots" sheetId="12" r:id="Refd189a4a42a4f58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Pending Review" sheetId="13" r:id="R081d8886e9044352"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Rules" sheetId="14" r:id="R660cb61b351d474a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Sources" sheetId="15" r:id="R1f6970fb754948dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Start" sheetId="1" r:id="R8680f6dd342149e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Tuesday Review" sheetId="2" r:id="Rbe2ffdc4096a48ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. This Week" sheetId="3" r:id="R9dd9cb422ca34209"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Money Plan" sheetId="4" r:id="Rbe77311ed4a84312"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Savings &amp; Debt" sheetId="5" r:id="R555dd8c26dde464e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. History" sheetId="6" r:id="R64747f67acd8486a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Ledger" sheetId="7" r:id="R7f55fcdfd49c484e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Budget Inputs" sheetId="8" r:id="Red0e40b1cfc94df0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Funding Detail" sheetId="9" r:id="R5c3cdc40f6104cfa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Debt Detail" sheetId="10" r:id="R7696725fa0914ef0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Promo Detail" sheetId="11" r:id="Re01bcc785712437d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Account Snapshots" sheetId="12" r:id="R86c32bf2a72f4bfe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Pending Review" sheetId="13" r:id="R8b6efbda20c34993"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Rules" sheetId="14" r:id="Rd47c5298df364203"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Sources" sheetId="15" r:id="R81124eeafab14937"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5242,8 +5242,8 @@
         <x:v>Sep 1–Sep 7 purchases</x:v>
       </x:c>
       <x:c r="C6" s="393" t="str">
-        <x:f>COUNTIF(F9:F19,"✓ Done")&amp;" / "&amp;COUNTA(B9:B19)&amp;" actions completed"</x:f>
-        <x:v>1 / 11 actions completed</x:v>
+        <x:f>COUNTIF(F9:F19,"Done")&amp;" / "&amp;COUNTA(B9:B19)&amp;" actions completed"</x:f>
+        <x:v>4 / 11 actions completed</x:v>
       </x:c>
       <x:c r="D6" s="393" t="str">
         <x:v>Use now</x:v>
@@ -5430,7 +5430,7 @@
       </x:c>
       <x:c r="E15" s="395"/>
       <x:c r="F15" s="404" t="str">
-        <x:v>✓ Done</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="G15" s="362" t="str">
         <x:v>Do not count again in cash required</x:v>
@@ -5451,7 +5451,7 @@
       </x:c>
       <x:c r="E16" s="395"/>
       <x:c r="F16" s="404" t="str">
-        <x:v>Scheduled</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="G16" s="362" t="str">
         <x:v>Included in cash required; confirm after it posts</x:v>
@@ -5472,7 +5472,7 @@
       </x:c>
       <x:c r="E17" s="395"/>
       <x:c r="F17" s="404" t="str">
-        <x:v>Scheduled</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="G17" s="362" t="str">
         <x:v>Included in cash required; confirm after it posts</x:v>
@@ -5493,7 +5493,7 @@
       </x:c>
       <x:c r="E18" s="395"/>
       <x:c r="F18" s="404" t="str">
-        <x:v>Scheduled</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="G18" s="362" t="str">
         <x:v>Included in cash required; confirm after it posts</x:v>
@@ -5603,7 +5603,7 @@
   </x:mergeCells>
   <x:dataValidations count="1">
     <x:dataValidation type="list" sqref="F9:F19">
-      <x:formula1>"Not done,✓ Done,Not due,Scheduled,Deferred,Partial"</x:formula1>
+      <x:formula1>"Not done,Done,✓ Done,Not due,Scheduled,Deferred,Partial"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/outputs/01a04fdf-3751-72e2-88f1-daf19b8b9d1d/comprehensive_budget.xlsx
+++ b/outputs/01a04fdf-3751-72e2-88f1-daf19b8b9d1d/comprehensive_budget.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Start" sheetId="1" r:id="R8680f6dd342149e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Tuesday Review" sheetId="2" r:id="Rbe2ffdc4096a48ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. This Week" sheetId="3" r:id="R9dd9cb422ca34209"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Money Plan" sheetId="4" r:id="Rbe77311ed4a84312"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Savings &amp; Debt" sheetId="5" r:id="R555dd8c26dde464e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. History" sheetId="6" r:id="R64747f67acd8486a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Ledger" sheetId="7" r:id="R7f55fcdfd49c484e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Budget Inputs" sheetId="8" r:id="Red0e40b1cfc94df0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Funding Detail" sheetId="9" r:id="R5c3cdc40f6104cfa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Debt Detail" sheetId="10" r:id="R7696725fa0914ef0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Promo Detail" sheetId="11" r:id="Re01bcc785712437d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Account Snapshots" sheetId="12" r:id="R86c32bf2a72f4bfe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Pending Review" sheetId="13" r:id="R8b6efbda20c34993"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Rules" sheetId="14" r:id="Rd47c5298df364203"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Sources" sheetId="15" r:id="R81124eeafab14937"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Start" sheetId="1" r:id="R6f6fde561c3f491f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Tuesday Review" sheetId="2" r:id="R1a67045b52a24eb8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. This Week" sheetId="3" r:id="R9c4c2cf399b94c60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Money Plan" sheetId="4" r:id="R2d08efb0edda43fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Savings &amp; Debt" sheetId="5" r:id="Rd3ddf2c687514154"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. History" sheetId="6" r:id="R8566afad8e744fab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Ledger" sheetId="7" r:id="R85f4c16fec7b4abc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Budget Inputs" sheetId="8" r:id="Re967410d93a1466c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Funding Detail" sheetId="9" r:id="R766f33863c88424e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Debt Detail" sheetId="10" r:id="R7f80bbc84b854878"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Promo Detail" sheetId="11" r:id="R1b6a7984461e4f32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Account Snapshots" sheetId="12" r:id="R4b15b3dcf01048ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Pending Review" sheetId="13" r:id="R544422b8de8d4dbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Rules" sheetId="14" r:id="Raab1e6aa63ab4311"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Sources" sheetId="15" r:id="Ree1306e0197b4ec5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2570,6 +2570,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF173F5F"/>
+  </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="29" hidden="0" customWidth="1"/>
@@ -2902,6 +2905,9 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FFCBD5E1"/>
+  </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
@@ -3207,6 +3213,9 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FFCBD5E1"/>
+  </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
@@ -3450,6 +3459,9 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FFCBD5E1"/>
+  </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
@@ -3978,6 +3990,9 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FFCBD5E1"/>
+  </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
@@ -4440,6 +4455,9 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FFCBD5E1"/>
+  </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
@@ -4947,6 +4965,9 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FFCBD5E1"/>
+  </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
@@ -5163,6 +5184,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF173F5F"/>
+  </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
@@ -5612,6 +5636,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF173F5F"/>
+  </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="29" hidden="0" customWidth="1"/>
@@ -6245,6 +6272,9 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF6B4F9B"/>
+  </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
@@ -6829,6 +6859,9 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF0F766E"/>
+  </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
@@ -7454,6 +7487,9 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF566575"/>
+  </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="17" hidden="0" customWidth="1"/>
@@ -8492,6 +8528,9 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FFCBD5E1"/>
+  </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
@@ -15350,6 +15389,9 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FFCBD5E1"/>
+  </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
@@ -16049,6 +16091,9 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FFCBD5E1"/>
+  </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>

--- a/outputs/01a04fdf-3751-72e2-88f1-daf19b8b9d1d/comprehensive_budget.xlsx
+++ b/outputs/01a04fdf-3751-72e2-88f1-daf19b8b9d1d/comprehensive_budget.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Start" sheetId="1" r:id="R6f6fde561c3f491f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Tuesday Review" sheetId="2" r:id="R1a67045b52a24eb8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. This Week" sheetId="3" r:id="R9c4c2cf399b94c60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Money Plan" sheetId="4" r:id="R2d08efb0edda43fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Savings &amp; Debt" sheetId="5" r:id="Rd3ddf2c687514154"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. History" sheetId="6" r:id="R8566afad8e744fab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Ledger" sheetId="7" r:id="R85f4c16fec7b4abc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Budget Inputs" sheetId="8" r:id="Re967410d93a1466c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Funding Detail" sheetId="9" r:id="R766f33863c88424e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Debt Detail" sheetId="10" r:id="R7f80bbc84b854878"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Promo Detail" sheetId="11" r:id="R1b6a7984461e4f32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Account Snapshots" sheetId="12" r:id="R4b15b3dcf01048ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Pending Review" sheetId="13" r:id="R544422b8de8d4dbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Rules" sheetId="14" r:id="Raab1e6aa63ab4311"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Sources" sheetId="15" r:id="Ree1306e0197b4ec5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Start" sheetId="1" r:id="R05c9632189474eb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Tuesday Review" sheetId="2" r:id="Rab5b53a9dfac4b74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. This Week" sheetId="3" r:id="Rcda536e589074692"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Money Plan" sheetId="4" r:id="R1a4a0b916bca4c83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Savings &amp; Debt" sheetId="5" r:id="R370bd46d5f624597"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. History" sheetId="6" r:id="Rb81f56e531bd4a2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Ledger" sheetId="7" r:id="Rf2d1f9acfab24e8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Budget Inputs" sheetId="8" r:id="R7ff3f238ba024ffb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Funding Detail" sheetId="9" r:id="Rd63df3d526874574"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Debt Detail" sheetId="10" r:id="Rf34858d6597d4605"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Promo Detail" sheetId="11" r:id="Rfcd1c5c17b714e3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Account Snapshots" sheetId="12" r:id="R13c14963ef374241"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Pending Review" sheetId="13" r:id="Rdd751b484e7c4b74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Rules" sheetId="14" r:id="R6879fe08dfab4994"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Sources" sheetId="15" r:id="R8e2fed3642c84911"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -654,14 +654,14 @@
     <x:xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -697,6 +697,9 @@
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="200" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
@@ -704,9 +707,6 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5021,10 +5021,10 @@
         <x:v>Sep 9, 2026</x:v>
       </x:c>
       <x:c r="D4" s="362" t="str">
-        <x:v>Available Wells $1,227.78 after pending Fidelity debit; pending payroll $1,343.38; wife’s $220 total income is held in the personal safe</x:v>
+        <x:v>Available Wells $1,227.78 after pending Fidelity debit; personal-safe balance $220 includes the earlier $60 plus an additional $160</x:v>
       </x:c>
       <x:c r="E4" s="362" t="str">
-        <x:v>The earlier Jul–Aug account history establishes the $1,343.37 recurring-payroll baseline and $75 weekly Fidelity transfer. The Sep. 9 balance controls this live review. Rent funding is limited to verified Wells capacity after required actions, not a forced $300 deposit.</x:v>
+        <x:v>The earlier Jul–Aug account history establishes the $1,343.37 recurring-payroll baseline and $75 weekly Fidelity transfer. Personal-safe cash is savings-only and excluded from Wells cash-plan and spending-capacity calculations. The Sep. 9 Wells balance controls this live review.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -6658,11 +6658,11 @@
     </x:row>
     <x:row r="25" ht="25" customHeight="1">
       <x:c r="A25" s="362" t="str">
-        <x:v>Total weekly household income</x:v>
+        <x:v>Usable weekly income — Wells plan</x:v>
       </x:c>
       <x:c r="B25" s="445" t="n">
         <x:f>'Support - Budget Inputs'!D8</x:f>
-        <x:v>1563.37</x:v>
+        <x:v>1343.37</x:v>
       </x:c>
       <x:c r="C25" s="362"/>
       <x:c r="D25" s="362"/>
@@ -6671,10 +6671,10 @@
     </x:row>
     <x:row r="26" ht="25" customHeight="1">
       <x:c r="A26" s="401" t="str">
-        <x:v>Personal-safe income — included in household total</x:v>
+        <x:v>Personal-safe balance — savings only</x:v>
       </x:c>
       <x:c r="B26" s="446" t="n">
-        <x:f>'Support - Budget Inputs'!D7</x:f>
+        <x:f>'Support - Account Snapshots'!F7</x:f>
         <x:v>220</x:v>
       </x:c>
       <x:c r="C26" s="401"/>
@@ -6684,10 +6684,10 @@
     </x:row>
     <x:row r="27" ht="25" customHeight="1">
       <x:c r="A27" s="393" t="str">
-        <x:v>Banking income available for Wells plan</x:v>
+        <x:v>Income used by this plan</x:v>
       </x:c>
       <x:c r="B27" s="447" t="n">
-        <x:f>B25-B26</x:f>
+        <x:f>B25</x:f>
         <x:v>1343.37</x:v>
       </x:c>
       <x:c r="C27" s="393"/>
@@ -6697,7 +6697,7 @@
     </x:row>
     <x:row r="28" ht="25" customHeight="1">
       <x:c r="A28" s="436" t="str">
-        <x:v>Weekly buffer / shortfall from banking income</x:v>
+        <x:v>Weekly buffer / shortfall from Wells income</x:v>
       </x:c>
       <x:c r="B28" s="448" t="n">
         <x:f>B27-B23</x:f>
@@ -15475,30 +15475,30 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="362" t="str">
-        <x:v>Wife income (personal safe — Sep 9 total)</x:v>
+        <x:v>Personal-safe balance (excluded from Wells plan)</x:v>
       </x:c>
       <x:c r="B7" s="362" t="str">
-        <x:v>Weekly</x:v>
-      </x:c>
-      <x:c r="C7" s="396" t="n">
+        <x:v>Balance</x:v>
+      </x:c>
+      <x:c r="C7" s="394" t="n">
+        <x:f>'Support - Account Snapshots'!F7</x:f>
         <x:v>220</x:v>
       </x:c>
-      <x:c r="D7" s="416" t="n">
-        <x:f>IF(B7="Weekly",C7,C7*12/52)</x:f>
-        <x:v>220</x:v>
+      <x:c r="D7" s="394" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E7" s="362"/>
       <x:c r="F7" s="362"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="417" t="str">
-        <x:v>Total net income</x:v>
+        <x:v>Usable weekly income — Wells plan</x:v>
       </x:c>
       <x:c r="B8" s="417"/>
-      <x:c r="C8" s="417"/>
+      <x:c r="C8" s="418"/>
       <x:c r="D8" s="418" t="n">
-        <x:f>SUM(D6:D7)</x:f>
-        <x:v>1563.37</x:v>
+        <x:f>D6</x:f>
+        <x:v>1343.37</x:v>
       </x:c>
       <x:c r="E8" s="362"/>
       <x:c r="F8" s="362"/>
@@ -15995,7 +15995,7 @@
       <x:c r="D34" s="437"/>
       <x:c r="E34" s="437" t="n">
         <x:f>D8-E32</x:f>
-        <x:v>31.755330769230568</x:v>
+        <x:v>-188.24466923076943</x:v>
       </x:c>
       <x:c r="F34" s="439"/>
     </x:row>

--- a/outputs/01a04fdf-3751-72e2-88f1-daf19b8b9d1d/comprehensive_budget.xlsx
+++ b/outputs/01a04fdf-3751-72e2-88f1-daf19b8b9d1d/comprehensive_budget.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Start" sheetId="1" r:id="R05c9632189474eb7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Tuesday Review" sheetId="2" r:id="Rab5b53a9dfac4b74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. This Week" sheetId="3" r:id="Rcda536e589074692"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Money Plan" sheetId="4" r:id="R1a4a0b916bca4c83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Savings &amp; Debt" sheetId="5" r:id="R370bd46d5f624597"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. History" sheetId="6" r:id="Rb81f56e531bd4a2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Ledger" sheetId="7" r:id="Rf2d1f9acfab24e8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Budget Inputs" sheetId="8" r:id="R7ff3f238ba024ffb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Funding Detail" sheetId="9" r:id="Rd63df3d526874574"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Debt Detail" sheetId="10" r:id="Rf34858d6597d4605"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Promo Detail" sheetId="11" r:id="Rfcd1c5c17b714e3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Account Snapshots" sheetId="12" r:id="R13c14963ef374241"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Pending Review" sheetId="13" r:id="Rdd751b484e7c4b74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Rules" sheetId="14" r:id="R6879fe08dfab4994"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Sources" sheetId="15" r:id="R8e2fed3642c84911"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Start" sheetId="1" r:id="Rd99719b0078b4bd0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Tuesday Review" sheetId="2" r:id="Rd3305aaae7964f0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. This Week" sheetId="3" r:id="R699f6b3090244759"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Money Plan" sheetId="4" r:id="Rb00db621722645b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Savings &amp; Debt" sheetId="5" r:id="R71f8582e29304588"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. History" sheetId="6" r:id="R3e1861bacdef47c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Ledger" sheetId="7" r:id="R67d51dfed13c41dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Budget Inputs" sheetId="8" r:id="Ra5b9cdefb41d4b49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Funding Detail" sheetId="9" r:id="R43d1c89a6ebb49de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Debt Detail" sheetId="10" r:id="Rcf20d5580f65424e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Promo Detail" sheetId="11" r:id="R67b7455b383d4672"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Account Snapshots" sheetId="12" r:id="R0eae1fde02f54517"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Pending Review" sheetId="13" r:id="Raf5bcc4c0f2b473d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Rules" sheetId="14" r:id="R680e87be54cc4bd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Sources" sheetId="15" r:id="R4feb8ff3c0fc4f3a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4861,7 +4861,7 @@
         <x:v>Fidelity</x:v>
       </x:c>
       <x:c r="B25" s="581" t="str">
-        <x:v>Fidelity 401(k)</x:v>
+        <x:v>Fidelity Roth IRA</x:v>
       </x:c>
       <x:c r="C25" s="581" t="str">
         <x:v>Transfer / verify</x:v>
@@ -5444,7 +5444,7 @@
         <x:v>Automatic</x:v>
       </x:c>
       <x:c r="B15" s="362" t="str">
-        <x:v>Fidelity 401(k)</x:v>
+        <x:v>Fidelity Roth IRA</x:v>
       </x:c>
       <x:c r="C15" s="362" t="str">
         <x:v>Pending; already in Wells available balance</x:v>
@@ -6603,14 +6603,14 @@
     </x:row>
     <x:row r="21" ht="38" customHeight="1">
       <x:c r="A21" s="362" t="str">
-        <x:v>Fidelity + PayPal savings buckets</x:v>
+        <x:v>Fidelity Roth IRA + PayPal savings buckets</x:v>
       </x:c>
       <x:c r="B21" s="416" t="n">
         <x:f>'Support - Budget Inputs'!E27</x:f>
         <x:v>403.36</x:v>
       </x:c>
       <x:c r="C21" s="362" t="str">
-        <x:v>$75 Fidelity plus $85 cruise, $193.36 tuition, and $50 future fund automatically</x:v>
+        <x:v>$75 Roth IRA plus $85 cruise, $193.36 tuition, and $50 future fund automatically</x:v>
       </x:c>
       <x:c r="D21" s="362" t="str">
         <x:v>Formula from weekly budget</x:v>
@@ -7036,7 +7036,7 @@
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
       <x:c r="A13" s="362" t="str">
-        <x:v>Fidelity 401(k)</x:v>
+        <x:v>Fidelity Roth IRA</x:v>
       </x:c>
       <x:c r="B13" s="395" t="n">
         <x:v>75</x:v>
@@ -15864,7 +15864,7 @@
         <x:v>Savings</x:v>
       </x:c>
       <x:c r="B27" s="362" t="str">
-        <x:v>Fidelity + PayPal savings buckets</x:v>
+        <x:v>Fidelity Roth IRA + PayPal savings buckets</x:v>
       </x:c>
       <x:c r="C27" s="362" t="str">
         <x:v>Weekly</x:v>
@@ -15878,7 +15878,7 @@
         <x:v>403.36</x:v>
       </x:c>
       <x:c r="F27" s="362" t="str">
-        <x:v>$75 Fidelity plus automatic PayPal savings for cruise, tuition, and future expenses</x:v>
+        <x:v>$75 Roth IRA transfer plus automatic PayPal savings for cruise, tuition, and future expenses</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -16641,7 +16641,7 @@
         <x:v>Automatic</x:v>
       </x:c>
       <x:c r="B25" s="362" t="str">
-        <x:v>Fidelity 401(k)</x:v>
+        <x:v>Fidelity Roth IRA</x:v>
       </x:c>
       <x:c r="C25" s="362" t="str">
         <x:v>Weekly automatic transfer</x:v>

--- a/outputs/01a04fdf-3751-72e2-88f1-daf19b8b9d1d/comprehensive_budget.xlsx
+++ b/outputs/01a04fdf-3751-72e2-88f1-daf19b8b9d1d/comprehensive_budget.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Start" sheetId="1" r:id="Rd99719b0078b4bd0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Tuesday Review" sheetId="2" r:id="Rd3305aaae7964f0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. This Week" sheetId="3" r:id="R699f6b3090244759"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Money Plan" sheetId="4" r:id="Rb00db621722645b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Savings &amp; Debt" sheetId="5" r:id="R71f8582e29304588"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. History" sheetId="6" r:id="R3e1861bacdef47c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Ledger" sheetId="7" r:id="R67d51dfed13c41dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Budget Inputs" sheetId="8" r:id="Ra5b9cdefb41d4b49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Funding Detail" sheetId="9" r:id="R43d1c89a6ebb49de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Debt Detail" sheetId="10" r:id="Rcf20d5580f65424e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Promo Detail" sheetId="11" r:id="R67b7455b383d4672"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Account Snapshots" sheetId="12" r:id="R0eae1fde02f54517"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Pending Review" sheetId="13" r:id="Raf5bcc4c0f2b473d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Rules" sheetId="14" r:id="R680e87be54cc4bd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Sources" sheetId="15" r:id="R4feb8ff3c0fc4f3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Start" sheetId="1" r:id="R4565538089304063"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Tuesday Review" sheetId="2" r:id="R55002e43eb554e20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. This Week" sheetId="3" r:id="R6df0ed9da5ed42a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Money Plan" sheetId="4" r:id="R7e0dfc1259fa4191"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Savings &amp; Debt" sheetId="5" r:id="R1b2f56d55d9b4c40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. History" sheetId="6" r:id="R2a3fde61469249fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Ledger" sheetId="7" r:id="R8021ef8519484e9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Budget Inputs" sheetId="8" r:id="R202ff23997a24c0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Funding Detail" sheetId="9" r:id="R52e008cf3a8c4337"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Debt Detail" sheetId="10" r:id="Ra529a9e7e1044af5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Promo Detail" sheetId="11" r:id="Rb88f4ea7747944e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Account Snapshots" sheetId="12" r:id="R2dbd043a4c3c4f41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Pending Review" sheetId="13" r:id="R0d7eff0af0e04e57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Rules" sheetId="14" r:id="R888a69301d3a46b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support - Sources" sheetId="15" r:id="R51a69a6aeeee42f5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5211,7 +5211,7 @@
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="377" t="str">
-        <x:v>Use this live checklist after Start is verified. Planned amounts come from the Sep. 9 account snapshots and funding rules. Done means no further action is needed from you; a bank transaction may still be pending settlement. Scheduled means a transfer is expected but not yet confirmed.</x:v>
+        <x:v>Use this live checklist after Start is verified. Done means no manual action is required. Automatic transfers remain part of the cash plan even when marked Done; bank settlement is verified at the next weekly import.</x:v>
       </x:c>
       <x:c r="B2" s="377"/>
       <x:c r="C2" s="377"/>
@@ -5478,7 +5478,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="G16" s="362" t="str">
-        <x:v>Included in cash required; confirm after it posts</x:v>
+        <x:v>Automatic commitment; included in cash required</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="28" customHeight="1">
@@ -5499,7 +5499,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="G17" s="362" t="str">
-        <x:v>Included in cash required; confirm after it posts</x:v>
+        <x:v>Automatic commitment; included in cash required</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="28" customHeight="1">
@@ -5520,7 +5520,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="G18" s="362" t="str">
-        <x:v>Included in cash required; confirm after it posts</x:v>
+        <x:v>Automatic commitment; included in cash required</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="28" customHeight="1">
